--- a/__docs/RoadMap.xlsx
+++ b/__docs/RoadMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0708A4E6-49BE-4C40-A9E4-908FC9D529E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79947B38-ADA6-402B-BFF0-903C6756C414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тезисы" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="466">
   <si>
     <t>RL3 - это продолжение RL1</t>
   </si>
@@ -1457,6 +1457,12 @@
   </si>
   <si>
     <t>Анализ, фикс проблем</t>
+  </si>
+  <si>
+    <t>Работа над OrderCords</t>
+  </si>
+  <si>
+    <t>Убрал систему large</t>
   </si>
 </sst>
 </file>
@@ -5204,6 +5210,12 @@
       <c r="E4" t="s">
         <v>31</v>
       </c>
+      <c r="F4" s="3">
+        <v>46283</v>
+      </c>
+      <c r="G4" t="s">
+        <v>465</v>
+      </c>
       <c r="H4" t="s">
         <v>37</v>
       </c>
@@ -12253,6 +12265,12 @@
       <c r="B2" t="s">
         <v>28</v>
       </c>
+      <c r="C2" s="3">
+        <v>46283</v>
+      </c>
+      <c r="D2" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B3" t="s">

--- a/__docs/RoadMap.xlsx
+++ b/__docs/RoadMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79947B38-ADA6-402B-BFF0-903C6756C414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5607667F-174C-434C-83ED-4E4553462BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тезисы" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="471">
   <si>
     <t>RL3 - это продолжение RL1</t>
   </si>
@@ -1463,6 +1463,21 @@
   </si>
   <si>
     <t>Убрал систему large</t>
+  </si>
+  <si>
+    <t>UEG4_CANADIAN</t>
+  </si>
+  <si>
+    <t>4 версия GGD</t>
+  </si>
+  <si>
+    <t>Устарел</t>
+  </si>
+  <si>
+    <t>Плохие результаты</t>
+  </si>
+  <si>
+    <t>add_zigzag_window_210926</t>
   </si>
 </sst>
 </file>
@@ -1505,7 +1520,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1530,6 +1545,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1543,7 +1564,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1553,9 +1574,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -1573,6 +1591,12 @@
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1909,7 +1933,7 @@
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="16" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -1917,13 +1941,13 @@
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="13"/>
+      <c r="B4" s="16"/>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="16" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1931,43 +1955,43 @@
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="13"/>
+      <c r="B6" s="16"/>
       <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="13"/>
+      <c r="B7" s="16"/>
       <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="13"/>
+      <c r="B8" s="16"/>
       <c r="C8" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="13"/>
+      <c r="B9" s="16"/>
       <c r="C9" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="13"/>
+      <c r="B10" s="16"/>
       <c r="C10" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="13"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="13"/>
+      <c r="B12" s="16"/>
       <c r="C12" s="2" t="s">
         <v>17</v>
       </c>
@@ -2029,7 +2053,7 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C3" s="3">
@@ -5170,7 +5194,7 @@
       </c>
       <c r="O2">
         <f>COUNTIF(D:D,O1)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P2">
         <f>COUNTIF(D:D,P1)</f>
@@ -5195,25 +5219,25 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="A4" s="14">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="15">
         <v>46237</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="15">
         <v>46283</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="14" t="s">
         <v>465</v>
       </c>
       <c r="H4" t="s">
@@ -5258,25 +5282,25 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="A7" s="14">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="15">
         <v>46248</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="14" t="s">
         <v>432</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="15">
         <v>46267</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="14" t="s">
         <v>457</v>
       </c>
     </row>
@@ -5332,20 +5356,26 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="A11" s="14">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="15">
         <v>46248</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="14" t="s">
         <v>432</v>
+      </c>
+      <c r="F11" s="15">
+        <v>46286</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -5451,71 +5481,71 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="A18" s="14">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="15">
         <v>46248</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="14" t="s">
         <v>432</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="15">
         <v>46267</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="14" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="A19" s="14">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="15">
         <v>46248</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="14" t="s">
         <v>432</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="15">
         <v>46267</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="14" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="A20" s="14">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="15">
         <v>46248</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="14" t="s">
         <v>432</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="15">
         <v>46267</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="14" t="s">
         <v>457</v>
       </c>
     </row>
@@ -5724,94 +5754,118 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33">
+      <c r="A33" s="14">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="15">
         <v>46248</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="15">
         <v>46266</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" s="14" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34">
+      <c r="A34" s="14">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="15">
         <v>46248</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="14" t="s">
         <v>432</v>
       </c>
+      <c r="F34" s="15">
+        <v>46286</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>468</v>
+      </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35">
+      <c r="A35" s="14">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="14" t="s">
         <v>324</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="15">
         <v>46248</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="14" t="s">
         <v>432</v>
       </c>
+      <c r="F35" s="15">
+        <v>46286</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>468</v>
+      </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36">
+      <c r="A36" s="14">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="15">
         <v>46248</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="14" t="s">
         <v>432</v>
       </c>
+      <c r="F36" s="15">
+        <v>46286</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>469</v>
+      </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37">
+      <c r="A37" s="14">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="15">
         <v>46248</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="14" t="s">
         <v>432</v>
+      </c>
+      <c r="F37" s="15">
+        <v>46286</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -6345,16 +6399,16 @@
       <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="C69" s="12">
+      <c r="C69" s="11">
         <v>46249</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="D69" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E69" s="6" t="s">
+      <c r="E69" s="5" t="s">
         <v>44</v>
       </c>
     </row>
@@ -6362,16 +6416,16 @@
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="C70" s="12">
+      <c r="C70" s="11">
         <v>46249</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="D70" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E70" s="6" t="s">
+      <c r="E70" s="5" t="s">
         <v>44</v>
       </c>
     </row>
@@ -6379,39 +6433,39 @@
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C71" s="12">
+      <c r="C71" s="11">
         <v>46249</v>
       </c>
-      <c r="D71" s="6" t="s">
+      <c r="D71" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E71" s="6" t="s">
+      <c r="E71" s="5" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72">
+      <c r="A72" s="14">
         <v>71</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="14" t="s">
         <v>402</v>
       </c>
-      <c r="C72" s="3">
+      <c r="C72" s="15">
         <v>46249</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E72" s="14" t="s">
         <v>432</v>
       </c>
-      <c r="F72" s="3">
+      <c r="F72" s="15">
         <v>46266</v>
       </c>
-      <c r="G72" t="s">
+      <c r="G72" s="14" t="s">
         <v>452</v>
       </c>
     </row>
@@ -6433,48 +6487,48 @@
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74">
+      <c r="A74" s="14">
         <v>73</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="C74" s="3">
+      <c r="C74" s="15">
         <v>46249</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74" s="14" t="s">
         <v>432</v>
       </c>
-      <c r="F74" s="3">
+      <c r="F74" s="15">
         <v>46266</v>
       </c>
-      <c r="G74" t="s">
+      <c r="G74" s="14" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75">
+      <c r="A75" s="14">
         <v>74</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="C75" s="3">
+      <c r="C75" s="15">
         <v>46249</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E75" s="14" t="s">
         <v>432</v>
       </c>
-      <c r="F75" s="3">
+      <c r="F75" s="15">
         <v>46266</v>
       </c>
-      <c r="G75" t="s">
+      <c r="G75" s="14" t="s">
         <v>452</v>
       </c>
     </row>
@@ -7107,82 +7161,94 @@
         <v>456</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B113" t="s">
+        <v>466</v>
+      </c>
+      <c r="C113" s="3">
+        <v>46286</v>
+      </c>
+      <c r="D113" t="s">
+        <v>50</v>
+      </c>
+      <c r="E113" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -8603,3636 +8669,3636 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="B3" s="8">
+      <c r="B3" s="7">
         <v>1</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <v>46303</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="10">
         <v>40305</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>3</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="10">
         <v>40305</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <v>4</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="10">
         <v>40305</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="8">
+      <c r="B7" s="7">
         <v>5</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="10">
         <v>40305</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="B8" s="8">
+      <c r="B8" s="7">
         <v>6</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="10">
         <v>40305</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="B9" s="8">
+      <c r="B9" s="7">
         <v>7</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="10">
         <v>40305</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="B10" s="8">
+      <c r="B10" s="7">
         <v>8</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="10">
         <v>40305</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <v>9</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="10">
         <v>40305</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="B12" s="8">
+      <c r="B12" s="7">
         <v>10</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="10">
         <v>40305</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="8">
+      <c r="B13" s="7">
         <v>11</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="10">
         <v>40305</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="8">
+      <c r="B14" s="7">
         <v>12</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="10">
         <v>40305</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="8">
+      <c r="B15" s="7">
         <v>13</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="10">
         <v>40305</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="8">
+      <c r="B16" s="7">
         <v>14</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="9">
         <v>46302</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="8">
+      <c r="B17" s="7">
         <v>15</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="9">
         <v>46302</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B18" s="8">
+      <c r="B18" s="7">
         <v>16</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="9">
         <v>46302</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B19" s="8">
+      <c r="B19" s="7">
         <v>17</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="9">
         <v>46302</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B20" s="8">
+      <c r="B20" s="7">
         <v>18</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="9">
         <v>46302</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B21" s="8">
+      <c r="B21" s="7">
         <v>19</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="9">
         <v>46302</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B22" s="8">
+      <c r="B22" s="7">
         <v>20</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="9">
         <v>46302</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B23" s="8">
+      <c r="B23" s="7">
         <v>21</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="9">
         <v>46302</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B24" s="8">
+      <c r="B24" s="7">
         <v>22</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="10">
         <v>40305</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B25" s="8">
+      <c r="B25" s="7">
         <v>23</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="10">
         <v>40305</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B26" s="8">
+      <c r="B26" s="7">
         <v>24</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F26" s="10">
         <v>40304</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B27" s="8">
+      <c r="B27" s="7">
         <v>25</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="F27" s="11">
+      <c r="F27" s="10">
         <v>40304</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B28" s="8">
+      <c r="B28" s="7">
         <v>26</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="9">
         <v>46302</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G28" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B29" s="8">
+      <c r="B29" s="7">
         <v>27</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="9">
         <v>46302</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="G29" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="B30" s="8">
+      <c r="B30" s="7">
         <v>28</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="9">
         <v>46302</v>
       </c>
-      <c r="G30" s="8" t="s">
+      <c r="G30" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B31" s="8">
+      <c r="B31" s="7">
         <v>29</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="9">
         <v>46302</v>
       </c>
-      <c r="G31" s="8" t="s">
+      <c r="G31" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B32" s="8">
+      <c r="B32" s="7">
         <v>30</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E32" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="9">
         <v>46302</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="G32" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="33" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B33" s="8">
+      <c r="B33" s="7">
         <v>31</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="9">
         <v>46302</v>
       </c>
-      <c r="G33" s="8" t="s">
+      <c r="G33" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="34" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B34" s="8">
+      <c r="B34" s="7">
         <v>32</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="9">
         <v>46302</v>
       </c>
-      <c r="G34" s="8" t="s">
+      <c r="G34" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="35" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B35" s="8">
+      <c r="B35" s="7">
         <v>33</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="9">
         <v>46302</v>
       </c>
-      <c r="G35" s="8" t="s">
+      <c r="G35" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="36" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B36" s="8">
+      <c r="B36" s="7">
         <v>34</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="E36" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="F36" s="10">
+      <c r="F36" s="9">
         <v>46302</v>
       </c>
-      <c r="G36" s="8" t="s">
+      <c r="G36" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B37" s="8">
+      <c r="B37" s="7">
         <v>35</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F37" s="9">
         <v>46302</v>
       </c>
-      <c r="G37" s="8" t="s">
+      <c r="G37" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B38" s="8">
+      <c r="B38" s="7">
         <v>36</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="F38" s="10">
+      <c r="F38" s="9">
         <v>46302</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="G38" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="39" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B39" s="8">
+      <c r="B39" s="7">
         <v>37</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="9">
         <v>46302</v>
       </c>
-      <c r="G39" s="8" t="s">
+      <c r="G39" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="40" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B40" s="8">
+      <c r="B40" s="7">
         <v>38</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D40" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="F40" s="10">
+      <c r="F40" s="9">
         <v>46302</v>
       </c>
-      <c r="G40" s="8" t="s">
+      <c r="G40" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="41" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B41" s="8">
+      <c r="B41" s="7">
         <v>39</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D41" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E41" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="F41" s="10">
+      <c r="F41" s="9">
         <v>46302</v>
       </c>
-      <c r="G41" s="8" t="s">
+      <c r="G41" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="42" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B42" s="8">
+      <c r="B42" s="7">
         <v>40</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="F42" s="10">
+      <c r="F42" s="9">
         <v>46302</v>
       </c>
-      <c r="G42" s="8" t="s">
+      <c r="G42" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="43" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B43" s="8">
+      <c r="B43" s="7">
         <v>41</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E43" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F43" s="10">
+      <c r="F43" s="9">
         <v>46302</v>
       </c>
-      <c r="G43" s="8" t="s">
+      <c r="G43" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="44" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B44" s="8">
+      <c r="B44" s="7">
         <v>42</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C44" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D44" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="F44" s="10">
+      <c r="F44" s="9">
         <v>46302</v>
       </c>
-      <c r="G44" s="8" t="s">
+      <c r="G44" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="45" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B45" s="8">
+      <c r="B45" s="7">
         <v>43</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C45" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D45" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E45" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="F45" s="10">
+      <c r="F45" s="9">
         <v>46302</v>
       </c>
-      <c r="G45" s="8" t="s">
+      <c r="G45" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="46" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B46" s="8">
+      <c r="B46" s="7">
         <v>44</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="C46" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D46" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="F46" s="10">
+      <c r="F46" s="9">
         <v>46302</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="G46" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="47" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B47" s="8">
+      <c r="B47" s="7">
         <v>45</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C47" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="D47" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="F47" s="11">
+      <c r="F47" s="10">
         <v>40305</v>
       </c>
-      <c r="G47" s="8" t="s">
+      <c r="G47" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="48" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B48" s="8">
+      <c r="B48" s="7">
         <v>46</v>
       </c>
-      <c r="C48" s="9" t="s">
+      <c r="C48" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D48" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="F48" s="11">
+      <c r="F48" s="10">
         <v>40305</v>
       </c>
-      <c r="G48" s="8" t="s">
+      <c r="G48" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="49" spans="2:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="B49" s="8">
+      <c r="B49" s="7">
         <v>47</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="D49" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E49" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F49" s="11">
+      <c r="F49" s="10">
         <v>40305</v>
       </c>
-      <c r="G49" s="8" t="s">
+      <c r="G49" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="50" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B50" s="8">
+      <c r="B50" s="7">
         <v>48</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="C50" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D50" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="F50" s="11">
+      <c r="F50" s="10">
         <v>40305</v>
       </c>
-      <c r="G50" s="8" t="s">
+      <c r="G50" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="51" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B51" s="8">
+      <c r="B51" s="7">
         <v>49</v>
       </c>
-      <c r="C51" s="9" t="s">
+      <c r="C51" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D51" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="E51" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="F51" s="10">
+      <c r="F51" s="9">
         <v>46302</v>
       </c>
-      <c r="G51" s="8" t="s">
+      <c r="G51" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="52" spans="2:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="B52" s="8">
+      <c r="B52" s="7">
         <v>50</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D52" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="E52" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="F52" s="11">
+      <c r="F52" s="10">
         <v>40305</v>
       </c>
-      <c r="G52" s="8" t="s">
+      <c r="G52" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="53" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B53" s="8">
+      <c r="B53" s="7">
         <v>51</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="C53" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D53" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E53" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="F53" s="11">
+      <c r="F53" s="10">
         <v>40305</v>
       </c>
-      <c r="G53" s="8" t="s">
+      <c r="G53" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="54" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B54" s="8">
+      <c r="B54" s="7">
         <v>52</v>
       </c>
-      <c r="C54" s="9" t="s">
+      <c r="C54" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="D54" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E54" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="F54" s="11">
+      <c r="F54" s="10">
         <v>40305</v>
       </c>
-      <c r="G54" s="8" t="s">
+      <c r="G54" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B55" s="8">
+      <c r="B55" s="7">
         <v>53</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="C55" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="D55" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="E55" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="F55" s="10">
+      <c r="F55" s="9">
         <v>46302</v>
       </c>
-      <c r="G55" s="8" t="s">
+      <c r="G55" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="56" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B56" s="8">
+      <c r="B56" s="7">
         <v>54</v>
       </c>
-      <c r="C56" s="9" t="s">
+      <c r="C56" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="D56" s="8" t="s">
+      <c r="D56" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="E56" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="F56" s="11">
+      <c r="F56" s="10">
         <v>40305</v>
       </c>
-      <c r="G56" s="8" t="s">
+      <c r="G56" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="57" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B57" s="8">
+      <c r="B57" s="7">
         <v>55</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="C57" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="D57" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="E57" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="F57" s="11">
+      <c r="F57" s="10">
         <v>40305</v>
       </c>
-      <c r="G57" s="8" t="s">
+      <c r="G57" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="58" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B58" s="8">
+      <c r="B58" s="7">
         <v>56</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C58" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="D58" s="8" t="s">
+      <c r="D58" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="E58" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="F58" s="10">
+      <c r="F58" s="9">
         <v>46302</v>
       </c>
-      <c r="G58" s="8" t="s">
+      <c r="G58" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="59" spans="2:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="B59" s="8">
+      <c r="B59" s="7">
         <v>57</v>
       </c>
-      <c r="C59" s="9" t="s">
+      <c r="C59" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="D59" s="8" t="s">
+      <c r="D59" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="E59" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="F59" s="10">
+      <c r="F59" s="9">
         <v>46302</v>
       </c>
-      <c r="G59" s="8" t="s">
+      <c r="G59" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="60" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B60" s="8">
+      <c r="B60" s="7">
         <v>58</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C60" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D60" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E60" s="8" t="s">
+      <c r="E60" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="F60" s="11">
+      <c r="F60" s="10">
         <v>40305</v>
       </c>
-      <c r="G60" s="8" t="s">
+      <c r="G60" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="61" spans="2:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="B61" s="8">
+      <c r="B61" s="7">
         <v>59</v>
       </c>
-      <c r="C61" s="9" t="s">
+      <c r="C61" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="D61" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E61" s="8" t="s">
+      <c r="E61" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F61" s="11">
+      <c r="F61" s="10">
         <v>40305</v>
       </c>
-      <c r="G61" s="8" t="s">
+      <c r="G61" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B62" s="8">
+      <c r="B62" s="7">
         <v>60</v>
       </c>
-      <c r="C62" s="9" t="s">
+      <c r="C62" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="D62" s="8" t="s">
+      <c r="D62" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="E62" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="F62" s="11">
+      <c r="F62" s="10">
         <v>40305</v>
       </c>
-      <c r="G62" s="8" t="s">
+      <c r="G62" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B63" s="8">
+      <c r="B63" s="7">
         <v>61</v>
       </c>
-      <c r="C63" s="9" t="s">
+      <c r="C63" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="D63" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E63" s="8" t="s">
+      <c r="E63" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="F63" s="11">
+      <c r="F63" s="10">
         <v>40305</v>
       </c>
-      <c r="G63" s="8" t="s">
+      <c r="G63" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="64" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B64" s="8">
+      <c r="B64" s="7">
         <v>62</v>
       </c>
-      <c r="C64" s="9" t="s">
+      <c r="C64" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="D64" s="8" t="s">
+      <c r="D64" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E64" s="8" t="s">
+      <c r="E64" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="F64" s="10">
+      <c r="F64" s="9">
         <v>46302</v>
       </c>
-      <c r="G64" s="8" t="s">
+      <c r="G64" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B65" s="8">
+      <c r="B65" s="7">
         <v>63</v>
       </c>
-      <c r="C65" s="9" t="s">
+      <c r="C65" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="D65" s="8" t="s">
+      <c r="D65" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="E65" s="8" t="s">
+      <c r="E65" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="F65" s="11">
+      <c r="F65" s="10">
         <v>40305</v>
       </c>
-      <c r="G65" s="8" t="s">
+      <c r="G65" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B66" s="8">
+      <c r="B66" s="7">
         <v>64</v>
       </c>
-      <c r="C66" s="9" t="s">
+      <c r="C66" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="D66" s="8" t="s">
+      <c r="D66" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="E66" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="F66" s="11">
+      <c r="F66" s="10">
         <v>40305</v>
       </c>
-      <c r="G66" s="8" t="s">
+      <c r="G66" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B67" s="8">
+      <c r="B67" s="7">
         <v>65</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C67" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="D67" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E67" s="11">
+      <c r="E67" s="10">
         <v>40305</v>
       </c>
-      <c r="F67" s="8" t="s">
+      <c r="F67" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="68" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B68" s="8">
+      <c r="B68" s="7">
         <v>66</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="D68" s="8" t="s">
+      <c r="D68" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E68" s="10">
+      <c r="E68" s="9">
         <v>46302</v>
       </c>
-      <c r="F68" s="8" t="s">
+      <c r="F68" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="69" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B69" s="8">
+      <c r="B69" s="7">
         <v>67</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C69" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D69" s="8" t="s">
+      <c r="D69" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E69" s="10">
+      <c r="E69" s="9">
         <v>46302</v>
       </c>
-      <c r="F69" s="8" t="s">
+      <c r="F69" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="70" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B70" s="8">
+      <c r="B70" s="7">
         <v>68</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="C70" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="D70" s="8" t="s">
+      <c r="D70" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E70" s="10">
+      <c r="E70" s="9">
         <v>46302</v>
       </c>
-      <c r="F70" s="8" t="s">
+      <c r="F70" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="71" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B71" s="8">
+      <c r="B71" s="7">
         <v>69</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C71" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="D71" s="8" t="s">
+      <c r="D71" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E71" s="10">
+      <c r="E71" s="9">
         <v>46302</v>
       </c>
-      <c r="F71" s="8" t="s">
+      <c r="F71" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="72" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B72" s="8">
+      <c r="B72" s="7">
         <v>70</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C72" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="D72" s="8" t="s">
+      <c r="D72" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E72" s="11">
+      <c r="E72" s="10">
         <v>40304</v>
       </c>
-      <c r="F72" s="8" t="s">
+      <c r="F72" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="73" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B73" s="8">
+      <c r="B73" s="7">
         <v>71</v>
       </c>
-      <c r="C73" s="8" t="s">
+      <c r="C73" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D73" s="8" t="s">
+      <c r="D73" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E73" s="11">
+      <c r="E73" s="10">
         <v>40304</v>
       </c>
-      <c r="F73" s="8" t="s">
+      <c r="F73" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="74" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B74" s="8">
+      <c r="B74" s="7">
         <v>72</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="C74" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D74" s="8" t="s">
+      <c r="D74" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E74" s="11">
+      <c r="E74" s="10">
         <v>40304</v>
       </c>
-      <c r="F74" s="8" t="s">
+      <c r="F74" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="75" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B75" s="8">
+      <c r="B75" s="7">
         <v>73</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C75" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="D75" s="8" t="s">
+      <c r="D75" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E75" s="11">
+      <c r="E75" s="10">
         <v>40304</v>
       </c>
-      <c r="F75" s="8" t="s">
+      <c r="F75" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="76" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B76" s="8">
+      <c r="B76" s="7">
         <v>74</v>
       </c>
-      <c r="C76" s="8" t="s">
+      <c r="C76" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D76" s="8" t="s">
+      <c r="D76" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="E76" s="10">
+      <c r="E76" s="9">
         <v>46302</v>
       </c>
-      <c r="F76" s="8" t="s">
+      <c r="F76" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="77" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B77" s="8">
+      <c r="B77" s="7">
         <v>75</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C77" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="D77" s="8" t="s">
+      <c r="D77" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="E77" s="10">
+      <c r="E77" s="9">
         <v>46302</v>
       </c>
-      <c r="F77" s="8" t="s">
+      <c r="F77" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="78" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B78" s="8">
+      <c r="B78" s="7">
         <v>76</v>
       </c>
-      <c r="C78" s="8" t="s">
+      <c r="C78" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="D78" s="8" t="s">
+      <c r="D78" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="E78" s="11">
+      <c r="E78" s="10">
         <v>40304</v>
       </c>
-      <c r="F78" s="8" t="s">
+      <c r="F78" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="79" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B79" s="8">
+      <c r="B79" s="7">
         <v>77</v>
       </c>
-      <c r="C79" s="8" t="s">
+      <c r="C79" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="D79" s="8" t="s">
+      <c r="D79" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="E79" s="11">
+      <c r="E79" s="10">
         <v>40304</v>
       </c>
-      <c r="F79" s="8" t="s">
+      <c r="F79" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="80" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B80" s="8">
+      <c r="B80" s="7">
         <v>78</v>
       </c>
-      <c r="C80" s="8" t="s">
+      <c r="C80" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="D80" s="8" t="s">
+      <c r="D80" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="E80" s="11">
+      <c r="E80" s="10">
         <v>40304</v>
       </c>
-      <c r="F80" s="8" t="s">
+      <c r="F80" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="81" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B81" s="8">
+      <c r="B81" s="7">
         <v>79</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="C81" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="D81" s="8" t="s">
+      <c r="D81" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E81" s="10">
+      <c r="E81" s="9">
         <v>46302</v>
       </c>
-      <c r="F81" s="8" t="s">
+      <c r="F81" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="82" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B82" s="8">
+      <c r="B82" s="7">
         <v>80</v>
       </c>
-      <c r="C82" s="8" t="s">
+      <c r="C82" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="D82" s="8" t="s">
+      <c r="D82" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E82" s="10">
+      <c r="E82" s="9">
         <v>46302</v>
       </c>
-      <c r="F82" s="8" t="s">
+      <c r="F82" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="83" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B83" s="8">
+      <c r="B83" s="7">
         <v>81</v>
       </c>
-      <c r="C83" s="8" t="s">
+      <c r="C83" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="D83" s="8" t="s">
+      <c r="D83" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E83" s="11">
+      <c r="E83" s="10">
         <v>40304</v>
       </c>
-      <c r="F83" s="8" t="s">
+      <c r="F83" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="84" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B84" s="8">
+      <c r="B84" s="7">
         <v>82</v>
       </c>
-      <c r="C84" s="8" t="s">
+      <c r="C84" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="D84" s="8" t="s">
+      <c r="D84" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E84" s="11">
+      <c r="E84" s="10">
         <v>40304</v>
       </c>
-      <c r="F84" s="8" t="s">
+      <c r="F84" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="85" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B85" s="8">
+      <c r="B85" s="7">
         <v>83</v>
       </c>
-      <c r="C85" s="8" t="s">
+      <c r="C85" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="D85" s="8" t="s">
+      <c r="D85" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E85" s="10">
+      <c r="E85" s="9">
         <v>46302</v>
       </c>
-      <c r="F85" s="8" t="s">
+      <c r="F85" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="86" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B86" s="8">
+      <c r="B86" s="7">
         <v>84</v>
       </c>
-      <c r="C86" s="8" t="s">
+      <c r="C86" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="D86" s="8" t="s">
+      <c r="D86" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E86" s="11">
+      <c r="E86" s="10">
         <v>40304</v>
       </c>
-      <c r="F86" s="8" t="s">
+      <c r="F86" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="87" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B87" s="8">
+      <c r="B87" s="7">
         <v>85</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="C87" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="D87" s="8" t="s">
+      <c r="D87" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E87" s="11">
+      <c r="E87" s="10">
         <v>40304</v>
       </c>
-      <c r="F87" s="8" t="s">
+      <c r="F87" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="88" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B88" s="8">
+      <c r="B88" s="7">
         <v>86</v>
       </c>
-      <c r="C88" s="8" t="s">
+      <c r="C88" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="D88" s="8" t="s">
+      <c r="D88" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E88" s="11">
+      <c r="E88" s="10">
         <v>40304</v>
       </c>
-      <c r="F88" s="8" t="s">
+      <c r="F88" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="89" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B89" s="8">
+      <c r="B89" s="7">
         <v>87</v>
       </c>
-      <c r="C89" s="8" t="s">
+      <c r="C89" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="D89" s="8" t="s">
+      <c r="D89" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E89" s="10">
+      <c r="E89" s="9">
         <v>46301</v>
       </c>
-      <c r="F89" s="8" t="s">
+      <c r="F89" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="90" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B90" s="8">
+      <c r="B90" s="7">
         <v>88</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="C90" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D90" s="8" t="s">
+      <c r="D90" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E90" s="11">
+      <c r="E90" s="10">
         <v>40304</v>
       </c>
-      <c r="F90" s="8" t="s">
+      <c r="F90" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="91" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B91" s="8">
+      <c r="B91" s="7">
         <v>89</v>
       </c>
-      <c r="C91" s="8" t="s">
+      <c r="C91" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="D91" s="8" t="s">
+      <c r="D91" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E91" s="11">
+      <c r="E91" s="10">
         <v>40304</v>
       </c>
-      <c r="F91" s="8" t="s">
+      <c r="F91" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="92" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B92" s="8">
+      <c r="B92" s="7">
         <v>90</v>
       </c>
-      <c r="C92" s="8" t="s">
+      <c r="C92" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="D92" s="8" t="s">
+      <c r="D92" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E92" s="11">
+      <c r="E92" s="10">
         <v>40304</v>
       </c>
-      <c r="F92" s="8" t="s">
+      <c r="F92" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="93" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B93" s="8">
+      <c r="B93" s="7">
         <v>91</v>
       </c>
-      <c r="C93" s="8" t="s">
+      <c r="C93" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D93" s="8" t="s">
+      <c r="D93" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E93" s="11">
+      <c r="E93" s="10">
         <v>40304</v>
       </c>
-      <c r="F93" s="8" t="s">
+      <c r="F93" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="94" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B94" s="8">
+      <c r="B94" s="7">
         <v>92</v>
       </c>
-      <c r="C94" s="8" t="s">
+      <c r="C94" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="D94" s="8" t="s">
+      <c r="D94" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E94" s="11">
+      <c r="E94" s="10">
         <v>40304</v>
       </c>
-      <c r="F94" s="8" t="s">
+      <c r="F94" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="95" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B95" s="8">
+      <c r="B95" s="7">
         <v>93</v>
       </c>
-      <c r="C95" s="8" t="s">
+      <c r="C95" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="D95" s="8" t="s">
+      <c r="D95" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E95" s="11">
+      <c r="E95" s="10">
         <v>40304</v>
       </c>
-      <c r="F95" s="8" t="s">
+      <c r="F95" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="96" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B96" s="8">
+      <c r="B96" s="7">
         <v>94</v>
       </c>
-      <c r="C96" s="8" t="s">
+      <c r="C96" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="D96" s="8" t="s">
+      <c r="D96" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E96" s="11">
+      <c r="E96" s="10">
         <v>40304</v>
       </c>
-      <c r="F96" s="8" t="s">
+      <c r="F96" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="97" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B97" s="8">
+      <c r="B97" s="7">
         <v>95</v>
       </c>
-      <c r="C97" s="8" t="s">
+      <c r="C97" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="D97" s="8" t="s">
+      <c r="D97" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E97" s="11">
+      <c r="E97" s="10">
         <v>40304</v>
       </c>
-      <c r="F97" s="8" t="s">
+      <c r="F97" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="98" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B98" s="8">
+      <c r="B98" s="7">
         <v>96</v>
       </c>
-      <c r="C98" s="8" t="s">
+      <c r="C98" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="D98" s="8" t="s">
+      <c r="D98" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E98" s="11">
+      <c r="E98" s="10">
         <v>40304</v>
       </c>
-      <c r="F98" s="8" t="s">
+      <c r="F98" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="99" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B99" s="8">
+      <c r="B99" s="7">
         <v>97</v>
       </c>
-      <c r="C99" s="8" t="s">
+      <c r="C99" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="D99" s="8" t="s">
+      <c r="D99" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E99" s="11">
+      <c r="E99" s="10">
         <v>40304</v>
       </c>
-      <c r="F99" s="8" t="s">
+      <c r="F99" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="100" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B100" s="8">
+      <c r="B100" s="7">
         <v>98</v>
       </c>
-      <c r="C100" s="8" t="s">
+      <c r="C100" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="D100" s="8" t="s">
+      <c r="D100" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E100" s="11">
+      <c r="E100" s="10">
         <v>40304</v>
       </c>
-      <c r="F100" s="8" t="s">
+      <c r="F100" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="101" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B101" s="8">
+      <c r="B101" s="7">
         <v>99</v>
       </c>
-      <c r="C101" s="8" t="s">
+      <c r="C101" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="D101" s="8" t="s">
+      <c r="D101" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E101" s="11">
+      <c r="E101" s="10">
         <v>40304</v>
       </c>
-      <c r="F101" s="8" t="s">
+      <c r="F101" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="102" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B102" s="8">
+      <c r="B102" s="7">
         <v>100</v>
       </c>
-      <c r="C102" s="8" t="s">
+      <c r="C102" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="D102" s="8" t="s">
+      <c r="D102" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E102" s="11">
+      <c r="E102" s="10">
         <v>40304</v>
       </c>
-      <c r="F102" s="8" t="s">
+      <c r="F102" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="103" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B103" s="8">
+      <c r="B103" s="7">
         <v>101</v>
       </c>
-      <c r="C103" s="8" t="s">
+      <c r="C103" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="D103" s="8" t="s">
+      <c r="D103" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E103" s="10">
+      <c r="E103" s="9">
         <v>46302</v>
       </c>
-      <c r="F103" s="8" t="s">
+      <c r="F103" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="104" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B104" s="8">
+      <c r="B104" s="7">
         <v>102</v>
       </c>
-      <c r="C104" s="8" t="s">
+      <c r="C104" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="D104" s="8" t="s">
+      <c r="D104" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E104" s="11">
+      <c r="E104" s="10">
         <v>40304</v>
       </c>
-      <c r="F104" s="8" t="s">
+      <c r="F104" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="105" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B105" s="8">
+      <c r="B105" s="7">
         <v>103</v>
       </c>
-      <c r="C105" s="8" t="s">
+      <c r="C105" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="D105" s="8" t="s">
+      <c r="D105" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E105" s="10">
+      <c r="E105" s="9">
         <v>46302</v>
       </c>
-      <c r="F105" s="8" t="s">
+      <c r="F105" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="106" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B106" s="8">
+      <c r="B106" s="7">
         <v>104</v>
       </c>
-      <c r="C106" s="8" t="s">
+      <c r="C106" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="D106" s="8" t="s">
+      <c r="D106" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E106" s="10">
+      <c r="E106" s="9">
         <v>46302</v>
       </c>
-      <c r="F106" s="8" t="s">
+      <c r="F106" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="107" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B107" s="8">
+      <c r="B107" s="7">
         <v>105</v>
       </c>
-      <c r="C107" s="8" t="s">
+      <c r="C107" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="D107" s="8" t="s">
+      <c r="D107" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E107" s="10">
+      <c r="E107" s="9">
         <v>46302</v>
       </c>
-      <c r="F107" s="8" t="s">
+      <c r="F107" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="108" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B108" s="8">
+      <c r="B108" s="7">
         <v>106</v>
       </c>
-      <c r="C108" s="8" t="s">
+      <c r="C108" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="D108" s="8" t="s">
+      <c r="D108" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E108" s="10">
+      <c r="E108" s="9">
         <v>46302</v>
       </c>
-      <c r="F108" s="8" t="s">
+      <c r="F108" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="109" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B109" s="8">
+      <c r="B109" s="7">
         <v>107</v>
       </c>
-      <c r="C109" s="8" t="s">
+      <c r="C109" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="D109" s="8" t="s">
+      <c r="D109" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E109" s="10">
+      <c r="E109" s="9">
         <v>46302</v>
       </c>
-      <c r="F109" s="8" t="s">
+      <c r="F109" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="110" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B110" s="8">
+      <c r="B110" s="7">
         <v>108</v>
       </c>
-      <c r="C110" s="8" t="s">
+      <c r="C110" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="D110" s="8" t="s">
+      <c r="D110" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E110" s="10">
+      <c r="E110" s="9">
         <v>46302</v>
       </c>
-      <c r="F110" s="8" t="s">
+      <c r="F110" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="111" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B111" s="8">
+      <c r="B111" s="7">
         <v>109</v>
       </c>
-      <c r="C111" s="8" t="s">
+      <c r="C111" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="D111" s="8" t="s">
+      <c r="D111" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E111" s="11">
+      <c r="E111" s="10">
         <v>40303</v>
       </c>
-      <c r="F111" s="8" t="s">
+      <c r="F111" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="112" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B112" s="8">
+      <c r="B112" s="7">
         <v>110</v>
       </c>
-      <c r="C112" s="8" t="s">
+      <c r="C112" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="D112" s="8" t="s">
+      <c r="D112" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E112" s="11">
+      <c r="E112" s="10">
         <v>40304</v>
       </c>
-      <c r="F112" s="8" t="s">
+      <c r="F112" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="113" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B113" s="8">
+      <c r="B113" s="7">
         <v>111</v>
       </c>
-      <c r="C113" s="8" t="s">
+      <c r="C113" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="D113" s="8" t="s">
+      <c r="D113" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E113" s="11">
+      <c r="E113" s="10">
         <v>40303</v>
       </c>
-      <c r="F113" s="8" t="s">
+      <c r="F113" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="114" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B114" s="8">
+      <c r="B114" s="7">
         <v>112</v>
       </c>
-      <c r="C114" s="8" t="s">
+      <c r="C114" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="D114" s="8" t="s">
+      <c r="D114" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E114" s="10">
+      <c r="E114" s="9">
         <v>46301</v>
       </c>
-      <c r="F114" s="8" t="s">
+      <c r="F114" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="115" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B115" s="8">
+      <c r="B115" s="7">
         <v>113</v>
       </c>
-      <c r="C115" s="8" t="s">
+      <c r="C115" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="D115" s="8" t="s">
+      <c r="D115" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E115" s="10">
+      <c r="E115" s="9">
         <v>46301</v>
       </c>
-      <c r="F115" s="8" t="s">
+      <c r="F115" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="116" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B116" s="8">
+      <c r="B116" s="7">
         <v>114</v>
       </c>
-      <c r="C116" s="8" t="s">
+      <c r="C116" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="D116" s="8" t="s">
+      <c r="D116" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="E116" s="11">
+      <c r="E116" s="10">
         <v>40303</v>
       </c>
-      <c r="F116" s="8" t="s">
+      <c r="F116" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B117" s="8">
+      <c r="B117" s="7">
         <v>115</v>
       </c>
-      <c r="C117" s="8" t="s">
+      <c r="C117" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="D117" s="8" t="s">
+      <c r="D117" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="E117" s="10">
+      <c r="E117" s="9">
         <v>46300</v>
       </c>
-      <c r="F117" s="8" t="s">
+      <c r="F117" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="118" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B118" s="8">
+      <c r="B118" s="7">
         <v>116</v>
       </c>
-      <c r="C118" s="8" t="s">
+      <c r="C118" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="D118" s="8" t="s">
+      <c r="D118" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="E118" s="10">
+      <c r="E118" s="9">
         <v>46301</v>
       </c>
-      <c r="F118" s="8" t="s">
+      <c r="F118" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="119" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B119" s="8">
+      <c r="B119" s="7">
         <v>117</v>
       </c>
-      <c r="C119" s="8" t="s">
+      <c r="C119" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="D119" s="8" t="s">
+      <c r="D119" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="E119" s="10">
+      <c r="E119" s="9">
         <v>46300</v>
       </c>
-      <c r="F119" s="8" t="s">
+      <c r="F119" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="120" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B120" s="8">
+      <c r="B120" s="7">
         <v>118</v>
       </c>
-      <c r="C120" s="8" t="s">
+      <c r="C120" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="D120" s="8" t="s">
+      <c r="D120" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="E120" s="10">
+      <c r="E120" s="9">
         <v>46300</v>
       </c>
-      <c r="F120" s="8" t="s">
+      <c r="F120" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="121" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B121" s="8">
+      <c r="B121" s="7">
         <v>119</v>
       </c>
-      <c r="C121" s="8" t="s">
+      <c r="C121" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="D121" s="8" t="s">
+      <c r="D121" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="E121" s="10">
+      <c r="E121" s="9">
         <v>46300</v>
       </c>
-      <c r="F121" s="8" t="s">
+      <c r="F121" s="7" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="122" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B122" s="8">
+      <c r="B122" s="7">
         <v>120</v>
       </c>
-      <c r="C122" s="8" t="s">
+      <c r="C122" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="D122" s="8" t="s">
+      <c r="D122" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E122" s="11">
+      <c r="E122" s="10">
         <v>40304</v>
       </c>
-      <c r="F122" s="8" t="s">
+      <c r="F122" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="123" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B123" s="8">
+      <c r="B123" s="7">
         <v>121</v>
       </c>
-      <c r="C123" s="8" t="s">
+      <c r="C123" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="D123" s="8" t="s">
+      <c r="D123" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E123" s="10">
+      <c r="E123" s="9">
         <v>46301</v>
       </c>
-      <c r="F123" s="8" t="s">
+      <c r="F123" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="124" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B124" s="8">
+      <c r="B124" s="7">
         <v>122</v>
       </c>
-      <c r="C124" s="8" t="s">
+      <c r="C124" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="D124" s="8" t="s">
+      <c r="D124" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E124" s="10">
+      <c r="E124" s="9">
         <v>46301</v>
       </c>
-      <c r="F124" s="8" t="s">
+      <c r="F124" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="125" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B125" s="8">
+      <c r="B125" s="7">
         <v>123</v>
       </c>
-      <c r="C125" s="8" t="s">
+      <c r="C125" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="D125" s="8" t="s">
+      <c r="D125" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E125" s="11">
+      <c r="E125" s="10">
         <v>40303</v>
       </c>
-      <c r="F125" s="8" t="s">
+      <c r="F125" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="126" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B126" s="8">
+      <c r="B126" s="7">
         <v>124</v>
       </c>
-      <c r="C126" s="8" t="s">
+      <c r="C126" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D126" s="8" t="s">
+      <c r="D126" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E126" s="10">
+      <c r="E126" s="9">
         <v>46300</v>
       </c>
-      <c r="F126" s="8" t="s">
+      <c r="F126" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="127" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B127" s="8">
+      <c r="B127" s="7">
         <v>125</v>
       </c>
-      <c r="C127" s="8" t="s">
+      <c r="C127" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="D127" s="8" t="s">
+      <c r="D127" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E127" s="11">
+      <c r="E127" s="10">
         <v>40303</v>
       </c>
-      <c r="F127" s="8" t="s">
+      <c r="F127" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="128" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B128" s="8">
+      <c r="B128" s="7">
         <v>126</v>
       </c>
-      <c r="C128" s="8" t="s">
+      <c r="C128" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="D128" s="8" t="s">
+      <c r="D128" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E128" s="10">
+      <c r="E128" s="9">
         <v>46301</v>
       </c>
-      <c r="F128" s="8" t="s">
+      <c r="F128" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="129" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B129" s="8">
+      <c r="B129" s="7">
         <v>127</v>
       </c>
-      <c r="C129" s="8" t="s">
+      <c r="C129" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="D129" s="8" t="s">
+      <c r="D129" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E129" s="10">
+      <c r="E129" s="9">
         <v>46301</v>
       </c>
-      <c r="F129" s="8" t="s">
+      <c r="F129" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="130" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B130" s="8">
+      <c r="B130" s="7">
         <v>128</v>
       </c>
-      <c r="C130" s="8" t="s">
+      <c r="C130" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="D130" s="8" t="s">
+      <c r="D130" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E130" s="10">
+      <c r="E130" s="9">
         <v>46300</v>
       </c>
-      <c r="F130" s="8" t="s">
+      <c r="F130" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="131" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B131" s="8">
+      <c r="B131" s="7">
         <v>129</v>
       </c>
-      <c r="C131" s="8" t="s">
+      <c r="C131" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="D131" s="8" t="s">
+      <c r="D131" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E131" s="11">
+      <c r="E131" s="10">
         <v>40303</v>
       </c>
-      <c r="F131" s="8" t="s">
+      <c r="F131" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="132" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B132" s="8">
+      <c r="B132" s="7">
         <v>130</v>
       </c>
-      <c r="C132" s="8" t="s">
+      <c r="C132" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="D132" s="8" t="s">
+      <c r="D132" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E132" s="11">
+      <c r="E132" s="10">
         <v>40303</v>
       </c>
-      <c r="F132" s="8" t="s">
+      <c r="F132" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="133" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B133" s="8">
+      <c r="B133" s="7">
         <v>131</v>
       </c>
-      <c r="C133" s="8" t="s">
+      <c r="C133" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="D133" s="8" t="s">
+      <c r="D133" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E133" s="11">
+      <c r="E133" s="10">
         <v>40303</v>
       </c>
-      <c r="F133" s="8" t="s">
+      <c r="F133" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="134" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B134" s="8">
+      <c r="B134" s="7">
         <v>132</v>
       </c>
-      <c r="C134" s="8" t="s">
+      <c r="C134" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="D134" s="8" t="s">
+      <c r="D134" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E134" s="10">
+      <c r="E134" s="9">
         <v>46301</v>
       </c>
-      <c r="F134" s="8" t="s">
+      <c r="F134" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="135" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B135" s="8">
+      <c r="B135" s="7">
         <v>133</v>
       </c>
-      <c r="C135" s="8" t="s">
+      <c r="C135" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="D135" s="8" t="s">
+      <c r="D135" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E135" s="10">
+      <c r="E135" s="9">
         <v>46301</v>
       </c>
-      <c r="F135" s="8" t="s">
+      <c r="F135" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="136" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B136" s="8">
+      <c r="B136" s="7">
         <v>134</v>
       </c>
-      <c r="C136" s="8" t="s">
+      <c r="C136" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="D136" s="8" t="s">
+      <c r="D136" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E136" s="10">
+      <c r="E136" s="9">
         <v>46301</v>
       </c>
-      <c r="F136" s="8" t="s">
+      <c r="F136" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="137" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B137" s="8">
+      <c r="B137" s="7">
         <v>135</v>
       </c>
-      <c r="C137" s="8" t="s">
+      <c r="C137" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="D137" s="8" t="s">
+      <c r="D137" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E137" s="11">
+      <c r="E137" s="10">
         <v>40303</v>
       </c>
-      <c r="F137" s="8" t="s">
+      <c r="F137" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="138" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B138" s="8">
+      <c r="B138" s="7">
         <v>136</v>
       </c>
-      <c r="C138" s="8" t="s">
+      <c r="C138" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="D138" s="8" t="s">
+      <c r="D138" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E138" s="11">
+      <c r="E138" s="10">
         <v>40303</v>
       </c>
-      <c r="F138" s="8" t="s">
+      <c r="F138" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="139" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B139" s="8">
+      <c r="B139" s="7">
         <v>137</v>
       </c>
-      <c r="C139" s="8" t="s">
+      <c r="C139" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="D139" s="8" t="s">
+      <c r="D139" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E139" s="11">
+      <c r="E139" s="10">
         <v>40303</v>
       </c>
-      <c r="F139" s="8" t="s">
+      <c r="F139" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="140" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B140" s="8">
+      <c r="B140" s="7">
         <v>138</v>
       </c>
-      <c r="C140" s="8" t="s">
+      <c r="C140" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="D140" s="8" t="s">
+      <c r="D140" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E140" s="10">
+      <c r="E140" s="9">
         <v>46301</v>
       </c>
-      <c r="F140" s="8" t="s">
+      <c r="F140" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="141" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B141" s="8">
+      <c r="B141" s="7">
         <v>139</v>
       </c>
-      <c r="C141" s="8" t="s">
+      <c r="C141" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="D141" s="8" t="s">
+      <c r="D141" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E141" s="10">
+      <c r="E141" s="9">
         <v>46301</v>
       </c>
-      <c r="F141" s="8" t="s">
+      <c r="F141" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="142" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B142" s="8">
+      <c r="B142" s="7">
         <v>140</v>
       </c>
-      <c r="C142" s="8" t="s">
+      <c r="C142" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="D142" s="8" t="s">
+      <c r="D142" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E142" s="10">
+      <c r="E142" s="9">
         <v>46301</v>
       </c>
-      <c r="F142" s="8" t="s">
+      <c r="F142" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="143" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B143" s="8">
+      <c r="B143" s="7">
         <v>141</v>
       </c>
-      <c r="C143" s="8" t="s">
+      <c r="C143" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="D143" s="8" t="s">
+      <c r="D143" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E143" s="10">
+      <c r="E143" s="9">
         <v>46300</v>
       </c>
-      <c r="F143" s="8" t="s">
+      <c r="F143" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="144" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B144" s="8">
+      <c r="B144" s="7">
         <v>142</v>
       </c>
-      <c r="C144" s="8" t="s">
+      <c r="C144" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="D144" s="8" t="s">
+      <c r="D144" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E144" s="10">
+      <c r="E144" s="9">
         <v>46301</v>
       </c>
-      <c r="F144" s="8" t="s">
+      <c r="F144" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="145" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B145" s="8">
+      <c r="B145" s="7">
         <v>143</v>
       </c>
-      <c r="C145" s="8" t="s">
+      <c r="C145" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="D145" s="8" t="s">
+      <c r="D145" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E145" s="10">
+      <c r="E145" s="9">
         <v>46301</v>
       </c>
-      <c r="F145" s="8" t="s">
+      <c r="F145" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="146" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B146" s="8">
+      <c r="B146" s="7">
         <v>144</v>
       </c>
-      <c r="C146" s="8" t="s">
+      <c r="C146" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="D146" s="8" t="s">
+      <c r="D146" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E146" s="11">
+      <c r="E146" s="10">
         <v>40304</v>
       </c>
-      <c r="F146" s="8" t="s">
+      <c r="F146" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="147" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B147" s="8">
+      <c r="B147" s="7">
         <v>145</v>
       </c>
-      <c r="C147" s="8" t="s">
+      <c r="C147" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="D147" s="8" t="s">
+      <c r="D147" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E147" s="11">
+      <c r="E147" s="10">
         <v>40304</v>
       </c>
-      <c r="F147" s="8" t="s">
+      <c r="F147" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="148" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B148" s="8">
+      <c r="B148" s="7">
         <v>146</v>
       </c>
-      <c r="C148" s="8" t="s">
+      <c r="C148" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="D148" s="8" t="s">
+      <c r="D148" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E148" s="11">
+      <c r="E148" s="10">
         <v>40304</v>
       </c>
-      <c r="F148" s="8" t="s">
+      <c r="F148" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="149" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B149" s="8">
+      <c r="B149" s="7">
         <v>147</v>
       </c>
-      <c r="C149" s="8" t="s">
+      <c r="C149" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="D149" s="8" t="s">
+      <c r="D149" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E149" s="11">
+      <c r="E149" s="10">
         <v>40304</v>
       </c>
-      <c r="F149" s="8" t="s">
+      <c r="F149" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="150" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B150" s="8">
+      <c r="B150" s="7">
         <v>148</v>
       </c>
-      <c r="C150" s="8" t="s">
+      <c r="C150" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="D150" s="8" t="s">
+      <c r="D150" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E150" s="10">
+      <c r="E150" s="9">
         <v>46301</v>
       </c>
-      <c r="F150" s="8" t="s">
+      <c r="F150" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="151" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B151" s="8">
+      <c r="B151" s="7">
         <v>149</v>
       </c>
-      <c r="C151" s="8" t="s">
+      <c r="C151" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="D151" s="8" t="s">
+      <c r="D151" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E151" s="10">
+      <c r="E151" s="9">
         <v>46302</v>
       </c>
-      <c r="F151" s="8" t="s">
+      <c r="F151" s="7" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="152" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B152" s="8">
+      <c r="B152" s="7">
         <v>150</v>
       </c>
-      <c r="C152" s="8" t="s">
+      <c r="C152" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="D152" s="8" t="s">
+      <c r="D152" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E152" s="11">
+      <c r="E152" s="10">
         <v>40304</v>
       </c>
-      <c r="F152" s="8" t="s">
+      <c r="F152" s="7" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="153" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B153" s="8">
+      <c r="B153" s="7">
         <v>151</v>
       </c>
-      <c r="C153" s="8" t="s">
+      <c r="C153" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="D153" s="8" t="s">
+      <c r="D153" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E153" s="11">
+      <c r="E153" s="10">
         <v>40304</v>
       </c>
-      <c r="F153" s="8" t="s">
+      <c r="F153" s="7" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="154" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B154" s="8">
+      <c r="B154" s="7">
         <v>152</v>
       </c>
-      <c r="C154" s="8" t="s">
+      <c r="C154" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="D154" s="8" t="s">
+      <c r="D154" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E154" s="11">
+      <c r="E154" s="10">
         <v>40304</v>
       </c>
-      <c r="F154" s="8" t="s">
+      <c r="F154" s="7" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="155" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B155" s="8">
+      <c r="B155" s="7">
         <v>153</v>
       </c>
-      <c r="C155" s="8" t="s">
+      <c r="C155" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="D155" s="8" t="s">
+      <c r="D155" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E155" s="10">
+      <c r="E155" s="9">
         <v>46299</v>
       </c>
-      <c r="F155" s="8" t="s">
+      <c r="F155" s="7" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="156" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B156" s="8">
+      <c r="B156" s="7">
         <v>154</v>
       </c>
-      <c r="C156" s="8" t="s">
+      <c r="C156" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="D156" s="8" t="s">
+      <c r="D156" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E156" s="11">
+      <c r="E156" s="10">
         <v>40301</v>
       </c>
-      <c r="F156" s="8" t="s">
+      <c r="F156" s="7" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="157" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B157" s="8">
+      <c r="B157" s="7">
         <v>155</v>
       </c>
-      <c r="C157" s="8" t="s">
+      <c r="C157" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="D157" s="8" t="s">
+      <c r="D157" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E157" s="11">
+      <c r="E157" s="10">
         <v>40302</v>
       </c>
-      <c r="F157" s="8" t="s">
+      <c r="F157" s="7" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="158" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B158" s="8">
+      <c r="B158" s="7">
         <v>156</v>
       </c>
-      <c r="C158" s="8" t="s">
+      <c r="C158" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="D158" s="8" t="s">
+      <c r="D158" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E158" s="10">
+      <c r="E158" s="9">
         <v>46299</v>
       </c>
-      <c r="F158" s="8" t="s">
+      <c r="F158" s="7" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="159" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B159" s="8">
+      <c r="B159" s="7">
         <v>157</v>
       </c>
-      <c r="C159" s="8" t="s">
+      <c r="C159" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="D159" s="8" t="s">
+      <c r="D159" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="E159" s="10">
+      <c r="E159" s="9">
         <v>46299</v>
       </c>
-      <c r="F159" s="8" t="s">
+      <c r="F159" s="7" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="160" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B160" s="8">
+      <c r="B160" s="7">
         <v>158</v>
       </c>
-      <c r="C160" s="8" t="s">
+      <c r="C160" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="D160" s="8" t="s">
+      <c r="D160" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E160" s="10">
+      <c r="E160" s="9">
         <v>46297</v>
       </c>
-      <c r="F160" s="8" t="s">
+      <c r="F160" s="7" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="161" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B161" s="8">
+      <c r="B161" s="7">
         <v>159</v>
       </c>
-      <c r="C161" s="8" t="s">
+      <c r="C161" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="D161" s="8" t="s">
+      <c r="D161" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E161" s="10">
+      <c r="E161" s="9">
         <v>46299</v>
       </c>
-      <c r="F161" s="8" t="s">
+      <c r="F161" s="7" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="162" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B162" s="8">
+      <c r="B162" s="7">
         <v>160</v>
       </c>
-      <c r="C162" s="8" t="s">
+      <c r="C162" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="D162" s="8" t="s">
+      <c r="D162" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E162" s="10">
+      <c r="E162" s="9">
         <v>46300</v>
       </c>
-      <c r="F162" s="8" t="s">
+      <c r="F162" s="7" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="163" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B163" s="8">
+      <c r="B163" s="7">
         <v>161</v>
       </c>
-      <c r="C163" s="8" t="s">
+      <c r="C163" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="D163" s="8" t="s">
+      <c r="D163" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E163" s="10">
+      <c r="E163" s="9">
         <v>46299</v>
       </c>
-      <c r="F163" s="8" t="s">
+      <c r="F163" s="7" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="164" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B164" s="8">
+      <c r="B164" s="7">
         <v>162</v>
       </c>
-      <c r="C164" s="8" t="s">
+      <c r="C164" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="D164" s="8" t="s">
+      <c r="D164" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E164" s="10">
+      <c r="E164" s="9">
         <v>46299</v>
       </c>
-      <c r="F164" s="8" t="s">
+      <c r="F164" s="7" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="165" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B165" s="8">
+      <c r="B165" s="7">
         <v>163</v>
       </c>
-      <c r="C165" s="8" t="s">
+      <c r="C165" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="D165" s="8" t="s">
+      <c r="D165" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E165" s="11">
+      <c r="E165" s="10">
         <v>40304</v>
       </c>
-      <c r="F165" s="8" t="s">
+      <c r="F165" s="7" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="179" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B179" s="7" t="s">
+      <c r="B179" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C179" s="7" t="s">
+      <c r="C179" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="D179" s="7" t="s">
+      <c r="D179" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="E179" s="7" t="s">
+      <c r="E179" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="F179" s="7" t="s">
+      <c r="F179" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="G179" s="7" t="s">
+      <c r="G179" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="H179" s="7" t="s">
+      <c r="H179" s="6" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="180" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B180" s="9" t="s">
+      <c r="B180" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="C180" s="8">
+      <c r="C180" s="7">
         <v>9</v>
       </c>
-      <c r="D180" s="8">
+      <c r="D180" s="7">
         <v>10</v>
       </c>
-      <c r="E180" s="8">
+      <c r="E180" s="7">
         <v>9</v>
       </c>
-      <c r="F180" s="8">
+      <c r="F180" s="7">
         <v>10</v>
       </c>
-      <c r="G180" s="8">
+      <c r="G180" s="7">
         <v>8</v>
       </c>
-      <c r="H180" s="9">
+      <c r="H180" s="8">
         <v>9.5</v>
       </c>
     </row>
     <row r="181" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B181" s="9" t="s">
+      <c r="B181" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="C181" s="8">
+      <c r="C181" s="7">
         <v>9</v>
       </c>
-      <c r="D181" s="8">
+      <c r="D181" s="7">
         <v>9</v>
       </c>
-      <c r="E181" s="8">
+      <c r="E181" s="7">
         <v>9</v>
       </c>
-      <c r="F181" s="8">
+      <c r="F181" s="7">
         <v>10</v>
       </c>
-      <c r="G181" s="8">
+      <c r="G181" s="7">
         <v>7</v>
       </c>
-      <c r="H181" s="9">
+      <c r="H181" s="8">
         <v>9.1999999999999993</v>
       </c>
     </row>
     <row r="182" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B182" s="9" t="s">
+      <c r="B182" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="C182" s="8">
+      <c r="C182" s="7">
         <v>9</v>
       </c>
-      <c r="D182" s="8">
+      <c r="D182" s="7">
         <v>9</v>
       </c>
-      <c r="E182" s="8">
+      <c r="E182" s="7">
         <v>10</v>
       </c>
-      <c r="F182" s="8">
+      <c r="F182" s="7">
         <v>8</v>
       </c>
-      <c r="G182" s="8">
+      <c r="G182" s="7">
         <v>7</v>
       </c>
-      <c r="H182" s="9">
+      <c r="H182" s="8">
         <v>9</v>
       </c>
     </row>
     <row r="183" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B183" s="9" t="s">
+      <c r="B183" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="C183" s="8">
+      <c r="C183" s="7">
         <v>8</v>
       </c>
-      <c r="D183" s="8">
+      <c r="D183" s="7">
         <v>8</v>
       </c>
-      <c r="E183" s="8">
+      <c r="E183" s="7">
         <v>9</v>
       </c>
-      <c r="F183" s="8">
+      <c r="F183" s="7">
         <v>10</v>
       </c>
-      <c r="G183" s="8">
+      <c r="G183" s="7">
         <v>8</v>
       </c>
-      <c r="H183" s="9">
+      <c r="H183" s="8">
         <v>8.8000000000000007</v>
       </c>
     </row>
     <row r="184" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B184" s="9" t="s">
+      <c r="B184" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="C184" s="8">
+      <c r="C184" s="7">
         <v>8</v>
       </c>
-      <c r="D184" s="8">
+      <c r="D184" s="7">
         <v>9</v>
       </c>
-      <c r="E184" s="8">
+      <c r="E184" s="7">
         <v>8</v>
       </c>
-      <c r="F184" s="8">
+      <c r="F184" s="7">
         <v>9</v>
       </c>
-      <c r="G184" s="8">
+      <c r="G184" s="7">
         <v>7</v>
       </c>
-      <c r="H184" s="9">
+      <c r="H184" s="8">
         <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="185" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B185" s="9" t="s">
+      <c r="B185" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="C185" s="8">
+      <c r="C185" s="7">
         <v>7</v>
       </c>
-      <c r="D185" s="8">
+      <c r="D185" s="7">
         <v>9</v>
       </c>
-      <c r="E185" s="8">
+      <c r="E185" s="7">
         <v>8</v>
       </c>
-      <c r="F185" s="8">
+      <c r="F185" s="7">
         <v>8</v>
       </c>
-      <c r="G185" s="8">
+      <c r="G185" s="7">
         <v>9</v>
       </c>
-      <c r="H185" s="9">
+      <c r="H185" s="8">
         <v>8.5</v>
       </c>
     </row>
     <row r="186" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B186" s="9" t="s">
+      <c r="B186" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="C186" s="8">
+      <c r="C186" s="7">
         <v>7</v>
       </c>
-      <c r="D186" s="8">
+      <c r="D186" s="7">
         <v>9</v>
       </c>
-      <c r="E186" s="8">
+      <c r="E186" s="7">
         <v>6</v>
       </c>
-      <c r="F186" s="8">
+      <c r="F186" s="7">
         <v>7</v>
       </c>
-      <c r="G186" s="8">
+      <c r="G186" s="7">
         <v>9</v>
       </c>
-      <c r="H186" s="9">
+      <c r="H186" s="8">
         <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="187" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B187" s="9" t="s">
+      <c r="B187" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="C187" s="8">
+      <c r="C187" s="7">
         <v>8</v>
       </c>
-      <c r="D187" s="8">
+      <c r="D187" s="7">
         <v>8</v>
       </c>
-      <c r="E187" s="8">
+      <c r="E187" s="7">
         <v>8</v>
       </c>
-      <c r="F187" s="8">
+      <c r="F187" s="7">
         <v>7</v>
       </c>
-      <c r="G187" s="8">
+      <c r="G187" s="7">
         <v>7</v>
       </c>
-      <c r="H187" s="9">
+      <c r="H187" s="8">
         <v>8.1999999999999993</v>
       </c>
     </row>
     <row r="188" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B188" s="9" t="s">
+      <c r="B188" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="C188" s="8">
+      <c r="C188" s="7">
         <v>8</v>
       </c>
-      <c r="D188" s="8">
+      <c r="D188" s="7">
         <v>7</v>
       </c>
-      <c r="E188" s="8">
+      <c r="E188" s="7">
         <v>8</v>
       </c>
-      <c r="F188" s="8">
+      <c r="F188" s="7">
         <v>7</v>
       </c>
-      <c r="G188" s="8">
+      <c r="G188" s="7">
         <v>7</v>
       </c>
-      <c r="H188" s="9">
+      <c r="H188" s="8">
         <v>8</v>
       </c>
     </row>
     <row r="189" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B189" s="9" t="s">
+      <c r="B189" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="C189" s="8">
+      <c r="C189" s="7">
         <v>7</v>
       </c>
-      <c r="D189" s="8">
+      <c r="D189" s="7">
         <v>8</v>
       </c>
-      <c r="E189" s="8">
+      <c r="E189" s="7">
         <v>7</v>
       </c>
-      <c r="F189" s="8">
+      <c r="F189" s="7">
         <v>7</v>
       </c>
-      <c r="G189" s="8">
+      <c r="G189" s="7">
         <v>7</v>
       </c>
-      <c r="H189" s="9">
+      <c r="H189" s="8">
         <v>7.8</v>
       </c>
     </row>
     <row r="190" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B190" s="9" t="s">
+      <c r="B190" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="C190" s="8">
+      <c r="C190" s="7">
         <v>6</v>
       </c>
-      <c r="D190" s="8">
+      <c r="D190" s="7">
         <v>8</v>
       </c>
-      <c r="E190" s="8">
+      <c r="E190" s="7">
         <v>5</v>
       </c>
-      <c r="F190" s="8">
+      <c r="F190" s="7">
         <v>6</v>
       </c>
-      <c r="G190" s="8">
+      <c r="G190" s="7">
         <v>10</v>
       </c>
-      <c r="H190" s="9">
+      <c r="H190" s="8">
         <v>7.6</v>
       </c>
     </row>
     <row r="191" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B191" s="9" t="s">
+      <c r="B191" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="C191" s="8">
+      <c r="C191" s="7">
         <v>6</v>
       </c>
-      <c r="D191" s="8">
+      <c r="D191" s="7">
         <v>8</v>
       </c>
-      <c r="E191" s="8">
+      <c r="E191" s="7">
         <v>6</v>
       </c>
-      <c r="F191" s="8">
+      <c r="F191" s="7">
         <v>7</v>
       </c>
-      <c r="G191" s="8">
+      <c r="G191" s="7">
         <v>9</v>
       </c>
-      <c r="H191" s="9">
+      <c r="H191" s="8">
         <v>7.5</v>
       </c>
     </row>
     <row r="192" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B192" s="9" t="s">
+      <c r="B192" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="C192" s="8">
+      <c r="C192" s="7">
         <v>7</v>
       </c>
-      <c r="D192" s="8">
+      <c r="D192" s="7">
         <v>7</v>
       </c>
-      <c r="E192" s="8">
+      <c r="E192" s="7">
         <v>7</v>
       </c>
-      <c r="F192" s="8">
+      <c r="F192" s="7">
         <v>6</v>
       </c>
-      <c r="G192" s="8">
+      <c r="G192" s="7">
         <v>7</v>
       </c>
-      <c r="H192" s="9">
+      <c r="H192" s="8">
         <v>7.3</v>
       </c>
     </row>
     <row r="193" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B193" s="9" t="s">
+      <c r="B193" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="C193" s="8">
+      <c r="C193" s="7">
         <v>6</v>
       </c>
-      <c r="D193" s="8">
+      <c r="D193" s="7">
         <v>7</v>
       </c>
-      <c r="E193" s="8">
+      <c r="E193" s="7">
         <v>7</v>
       </c>
-      <c r="F193" s="8">
+      <c r="F193" s="7">
         <v>7</v>
       </c>
-      <c r="G193" s="8">
+      <c r="G193" s="7">
         <v>7</v>
       </c>
-      <c r="H193" s="9">
+      <c r="H193" s="8">
         <v>7.2</v>
       </c>
     </row>
     <row r="194" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B194" s="9" t="s">
+      <c r="B194" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="C194" s="8">
+      <c r="C194" s="7">
         <v>5</v>
       </c>
-      <c r="D194" s="8">
+      <c r="D194" s="7">
         <v>7</v>
       </c>
-      <c r="E194" s="8">
+      <c r="E194" s="7">
         <v>6</v>
       </c>
-      <c r="F194" s="8">
+      <c r="F194" s="7">
         <v>6</v>
       </c>
-      <c r="G194" s="8">
+      <c r="G194" s="7">
         <v>9</v>
       </c>
-      <c r="H194" s="9">
+      <c r="H194" s="8">
         <v>6.8</v>
       </c>
     </row>
     <row r="195" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B195" s="9" t="s">
+      <c r="B195" s="8" t="s">
         <v>382</v>
       </c>
-      <c r="C195" s="8">
+      <c r="C195" s="7">
         <v>6</v>
       </c>
-      <c r="D195" s="8">
+      <c r="D195" s="7">
         <v>6</v>
       </c>
-      <c r="E195" s="8">
+      <c r="E195" s="7">
         <v>6</v>
       </c>
-      <c r="F195" s="8">
+      <c r="F195" s="7">
         <v>5</v>
       </c>
-      <c r="G195" s="8">
+      <c r="G195" s="7">
         <v>7</v>
       </c>
-      <c r="H195" s="9">
+      <c r="H195" s="8">
         <v>6.5</v>
       </c>
     </row>
     <row r="196" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B196" s="9" t="s">
+      <c r="B196" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="C196" s="8">
+      <c r="C196" s="7">
         <v>6</v>
       </c>
-      <c r="D196" s="8">
+      <c r="D196" s="7">
         <v>5</v>
       </c>
-      <c r="E196" s="8">
+      <c r="E196" s="7">
         <v>7</v>
       </c>
-      <c r="F196" s="8">
+      <c r="F196" s="7">
         <v>5</v>
       </c>
-      <c r="G196" s="8">
+      <c r="G196" s="7">
         <v>6</v>
       </c>
-      <c r="H196" s="9">
+      <c r="H196" s="8">
         <v>6.3</v>
       </c>
     </row>
     <row r="197" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B197" s="9" t="s">
+      <c r="B197" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="C197" s="8">
+      <c r="C197" s="7">
         <v>5</v>
       </c>
-      <c r="D197" s="8">
+      <c r="D197" s="7">
         <v>5</v>
       </c>
-      <c r="E197" s="8">
+      <c r="E197" s="7">
         <v>5</v>
       </c>
-      <c r="F197" s="8">
+      <c r="F197" s="7">
         <v>5</v>
       </c>
-      <c r="G197" s="8">
+      <c r="G197" s="7">
         <v>7</v>
       </c>
-      <c r="H197" s="9">
+      <c r="H197" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="198" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B198" s="9" t="s">
+      <c r="B198" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="C198" s="8">
+      <c r="C198" s="7">
         <v>5</v>
       </c>
-      <c r="D198" s="8">
+      <c r="D198" s="7">
         <v>5</v>
       </c>
-      <c r="E198" s="8">
+      <c r="E198" s="7">
         <v>5</v>
       </c>
-      <c r="F198" s="8">
+      <c r="F198" s="7">
         <v>5</v>
       </c>
-      <c r="G198" s="8">
+      <c r="G198" s="7">
         <v>7</v>
       </c>
-      <c r="H198" s="9">
+      <c r="H198" s="8">
         <v>5.8</v>
       </c>
     </row>
     <row r="199" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B199" s="9" t="s">
+      <c r="B199" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C199" s="8">
+      <c r="C199" s="7">
         <v>4</v>
       </c>
-      <c r="D199" s="8">
+      <c r="D199" s="7">
         <v>5</v>
       </c>
-      <c r="E199" s="8">
+      <c r="E199" s="7">
         <v>4</v>
       </c>
-      <c r="F199" s="8">
+      <c r="F199" s="7">
         <v>4</v>
       </c>
-      <c r="G199" s="8">
+      <c r="G199" s="7">
         <v>7</v>
       </c>
-      <c r="H199" s="9">
+      <c r="H199" s="8">
         <v>5.5</v>
       </c>
     </row>
     <row r="202" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B202" s="7" t="s">
+      <c r="B202" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C202" s="7" t="s">
+      <c r="C202" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D202" s="7" t="s">
+      <c r="D202" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="E202" s="7" t="s">
+      <c r="E202" s="6" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="203" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B203" s="8">
+      <c r="B203" s="7">
         <v>1</v>
       </c>
-      <c r="C203" s="9" t="s">
+      <c r="C203" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="D203" s="8" t="s">
+      <c r="D203" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="E203" s="8" t="s">
+      <c r="E203" s="7" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="204" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B204" s="8">
+      <c r="B204" s="7">
         <v>2</v>
       </c>
-      <c r="C204" s="9" t="s">
+      <c r="C204" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="D204" s="8" t="s">
+      <c r="D204" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="E204" s="8" t="s">
+      <c r="E204" s="7" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="205" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B205" s="8">
+      <c r="B205" s="7">
         <v>3</v>
       </c>
-      <c r="C205" s="9" t="s">
+      <c r="C205" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="D205" s="8" t="s">
+      <c r="D205" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="E205" s="8" t="s">
+      <c r="E205" s="7" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="206" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B206" s="8">
+      <c r="B206" s="7">
         <v>4</v>
       </c>
-      <c r="C206" s="9" t="s">
+      <c r="C206" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="D206" s="8" t="s">
+      <c r="D206" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="E206" s="8" t="s">
+      <c r="E206" s="7" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="207" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B207" s="8">
+      <c r="B207" s="7">
         <v>5</v>
       </c>
-      <c r="C207" s="9" t="s">
+      <c r="C207" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="D207" s="8" t="s">
+      <c r="D207" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="E207" s="8" t="s">
+      <c r="E207" s="7" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="208" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B208" s="8">
+      <c r="B208" s="7">
         <v>6</v>
       </c>
-      <c r="C208" s="9" t="s">
+      <c r="C208" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="D208" s="8" t="s">
+      <c r="D208" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="E208" s="8" t="s">
+      <c r="E208" s="7" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="209" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B209" s="8">
+      <c r="B209" s="7">
         <v>7</v>
       </c>
-      <c r="C209" s="9" t="s">
+      <c r="C209" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="D209" s="8" t="s">
+      <c r="D209" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="E209" s="8" t="s">
+      <c r="E209" s="7" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="210" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B210" s="8">
+      <c r="B210" s="7">
         <v>8</v>
       </c>
-      <c r="C210" s="9" t="s">
+      <c r="C210" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="D210" s="8" t="s">
+      <c r="D210" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="E210" s="8" t="s">
+      <c r="E210" s="7" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="211" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B211" s="8">
+      <c r="B211" s="7">
         <v>9</v>
       </c>
-      <c r="C211" s="9" t="s">
+      <c r="C211" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="D211" s="8" t="s">
+      <c r="D211" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="E211" s="8" t="s">
+      <c r="E211" s="7" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="212" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B212" s="8">
+      <c r="B212" s="7">
         <v>10</v>
       </c>
-      <c r="C212" s="9" t="s">
+      <c r="C212" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="D212" s="8" t="s">
+      <c r="D212" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="E212" s="8" t="s">
+      <c r="E212" s="7" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="213" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B213" s="8">
+      <c r="B213" s="7">
         <v>11</v>
       </c>
-      <c r="C213" s="9" t="s">
+      <c r="C213" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="D213" s="8" t="s">
+      <c r="D213" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="E213" s="8" t="s">
+      <c r="E213" s="7" t="s">
         <v>401</v>
       </c>
     </row>
@@ -12243,14 +12309,15 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD57C989-6F2B-410E-8934-538033C06A98}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.5703125" customWidth="1"/>
     <col min="4" max="4" width="43.42578125" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>25</v>
       </c>
@@ -12258,7 +12325,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -12272,7 +12339,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>12</v>
       </c>
@@ -12283,7 +12350,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>11</v>
       </c>
@@ -12294,22 +12361,22 @@
         <v>462</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>440</v>
       </c>
@@ -12320,22 +12387,57 @@
         <v>463</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C9" s="3">
+        <v>46286</v>
+      </c>
+      <c r="D9" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>440</v>
       </c>
+      <c r="Q11" s="12"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q12" s="12"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q13" s="12"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q14" s="12"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q15" s="12"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q16" s="12"/>
+    </row>
+    <row r="17" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q17" s="12"/>
+    </row>
+    <row r="18" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q18" s="12"/>
+    </row>
+    <row r="19" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q19" s="12"/>
+    </row>
+    <row r="20" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q20" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/__docs/RoadMap.xlsx
+++ b/__docs/RoadMap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5607667F-174C-434C-83ED-4E4553462BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A3556B-33B2-46C3-8ACA-7A6ACED81749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,6 +21,7 @@
     <sheet name="ТекПроблем" sheetId="6" r:id="rId6"/>
     <sheet name="Анализ нейронки стратегий" sheetId="7" r:id="rId7"/>
     <sheet name="Работа" sheetId="8" r:id="rId8"/>
+    <sheet name="Текущие задачи" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="483">
   <si>
     <t>RL3 - это продолжение RL1</t>
   </si>
@@ -1478,6 +1479,42 @@
   </si>
   <si>
     <t>add_zigzag_window_210926</t>
+  </si>
+  <si>
+    <t>Работал над зигзагом 220926</t>
+  </si>
+  <si>
+    <t>Ордер тест</t>
+  </si>
+  <si>
+    <t>Получение ленты</t>
+  </si>
+  <si>
+    <t>Получение кластеров</t>
+  </si>
+  <si>
+    <t>Зигзаг</t>
+  </si>
+  <si>
+    <t>Починка алгоритмов</t>
+  </si>
+  <si>
+    <t>Улучшение алгоритмов</t>
+  </si>
+  <si>
+    <t>Создание новых VEG</t>
+  </si>
+  <si>
+    <t>Создание новых WEG</t>
+  </si>
+  <si>
+    <t>Создание ST1</t>
+  </si>
+  <si>
+    <t>Создание робота на зебре</t>
+  </si>
+  <si>
+    <t>Создание SEGML c обучением на истории</t>
   </si>
 </sst>
 </file>
@@ -12309,7 +12346,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD57C989-6F2B-410E-8934-538033C06A98}">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.5703125" customWidth="1"/>
@@ -12402,6 +12439,12 @@
       <c r="B10" t="s">
         <v>440</v>
       </c>
+      <c r="C10" s="3">
+        <v>46287</v>
+      </c>
+      <c r="D10" t="s">
+        <v>471</v>
+      </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
@@ -12413,31 +12456,2052 @@
       <c r="Q12" s="12"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
       <c r="Q13" s="12"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
       <c r="Q14" s="12"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
       <c r="Q15" s="12"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
       <c r="Q16" s="12"/>
     </row>
-    <row r="17" spans="17:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
       <c r="Q17" s="12"/>
     </row>
-    <row r="18" spans="17:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>48</v>
+      </c>
       <c r="Q18" s="12"/>
     </row>
-    <row r="19" spans="17:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>50</v>
+      </c>
       <c r="Q19" s="12"/>
     </row>
-    <row r="20" spans="17:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
       <c r="Q20" s="12"/>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>440</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10B68135-0511-4A43-8FE7-1FF0E8B64F45}">
+  <dimension ref="A2:G378"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="7" width="39.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C3" t="s">
+        <v>476</v>
+      </c>
+      <c r="D3" t="s">
+        <v>476</v>
+      </c>
+      <c r="E3" t="s">
+        <v>477</v>
+      </c>
+      <c r="F3" t="s">
+        <v>476</v>
+      </c>
+      <c r="G3" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>473</v>
+      </c>
+      <c r="C4" t="s">
+        <v>477</v>
+      </c>
+      <c r="D4" t="s">
+        <v>477</v>
+      </c>
+      <c r="E4" t="s">
+        <v>478</v>
+      </c>
+      <c r="F4" t="s">
+        <v>477</v>
+      </c>
+      <c r="G4" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>474</v>
+      </c>
+      <c r="E5" t="s">
+        <v>479</v>
+      </c>
+      <c r="G5" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>475</v>
+      </c>
+      <c r="G6" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A289">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A291">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A293">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A295">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A296">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A298">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A299">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A300">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A301">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A302">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A303">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A307">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A308">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A309">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A310">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A311">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A312">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A313">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A314">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A315">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A316">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A317">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A318">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A319">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A320">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A321">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A322">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A323">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A324">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A325">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A326">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A327">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A328">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A329">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A330">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A331">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A332">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A333">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A334">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A335">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A336">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A337">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A338">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A340">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A341">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A342">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A343">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A344">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A345">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A346">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A347">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A348">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A349">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A350">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A351">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A352">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A353">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A354">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A356">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A357">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A358">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A359">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A360">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A361">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A362">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A363">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A364">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A365">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A366">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A367">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A368">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A369">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A370">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A371">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A372">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A373">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A374">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A375">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A376">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A377">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A378">
+        <v>376</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/__docs/RoadMap.xlsx
+++ b/__docs/RoadMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A3556B-33B2-46C3-8ACA-7A6ACED81749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF58C30-0039-4BD1-B24A-8EA696AB6AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тезисы" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="492">
   <si>
     <t>RL3 - это продолжение RL1</t>
   </si>
@@ -1515,6 +1515,33 @@
   </si>
   <si>
     <t>Создание SEGML c обучением на истории</t>
+  </si>
+  <si>
+    <t>Работал над зигзагом 230926</t>
+  </si>
+  <si>
+    <t>UEG8_SOLDIER</t>
+  </si>
+  <si>
+    <t>AVENGER на add_zigzag_window_210926</t>
+  </si>
+  <si>
+    <t>Новая версия на add_zigzag_window_210926</t>
+  </si>
+  <si>
+    <t>VEG1_MOON</t>
+  </si>
+  <si>
+    <t>Должен время для UT</t>
+  </si>
+  <si>
+    <t>Разработка UEG8</t>
+  </si>
+  <si>
+    <t>UEG8_DETECTIVE</t>
+  </si>
+  <si>
+    <t>Soldier с дополнительными настройками</t>
   </si>
 </sst>
 </file>
@@ -5227,11 +5254,11 @@
       </c>
       <c r="N2">
         <f>COUNTIF(D:D,N1)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O2">
         <f>COUNTIF(D:D,O1)</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P2">
         <f>COUNTIF(D:D,P1)</f>
@@ -7219,15 +7246,51 @@
       <c r="A114">
         <v>113</v>
       </c>
+      <c r="B114" t="s">
+        <v>484</v>
+      </c>
+      <c r="C114" s="3">
+        <v>46290</v>
+      </c>
+      <c r="D114" t="s">
+        <v>50</v>
+      </c>
+      <c r="E114" t="s">
+        <v>485</v>
+      </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
+      <c r="B115" t="s">
+        <v>487</v>
+      </c>
+      <c r="C115" s="3">
+        <v>46290</v>
+      </c>
+      <c r="D115" t="s">
+        <v>48</v>
+      </c>
+      <c r="E115" t="s">
+        <v>486</v>
+      </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>490</v>
+      </c>
+      <c r="C116" s="3">
+        <v>46290</v>
+      </c>
+      <c r="D116" t="s">
+        <v>50</v>
+      </c>
+      <c r="E116" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -12402,11 +12465,20 @@
       <c r="B5" t="s">
         <v>48</v>
       </c>
+      <c r="E5" t="s">
+        <v>488</v>
+      </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>50</v>
       </c>
+      <c r="C6" s="3">
+        <v>46290</v>
+      </c>
+      <c r="D6" t="s">
+        <v>489</v>
+      </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
@@ -12449,6 +12521,12 @@
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>440</v>
+      </c>
+      <c r="C11" s="3">
+        <v>46288</v>
+      </c>
+      <c r="D11" t="s">
+        <v>483</v>
       </c>
       <c r="Q11" s="12"/>
     </row>

--- a/__docs/RoadMap.xlsx
+++ b/__docs/RoadMap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF58C30-0039-4BD1-B24A-8EA696AB6AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D38D178-48F9-4C1C-BCB5-6F9856B20876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="494">
   <si>
     <t>RL3 - это продолжение RL1</t>
   </si>
@@ -1523,9 +1523,6 @@
     <t>UEG8_SOLDIER</t>
   </si>
   <si>
-    <t>AVENGER на add_zigzag_window_210926</t>
-  </si>
-  <si>
     <t>Новая версия на add_zigzag_window_210926</t>
   </si>
   <si>
@@ -1538,10 +1535,19 @@
     <t>Разработка UEG8</t>
   </si>
   <si>
-    <t>UEG8_DETECTIVE</t>
-  </si>
-  <si>
-    <t>Soldier с дополнительными настройками</t>
+    <t>AVENGER на add_zigzag_window_210926 с доп настройками</t>
+  </si>
+  <si>
+    <t>UEG7_LOVERGOOSE</t>
+  </si>
+  <si>
+    <t>UEG7_DODO на add_average_fractals_window</t>
+  </si>
+  <si>
+    <t>UEG7_LOVERDUCK</t>
+  </si>
+  <si>
+    <t>UEG7_DUELDODO на add_average_fractals_window</t>
   </si>
 </sst>
 </file>
@@ -5258,7 +5264,7 @@
       </c>
       <c r="O2">
         <f>COUNTIF(D:D,O1)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P2">
         <f>COUNTIF(D:D,P1)</f>
@@ -7256,7 +7262,7 @@
         <v>50</v>
       </c>
       <c r="E114" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -7264,7 +7270,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C115" s="3">
         <v>46290</v>
@@ -7273,7 +7279,7 @@
         <v>48</v>
       </c>
       <c r="E115" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -7296,6 +7302,18 @@
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>492</v>
+      </c>
+      <c r="C117" s="3">
+        <v>46290</v>
+      </c>
+      <c r="D117" t="s">
+        <v>50</v>
+      </c>
+      <c r="E117" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -12466,7 +12484,7 @@
         <v>48</v>
       </c>
       <c r="E5" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -12477,7 +12495,7 @@
         <v>46290</v>
       </c>
       <c r="D6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">

--- a/__docs/RoadMap.xlsx
+++ b/__docs/RoadMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D38D178-48F9-4C1C-BCB5-6F9856B20876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28616CD7-7552-41AA-A65F-F88F87573119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тезисы" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="509">
   <si>
     <t>RL3 - это продолжение RL1</t>
   </si>
@@ -1388,9 +1388,6 @@
     <t>Что делал</t>
   </si>
   <si>
-    <t>Своб</t>
-  </si>
-  <si>
     <t>PEG18 на супертренде</t>
   </si>
   <si>
@@ -1469,9 +1466,6 @@
     <t>UEG4_CANADIAN</t>
   </si>
   <si>
-    <t>4 версия GGD</t>
-  </si>
-  <si>
     <t>Устарел</t>
   </si>
   <si>
@@ -1529,9 +1523,6 @@
     <t>VEG1_MOON</t>
   </si>
   <si>
-    <t>Должен время для UT</t>
-  </si>
-  <si>
     <t>Разработка UEG8</t>
   </si>
   <si>
@@ -1548,6 +1539,60 @@
   </si>
   <si>
     <t>UEG7_DUELDODO на add_average_fractals_window</t>
+  </si>
+  <si>
+    <t>UEG4_FALCON2</t>
+  </si>
+  <si>
+    <t>Версия на оконных фунциях</t>
+  </si>
+  <si>
+    <t>UEG4_PELICAN2</t>
+  </si>
+  <si>
+    <t>UEG7_CELEBRITY</t>
+  </si>
+  <si>
+    <t>UEG7_CARRIER</t>
+  </si>
+  <si>
+    <t>UEG7_DETECTIVE</t>
+  </si>
+  <si>
+    <t>UEG7_CANNIBAL</t>
+  </si>
+  <si>
+    <t>UEG9_BIRDWATCHER2</t>
+  </si>
+  <si>
+    <t>UEG9_GRAVY2</t>
+  </si>
+  <si>
+    <t>UEG7_VULTURE на оконных функциях</t>
+  </si>
+  <si>
+    <t>UEG7_SHERIFF на оконными функциями</t>
+  </si>
+  <si>
+    <t>UEG7_PIGEON на оконных функциях</t>
+  </si>
+  <si>
+    <t>UEG7_ADVENTURE на оконных функциях</t>
+  </si>
+  <si>
+    <t>4 версия GGD с оконными функциями</t>
+  </si>
+  <si>
+    <t>Разработка UEG4-9</t>
+  </si>
+  <si>
+    <t>Разн</t>
+  </si>
+  <si>
+    <t>Написать 6-7 с rsi</t>
+  </si>
+  <si>
+    <t>Анализ оптимизации</t>
   </si>
 </sst>
 </file>
@@ -5213,10 +5258,10 @@
         <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="L1" t="s">
         <v>12</v>
@@ -5264,7 +5309,7 @@
       </c>
       <c r="O2">
         <f>COUNTIF(D:D,O1)</f>
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="P2">
         <f>COUNTIF(D:D,P1)</f>
@@ -5308,7 +5353,7 @@
         <v>46283</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H4" t="s">
         <v>37</v>
@@ -5371,7 +5416,7 @@
         <v>46267</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -5445,7 +5490,7 @@
         <v>46286</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -5570,7 +5615,7 @@
         <v>46267</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -5593,7 +5638,7 @@
         <v>46267</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -5616,7 +5661,7 @@
         <v>46267</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5843,7 +5888,7 @@
         <v>46266</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -5866,7 +5911,7 @@
         <v>46286</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -5889,7 +5934,7 @@
         <v>46286</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -5912,7 +5957,7 @@
         <v>46286</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -5935,7 +5980,7 @@
         <v>46286</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -6536,7 +6581,7 @@
         <v>46266</v>
       </c>
       <c r="G72" s="14" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -6576,7 +6621,7 @@
         <v>46266</v>
       </c>
       <c r="G74" s="14" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -6599,7 +6644,7 @@
         <v>46266</v>
       </c>
       <c r="G75" s="14" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -7066,7 +7111,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C103" s="3">
         <v>46266</v>
@@ -7075,7 +7120,7 @@
         <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -7083,7 +7128,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C104" s="3">
         <v>46266</v>
@@ -7092,7 +7137,7 @@
         <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -7100,7 +7145,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C105" s="3">
         <v>46266</v>
@@ -7109,7 +7154,7 @@
         <v>12</v>
       </c>
       <c r="E105" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -7117,7 +7162,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C106" s="3">
         <v>46266</v>
@@ -7126,7 +7171,7 @@
         <v>12</v>
       </c>
       <c r="E106" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -7134,7 +7179,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C107" s="3">
         <v>46266</v>
@@ -7143,7 +7188,7 @@
         <v>12</v>
       </c>
       <c r="E107" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -7151,7 +7196,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C108" s="3">
         <v>46266</v>
@@ -7168,7 +7213,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C109" s="3">
         <v>46267</v>
@@ -7177,7 +7222,7 @@
         <v>11</v>
       </c>
       <c r="E109" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -7185,7 +7230,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C110" s="3">
         <v>46267</v>
@@ -7194,7 +7239,7 @@
         <v>11</v>
       </c>
       <c r="E110" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -7202,7 +7247,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C111" s="3">
         <v>46267</v>
@@ -7211,7 +7256,7 @@
         <v>11</v>
       </c>
       <c r="E111" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -7219,7 +7264,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C112" s="3">
         <v>46267</v>
@@ -7228,7 +7273,7 @@
         <v>11</v>
       </c>
       <c r="E112" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -7236,7 +7281,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C113" s="3">
         <v>46286</v>
@@ -7245,7 +7290,7 @@
         <v>50</v>
       </c>
       <c r="E113" t="s">
-        <v>467</v>
+        <v>504</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -7253,7 +7298,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C114" s="3">
         <v>46290</v>
@@ -7262,7 +7307,7 @@
         <v>50</v>
       </c>
       <c r="E114" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -7270,7 +7315,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C115" s="3">
         <v>46290</v>
@@ -7279,7 +7324,7 @@
         <v>48</v>
       </c>
       <c r="E115" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -7287,7 +7332,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C116" s="3">
         <v>46290</v>
@@ -7296,7 +7341,7 @@
         <v>50</v>
       </c>
       <c r="E116" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -7304,7 +7349,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C117" s="3">
         <v>46290</v>
@@ -7313,47 +7358,143 @@
         <v>50</v>
       </c>
       <c r="E117" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
+      <c r="B118" t="s">
+        <v>491</v>
+      </c>
+      <c r="C118" s="3">
+        <v>46291</v>
+      </c>
+      <c r="D118" t="s">
+        <v>50</v>
+      </c>
+      <c r="E118" t="s">
+        <v>492</v>
+      </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
+      <c r="B119" t="s">
+        <v>493</v>
+      </c>
+      <c r="C119" s="3">
+        <v>46291</v>
+      </c>
+      <c r="D119" t="s">
+        <v>50</v>
+      </c>
+      <c r="E119" t="s">
+        <v>492</v>
+      </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
+      <c r="B120" t="s">
+        <v>494</v>
+      </c>
+      <c r="C120" s="3">
+        <v>46291</v>
+      </c>
+      <c r="D120" t="s">
+        <v>50</v>
+      </c>
+      <c r="E120" t="s">
+        <v>503</v>
+      </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
+      <c r="B121" t="s">
+        <v>495</v>
+      </c>
+      <c r="C121" s="3">
+        <v>46291</v>
+      </c>
+      <c r="D121" t="s">
+        <v>50</v>
+      </c>
+      <c r="E121" t="s">
+        <v>502</v>
+      </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
+      <c r="B122" t="s">
+        <v>496</v>
+      </c>
+      <c r="C122" s="3">
+        <v>46291</v>
+      </c>
+      <c r="D122" t="s">
+        <v>50</v>
+      </c>
+      <c r="E122" t="s">
+        <v>501</v>
+      </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
+      <c r="B123" t="s">
+        <v>497</v>
+      </c>
+      <c r="C123" s="3">
+        <v>46291</v>
+      </c>
+      <c r="D123" t="s">
+        <v>50</v>
+      </c>
+      <c r="E123" t="s">
+        <v>500</v>
+      </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
+      <c r="B124" t="s">
+        <v>498</v>
+      </c>
+      <c r="C124" s="3">
+        <v>46291</v>
+      </c>
+      <c r="D124" t="s">
+        <v>50</v>
+      </c>
+      <c r="E124" t="s">
+        <v>492</v>
+      </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>499</v>
+      </c>
+      <c r="C125" s="3">
+        <v>46291</v>
+      </c>
+      <c r="D125" t="s">
+        <v>50</v>
+      </c>
+      <c r="E125" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -12427,7 +12568,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD57C989-6F2B-410E-8934-538033C06A98}">
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q339"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.5703125" customWidth="1"/>
@@ -12442,194 +12583,1844 @@
       <c r="D1" t="s">
         <v>439</v>
       </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" t="s">
+        <v>506</v>
+      </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>46283</v>
+        <v>46266</v>
       </c>
       <c r="D2" t="s">
-        <v>464</v>
+        <v>453</v>
+      </c>
+      <c r="F2">
+        <f>COUNTIF(B:B,F1)</f>
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <f>COUNTIF(B:B,G1)</f>
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <f>COUNTIF(B:B,H1)</f>
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <f>COUNTIF(B:B,I1)</f>
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <f>COUNTIF(B:B,J1)</f>
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <f>COUNTIF(B:B,K1)</f>
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <f>COUNTIF(B:B,L1)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D3" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>506</v>
       </c>
       <c r="C4" s="3">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="D4" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
       <c r="B5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" t="s">
-        <v>487</v>
+        <v>28</v>
+      </c>
+      <c r="C5" s="3">
+        <v>46283</v>
+      </c>
+      <c r="D5" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
       <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="3">
+        <v>46286</v>
+      </c>
+      <c r="D6" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="3">
+        <v>46287</v>
+      </c>
+      <c r="D7" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="3">
+        <v>46288</v>
+      </c>
+      <c r="D8" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C9" s="3">
         <v>46290</v>
       </c>
-      <c r="D6" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>440</v>
-      </c>
-      <c r="C8" s="3">
-        <v>46269</v>
-      </c>
-      <c r="D8" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>440</v>
-      </c>
-      <c r="C9" s="3">
-        <v>46286</v>
-      </c>
       <c r="D9" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
       <c r="B10" t="s">
-        <v>440</v>
+        <v>50</v>
       </c>
       <c r="C10" s="3">
-        <v>46287</v>
+        <v>46291</v>
       </c>
       <c r="D10" t="s">
-        <v>471</v>
+        <v>505</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
       <c r="B11" t="s">
-        <v>440</v>
+        <v>506</v>
       </c>
       <c r="C11" s="3">
-        <v>46288</v>
+        <v>46292</v>
       </c>
       <c r="D11" t="s">
-        <v>483</v>
+        <v>508</v>
       </c>
       <c r="Q11" s="12"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
       <c r="Q12" s="12"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>2</v>
-      </c>
-      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q13" s="12"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="Q14" s="12"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="Q15" s="12"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="Q16" s="12"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="Q17" s="12"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="Q18" s="12"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="Q19" s="12"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="Q20" s="12"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="Q13" s="12"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q14" s="12"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q15" s="12"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q16" s="12"/>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49">
         <v>48</v>
       </c>
-      <c r="Q17" s="12"/>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q18" s="12"/>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51">
         <v>50</v>
       </c>
-      <c r="Q19" s="12"/>
-    </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q20" s="12"/>
-    </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>440</v>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A289">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A291">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A293">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A295">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A296">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A298">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A299">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A300">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A301">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A302">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A303">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A307">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A308">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A309">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A310">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A311">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A312">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A313">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A314">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A315">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A316">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A317">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A318">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A319">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A320">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A321">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A322">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A323">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A324">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A325">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A326">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A327">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A328">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A329">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A330">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A331">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A332">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A333">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A334">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A335">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A336">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A337">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A338">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -12671,22 +14462,22 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -12694,22 +14485,22 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E4" t="s">
+        <v>476</v>
+      </c>
+      <c r="F4" t="s">
+        <v>475</v>
+      </c>
+      <c r="G4" t="s">
         <v>478</v>
-      </c>
-      <c r="F4" t="s">
-        <v>477</v>
-      </c>
-      <c r="G4" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -12717,13 +14508,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E5" t="s">
+        <v>477</v>
+      </c>
+      <c r="F5" t="s">
+        <v>507</v>
+      </c>
+      <c r="G5" t="s">
         <v>479</v>
-      </c>
-      <c r="G5" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -12731,10 +14525,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="G6" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">

--- a/__docs/RoadMap.xlsx
+++ b/__docs/RoadMap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28616CD7-7552-41AA-A65F-F88F87573119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA36891B-FEB0-43B4-96CB-9E74B1DC5A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="519">
   <si>
     <t>RL3 - это продолжение RL1</t>
   </si>
@@ -1593,6 +1593,36 @@
   </si>
   <si>
     <t>Анализ оптимизации</t>
+  </si>
+  <si>
+    <t>Зоны имбаланса (можно по зигзагу)</t>
+  </si>
+  <si>
+    <t>Профиль объема</t>
+  </si>
+  <si>
+    <t>Свечные паттерны</t>
+  </si>
+  <si>
+    <t>Связать VEG и WEG</t>
+  </si>
+  <si>
+    <t>Алгоритмы на велкро</t>
+  </si>
+  <si>
+    <t>VEG1_EARTH</t>
+  </si>
+  <si>
+    <t>VEG1_VENUS на оконных фунциях</t>
+  </si>
+  <si>
+    <t>PEG30_ETC</t>
+  </si>
+  <si>
+    <t>Робот с заявками на шаг от close</t>
+  </si>
+  <si>
+    <t>Добавление step action</t>
   </si>
 </sst>
 </file>
@@ -1635,7 +1665,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1666,6 +1696,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1679,7 +1715,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1715,6 +1751,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -5297,7 +5334,7 @@
       </c>
       <c r="L2">
         <f>COUNTIF(D:D,L1)</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M2">
         <f>COUNTIF(D:D,M1)</f>
@@ -5305,7 +5342,7 @@
       </c>
       <c r="N2">
         <f>COUNTIF(D:D,N1)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O2">
         <f>COUNTIF(D:D,O1)</f>
@@ -5514,7 +5551,7 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="17" t="s">
         <v>53</v>
       </c>
       <c r="C13" s="3">
@@ -5548,7 +5585,7 @@
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="5" t="s">
         <v>54</v>
       </c>
       <c r="C15" s="3">
@@ -5668,7 +5705,7 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="17" t="s">
         <v>310</v>
       </c>
       <c r="C21" s="3">
@@ -5685,7 +5722,7 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="17" t="s">
         <v>311</v>
       </c>
       <c r="C22" s="3">
@@ -5702,7 +5739,7 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="17" t="s">
         <v>312</v>
       </c>
       <c r="C23" s="3">
@@ -5719,7 +5756,7 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="17" t="s">
         <v>313</v>
       </c>
       <c r="C24" s="3">
@@ -5753,7 +5790,7 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="17" t="s">
         <v>315</v>
       </c>
       <c r="C26" s="3">
@@ -5804,7 +5841,7 @@
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="17" t="s">
         <v>318</v>
       </c>
       <c r="C29" s="3">
@@ -5838,7 +5875,7 @@
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="5" t="s">
         <v>320</v>
       </c>
       <c r="C31" s="3">
@@ -5984,44 +6021,56 @@
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38">
+      <c r="A38" s="14">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="15">
         <v>46248</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="14" t="s">
         <v>432</v>
       </c>
+      <c r="F38" s="15">
+        <v>46294</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>467</v>
+      </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39">
+      <c r="A39" s="14">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="15">
         <v>46248</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="14" t="s">
         <v>432</v>
+      </c>
+      <c r="F39" s="15">
+        <v>46294</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="5" t="s">
         <v>329</v>
       </c>
       <c r="C40" s="3">
@@ -6170,7 +6219,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6187,7 +6236,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6204,7 +6253,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6221,7 +6270,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6238,7 +6287,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6255,41 +6304,53 @@
         <v>432</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="14">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="14" t="s">
         <v>343</v>
       </c>
-      <c r="C54" s="3">
+      <c r="C54" s="15">
         <v>46248</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="14" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55">
+      <c r="F54" s="15">
+        <v>46294</v>
+      </c>
+      <c r="G54" s="14" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="14">
         <v>54</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="14" t="s">
         <v>344</v>
       </c>
-      <c r="C55" s="3">
+      <c r="C55" s="15">
         <v>46248</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="14" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F55" s="15">
+        <v>46294</v>
+      </c>
+      <c r="G55" s="14" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6306,11 +6367,11 @@
         <v>44</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="17" t="s">
         <v>346</v>
       </c>
       <c r="C57" s="3">
@@ -6323,7 +6384,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6340,11 +6401,11 @@
         <v>44</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="17" t="s">
         <v>348</v>
       </c>
       <c r="C59" s="3">
@@ -6357,11 +6418,11 @@
         <v>432</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="17" t="s">
         <v>349</v>
       </c>
       <c r="C60" s="3">
@@ -6374,11 +6435,11 @@
         <v>44</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="17" t="s">
         <v>350</v>
       </c>
       <c r="C61" s="3">
@@ -6391,7 +6452,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6408,7 +6469,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -6425,7 +6486,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -6463,7 +6524,7 @@
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="17" t="s">
         <v>355</v>
       </c>
       <c r="C66" s="3">
@@ -6480,7 +6541,7 @@
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="17" t="s">
         <v>356</v>
       </c>
       <c r="C67" s="3">
@@ -6668,7 +6729,7 @@
       <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="5" t="s">
         <v>407</v>
       </c>
       <c r="C77" s="3">
@@ -6685,7 +6746,7 @@
       <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="5" t="s">
         <v>408</v>
       </c>
       <c r="C78" s="3">
@@ -6702,7 +6763,7 @@
       <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="5" t="s">
         <v>409</v>
       </c>
       <c r="C79" s="3">
@@ -6719,7 +6780,7 @@
       <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="5" t="s">
         <v>410</v>
       </c>
       <c r="C80" s="3">
@@ -6736,7 +6797,7 @@
       <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="5" t="s">
         <v>411</v>
       </c>
       <c r="C81" s="3">
@@ -6753,7 +6814,7 @@
       <c r="A82">
         <v>81</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="5" t="s">
         <v>412</v>
       </c>
       <c r="C82" s="3">
@@ -6770,7 +6831,7 @@
       <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="5" t="s">
         <v>413</v>
       </c>
       <c r="C83" s="3">
@@ -6787,7 +6848,7 @@
       <c r="A84">
         <v>83</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="5" t="s">
         <v>414</v>
       </c>
       <c r="C84" s="3">
@@ -6804,7 +6865,7 @@
       <c r="A85">
         <v>84</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="5" t="s">
         <v>415</v>
       </c>
       <c r="C85" s="3">
@@ -6821,7 +6882,7 @@
       <c r="A86">
         <v>85</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="5" t="s">
         <v>416</v>
       </c>
       <c r="C86" s="3">
@@ -6838,7 +6899,7 @@
       <c r="A87">
         <v>86</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="5" t="s">
         <v>417</v>
       </c>
       <c r="C87" s="3">
@@ -6855,7 +6916,7 @@
       <c r="A88">
         <v>87</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="5" t="s">
         <v>418</v>
       </c>
       <c r="C88" s="3">
@@ -6872,7 +6933,7 @@
       <c r="A89">
         <v>88</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="5" t="s">
         <v>419</v>
       </c>
       <c r="C89" s="3">
@@ -6923,7 +6984,7 @@
       <c r="A92">
         <v>91</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="5" t="s">
         <v>422</v>
       </c>
       <c r="C92" s="3">
@@ -6940,7 +7001,7 @@
       <c r="A93">
         <v>92</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="5" t="s">
         <v>423</v>
       </c>
       <c r="C93" s="3">
@@ -6957,7 +7018,7 @@
       <c r="A94">
         <v>93</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="5" t="s">
         <v>424</v>
       </c>
       <c r="C94" s="3">
@@ -6974,7 +7035,7 @@
       <c r="A95">
         <v>94</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="5" t="s">
         <v>425</v>
       </c>
       <c r="C95" s="3">
@@ -6991,7 +7052,7 @@
       <c r="A96">
         <v>95</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="5" t="s">
         <v>426</v>
       </c>
       <c r="C96" s="3">
@@ -7008,7 +7069,7 @@
       <c r="A97">
         <v>96</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="5" t="s">
         <v>427</v>
       </c>
       <c r="C97" s="3">
@@ -7025,7 +7086,7 @@
       <c r="A98">
         <v>97</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="5" t="s">
         <v>428</v>
       </c>
       <c r="C98" s="3">
@@ -7042,7 +7103,7 @@
       <c r="A99">
         <v>98</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="5" t="s">
         <v>429</v>
       </c>
       <c r="C99" s="3">
@@ -7059,7 +7120,7 @@
       <c r="A100">
         <v>99</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="5" t="s">
         <v>433</v>
       </c>
       <c r="C100" s="3">
@@ -7076,7 +7137,7 @@
       <c r="A101">
         <v>100</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="5" t="s">
         <v>435</v>
       </c>
       <c r="C101" s="3">
@@ -7178,7 +7239,7 @@
       <c r="A107">
         <v>106</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="17" t="s">
         <v>447</v>
       </c>
       <c r="C107" s="3">
@@ -7280,7 +7341,7 @@
       <c r="A113">
         <v>112</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="17" t="s">
         <v>465</v>
       </c>
       <c r="C113" s="3">
@@ -7365,7 +7426,7 @@
       <c r="A118">
         <v>117</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="17" t="s">
         <v>491</v>
       </c>
       <c r="C118" s="3">
@@ -7382,7 +7443,7 @@
       <c r="A119">
         <v>118</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="17" t="s">
         <v>493</v>
       </c>
       <c r="C119" s="3">
@@ -7467,7 +7528,7 @@
       <c r="A124">
         <v>123</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="17" t="s">
         <v>498</v>
       </c>
       <c r="C124" s="3">
@@ -7501,10 +7562,34 @@
       <c r="A126">
         <v>125</v>
       </c>
+      <c r="B126" t="s">
+        <v>514</v>
+      </c>
+      <c r="C126" s="3">
+        <v>46294</v>
+      </c>
+      <c r="D126" t="s">
+        <v>48</v>
+      </c>
+      <c r="E126" t="s">
+        <v>515</v>
+      </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>516</v>
+      </c>
+      <c r="C127" s="3">
+        <v>46294</v>
+      </c>
+      <c r="D127" t="s">
+        <v>12</v>
+      </c>
+      <c r="E127" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -12620,7 +12705,7 @@
       </c>
       <c r="F2">
         <f>COUNTIF(B:B,F1)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <f>COUNTIF(B:B,G1)</f>
@@ -12777,6 +12862,15 @@
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="3">
+        <v>46294</v>
+      </c>
+      <c r="D12" t="s">
+        <v>518</v>
       </c>
       <c r="Q12" s="12"/>
     </row>
@@ -14510,6 +14604,9 @@
       <c r="B5" t="s">
         <v>472</v>
       </c>
+      <c r="C5" t="s">
+        <v>513</v>
+      </c>
       <c r="E5" t="s">
         <v>477</v>
       </c>
@@ -14527,6 +14624,12 @@
       <c r="B6" t="s">
         <v>473</v>
       </c>
+      <c r="E6" t="s">
+        <v>510</v>
+      </c>
+      <c r="F6" t="s">
+        <v>509</v>
+      </c>
       <c r="G6" t="s">
         <v>480</v>
       </c>
@@ -14535,10 +14638,16 @@
       <c r="A7">
         <v>5</v>
       </c>
+      <c r="E7" t="s">
+        <v>511</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">

--- a/__docs/RoadMap.xlsx
+++ b/__docs/RoadMap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA36891B-FEB0-43B4-96CB-9E74B1DC5A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D49512-D9F8-40A0-A622-45DEDC9CDBB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="523">
   <si>
     <t>RL3 - это продолжение RL1</t>
   </si>
@@ -1623,6 +1623,18 @@
   </si>
   <si>
     <t>Добавление step action</t>
+  </si>
+  <si>
+    <t>Анализ оптимизации, результатов</t>
+  </si>
+  <si>
+    <t>PEG30_ETC2</t>
+  </si>
+  <si>
+    <t>Робот с заявками на шаг от close со спредом</t>
+  </si>
+  <si>
+    <t>Работа со spred action</t>
   </si>
 </sst>
 </file>
@@ -1748,10 +1760,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2085,7 +2097,7 @@
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -2093,13 +2105,13 @@
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="16"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="17" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -2107,43 +2119,43 @@
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="16"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="16"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="16"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="16"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="16"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="16"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="16"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="2" t="s">
         <v>17</v>
       </c>
@@ -5334,7 +5346,7 @@
       </c>
       <c r="L2">
         <f>COUNTIF(D:D,L1)</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M2">
         <f>COUNTIF(D:D,M1)</f>
@@ -5551,7 +5563,7 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="16" t="s">
         <v>53</v>
       </c>
       <c r="C13" s="3">
@@ -5705,7 +5717,7 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="16" t="s">
         <v>310</v>
       </c>
       <c r="C21" s="3">
@@ -5722,7 +5734,7 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="16" t="s">
         <v>311</v>
       </c>
       <c r="C22" s="3">
@@ -5739,7 +5751,7 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="16" t="s">
         <v>312</v>
       </c>
       <c r="C23" s="3">
@@ -5756,7 +5768,7 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="16" t="s">
         <v>313</v>
       </c>
       <c r="C24" s="3">
@@ -5790,7 +5802,7 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="16" t="s">
         <v>315</v>
       </c>
       <c r="C26" s="3">
@@ -5841,7 +5853,7 @@
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="16" t="s">
         <v>318</v>
       </c>
       <c r="C29" s="3">
@@ -6371,7 +6383,7 @@
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" s="17" t="s">
+      <c r="B57" s="16" t="s">
         <v>346</v>
       </c>
       <c r="C57" s="3">
@@ -6405,7 +6417,7 @@
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" s="17" t="s">
+      <c r="B59" s="16" t="s">
         <v>348</v>
       </c>
       <c r="C59" s="3">
@@ -6422,7 +6434,7 @@
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" s="17" t="s">
+      <c r="B60" s="16" t="s">
         <v>349</v>
       </c>
       <c r="C60" s="3">
@@ -6439,7 +6451,7 @@
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" s="17" t="s">
+      <c r="B61" s="16" t="s">
         <v>350</v>
       </c>
       <c r="C61" s="3">
@@ -6524,7 +6536,7 @@
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" s="17" t="s">
+      <c r="B66" s="16" t="s">
         <v>355</v>
       </c>
       <c r="C66" s="3">
@@ -6541,7 +6553,7 @@
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" s="17" t="s">
+      <c r="B67" s="16" t="s">
         <v>356</v>
       </c>
       <c r="C67" s="3">
@@ -7239,7 +7251,7 @@
       <c r="A107">
         <v>106</v>
       </c>
-      <c r="B107" s="17" t="s">
+      <c r="B107" s="16" t="s">
         <v>447</v>
       </c>
       <c r="C107" s="3">
@@ -7341,7 +7353,7 @@
       <c r="A113">
         <v>112</v>
       </c>
-      <c r="B113" s="17" t="s">
+      <c r="B113" s="16" t="s">
         <v>465</v>
       </c>
       <c r="C113" s="3">
@@ -7426,7 +7438,7 @@
       <c r="A118">
         <v>117</v>
       </c>
-      <c r="B118" s="17" t="s">
+      <c r="B118" s="16" t="s">
         <v>491</v>
       </c>
       <c r="C118" s="3">
@@ -7443,7 +7455,7 @@
       <c r="A119">
         <v>118</v>
       </c>
-      <c r="B119" s="17" t="s">
+      <c r="B119" s="16" t="s">
         <v>493</v>
       </c>
       <c r="C119" s="3">
@@ -7528,7 +7540,7 @@
       <c r="A124">
         <v>123</v>
       </c>
-      <c r="B124" s="17" t="s">
+      <c r="B124" s="16" t="s">
         <v>498</v>
       </c>
       <c r="C124" s="3">
@@ -7595,6 +7607,18 @@
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>520</v>
+      </c>
+      <c r="C128" s="3">
+        <v>46297</v>
+      </c>
+      <c r="D128" t="s">
+        <v>12</v>
+      </c>
+      <c r="E128" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
@@ -12705,7 +12729,7 @@
       </c>
       <c r="F2">
         <f>COUNTIF(B:B,F1)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2">
         <f>COUNTIF(B:B,G1)</f>
@@ -12729,7 +12753,7 @@
       </c>
       <c r="L2">
         <f>COUNTIF(B:B,L1)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -12878,11 +12902,29 @@
       <c r="A13">
         <v>12</v>
       </c>
+      <c r="B13" t="s">
+        <v>506</v>
+      </c>
+      <c r="C13" s="3">
+        <v>46295</v>
+      </c>
+      <c r="D13" t="s">
+        <v>519</v>
+      </c>
       <c r="Q13" s="12"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="3">
+        <v>46297</v>
+      </c>
+      <c r="D14" t="s">
+        <v>522</v>
       </c>
       <c r="Q14" s="12"/>
     </row>

--- a/__docs/RoadMap.xlsx
+++ b/__docs/RoadMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D49512-D9F8-40A0-A622-45DEDC9CDBB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937BE00C-AA97-4018-BF3B-00104DC9C6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тезисы" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="531">
   <si>
     <t>RL3 - это продолжение RL1</t>
   </si>
@@ -1635,6 +1635,30 @@
   </si>
   <si>
     <t>Работа со spred action</t>
+  </si>
+  <si>
+    <t>новые PEG17</t>
+  </si>
+  <si>
+    <t>PEG17_PROBIUS</t>
+  </si>
+  <si>
+    <t>PEG17_ZEALOT</t>
+  </si>
+  <si>
+    <t>PEG17_TEMPLAR</t>
+  </si>
+  <si>
+    <t>PEG17_ARCHON</t>
+  </si>
+  <si>
+    <t>PEG17_SELENDIS</t>
+  </si>
+  <si>
+    <t>Вариация PEG17</t>
+  </si>
+  <si>
+    <t>Вариация PEG17 + PEG15</t>
   </si>
 </sst>
 </file>
@@ -5346,7 +5370,7 @@
       </c>
       <c r="L2">
         <f>COUNTIF(D:D,L1)</f>
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M2">
         <f>COUNTIF(D:D,M1)</f>
@@ -7621,82 +7645,142 @@
         <v>521</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
+        <v>524</v>
+      </c>
+      <c r="C129" s="3">
+        <v>46298</v>
+      </c>
+      <c r="D129" t="s">
+        <v>12</v>
+      </c>
+      <c r="E129" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B130" t="s">
+        <v>525</v>
+      </c>
+      <c r="C130" s="3">
+        <v>46298</v>
+      </c>
+      <c r="D130" t="s">
+        <v>12</v>
+      </c>
+      <c r="E130" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B131" t="s">
+        <v>526</v>
+      </c>
+      <c r="C131" s="3">
+        <v>46298</v>
+      </c>
+      <c r="D131" t="s">
+        <v>12</v>
+      </c>
+      <c r="E131" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B132" t="s">
+        <v>527</v>
+      </c>
+      <c r="C132" s="3">
+        <v>46298</v>
+      </c>
+      <c r="D132" t="s">
+        <v>12</v>
+      </c>
+      <c r="E132" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B133" t="s">
+        <v>528</v>
+      </c>
+      <c r="C133" s="3">
+        <v>46298</v>
+      </c>
+      <c r="D133" t="s">
+        <v>12</v>
+      </c>
+      <c r="E133" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -12733,7 +12817,7 @@
       </c>
       <c r="G2">
         <f>COUNTIF(B:B,G1)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <f>COUNTIF(B:B,H1)</f>
@@ -12931,6 +13015,15 @@
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="3">
+        <v>46298</v>
+      </c>
+      <c r="D15" t="s">
+        <v>523</v>
       </c>
       <c r="Q15" s="12"/>
     </row>

--- a/__docs/RoadMap.xlsx
+++ b/__docs/RoadMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937BE00C-AA97-4018-BF3B-00104DC9C6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E877A4D-AF6E-4D49-A41F-3D51AB9FF340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тезисы" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="532">
   <si>
     <t>RL3 - это продолжение RL1</t>
   </si>
@@ -165,9 +165,6 @@
   </si>
   <si>
     <t>Универсальный сборщик с использование fg</t>
-  </si>
-  <si>
-    <t>Где-то в гиперионе у нас вылетают заявки не в ту сторону, из-за этого он открывает по рынку.</t>
   </si>
   <si>
     <t>В спред часто встает заявка, а под ней пустота в несколько пунктов. Нужно что бы робот их обходил</t>
@@ -1659,6 +1656,12 @@
   </si>
   <si>
     <t>Вариация PEG17 + PEG15</t>
+  </si>
+  <si>
+    <t>Смарт сброс заявки может оставлять заявку на закрытие, даже если у нас нет открытой позиции. Если заявка сначала выставлялась, как заявка на открытие. А на следующем ходе, может трактоваться, как заявка на закрытие.</t>
+  </si>
+  <si>
+    <t>Если дельта заполнится, то мы не получаем стакан.</t>
   </si>
 </sst>
 </file>
@@ -5331,10 +5334,10 @@
         <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L1" t="s">
         <v>12</v>
@@ -5343,10 +5346,10 @@
         <v>11</v>
       </c>
       <c r="N1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P1" t="s">
         <v>13</v>
@@ -5426,7 +5429,7 @@
         <v>46283</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H4" t="s">
         <v>37</v>
@@ -5474,7 +5477,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C7" s="15">
         <v>46248</v>
@@ -5483,13 +5486,13 @@
         <v>11</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F7" s="15">
         <v>46267</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -5497,7 +5500,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" s="3">
         <v>46248</v>
@@ -5506,7 +5509,7 @@
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -5514,7 +5517,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" s="3">
         <v>46248</v>
@@ -5523,7 +5526,7 @@
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -5531,16 +5534,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C10" s="3">
         <v>46248</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -5548,22 +5551,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" s="15">
         <v>46248</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F11" s="15">
         <v>46286</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -5571,7 +5574,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" s="3">
         <v>46248</v>
@@ -5580,7 +5583,7 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -5588,7 +5591,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13" s="3">
         <v>46248</v>
@@ -5597,7 +5600,7 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -5605,7 +5608,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" s="3">
         <v>46248</v>
@@ -5614,7 +5617,7 @@
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -5622,7 +5625,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15" s="3">
         <v>46248</v>
@@ -5631,7 +5634,7 @@
         <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -5639,7 +5642,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C16" s="3">
         <v>46248</v>
@@ -5648,7 +5651,7 @@
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -5656,7 +5659,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C17" s="3">
         <v>46248</v>
@@ -5665,7 +5668,7 @@
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -5673,7 +5676,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C18" s="15">
         <v>46248</v>
@@ -5682,13 +5685,13 @@
         <v>11</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F18" s="15">
         <v>46267</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -5696,7 +5699,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C19" s="15">
         <v>46248</v>
@@ -5705,13 +5708,13 @@
         <v>11</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F19" s="15">
         <v>46267</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -5719,7 +5722,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C20" s="15">
         <v>46248</v>
@@ -5728,13 +5731,13 @@
         <v>11</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F20" s="15">
         <v>46267</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5742,7 +5745,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C21" s="3">
         <v>46248</v>
@@ -5751,7 +5754,7 @@
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -5759,7 +5762,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C22" s="3">
         <v>46248</v>
@@ -5768,7 +5771,7 @@
         <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -5776,7 +5779,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C23" s="3">
         <v>46248</v>
@@ -5785,7 +5788,7 @@
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -5793,7 +5796,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C24" s="3">
         <v>46248</v>
@@ -5802,7 +5805,7 @@
         <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -5810,7 +5813,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C25" s="3">
         <v>46248</v>
@@ -5819,7 +5822,7 @@
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -5827,7 +5830,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C26" s="3">
         <v>46248</v>
@@ -5836,7 +5839,7 @@
         <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -5844,7 +5847,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C27" s="3">
         <v>46248</v>
@@ -5853,7 +5856,7 @@
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -5861,7 +5864,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C28" s="3">
         <v>46248</v>
@@ -5870,7 +5873,7 @@
         <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -5878,7 +5881,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C29" s="3">
         <v>46248</v>
@@ -5887,7 +5890,7 @@
         <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -5895,16 +5898,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C30" s="3">
         <v>46248</v>
       </c>
       <c r="D30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -5912,16 +5915,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C31" s="3">
         <v>46248</v>
       </c>
       <c r="D31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E31" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -5929,16 +5932,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C32" s="3">
         <v>46248</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -5946,22 +5949,22 @@
         <v>32</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C33" s="15">
         <v>46248</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F33" s="15">
         <v>46266</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -5969,22 +5972,22 @@
         <v>33</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C34" s="15">
         <v>46248</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F34" s="15">
         <v>46286</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -5992,22 +5995,22 @@
         <v>34</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C35" s="15">
         <v>46248</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F35" s="15">
         <v>46286</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -6015,22 +6018,22 @@
         <v>35</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C36" s="15">
         <v>46248</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F36" s="15">
         <v>46286</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -6038,22 +6041,22 @@
         <v>36</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C37" s="15">
         <v>46248</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F37" s="15">
         <v>46286</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -6061,22 +6064,22 @@
         <v>37</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C38" s="15">
         <v>46248</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F38" s="15">
         <v>46294</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -6084,22 +6087,22 @@
         <v>38</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C39" s="15">
         <v>46248</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F39" s="15">
         <v>46294</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -6107,16 +6110,16 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C40" s="3">
         <v>46248</v>
       </c>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E40" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -6124,16 +6127,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C41" s="3">
         <v>46248</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -6141,16 +6144,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C42" s="3">
         <v>46248</v>
       </c>
       <c r="D42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -6158,16 +6161,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C43" s="3">
         <v>46248</v>
       </c>
       <c r="D43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E43" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -6175,16 +6178,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C44" s="3">
         <v>46248</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E44" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -6192,16 +6195,16 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C45" s="3">
         <v>46248</v>
       </c>
       <c r="D45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E45" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -6209,16 +6212,16 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C46" s="3">
         <v>46248</v>
       </c>
       <c r="D46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E46" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -6226,16 +6229,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C47" s="3">
         <v>46248</v>
       </c>
       <c r="D47" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E47" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -6243,16 +6246,16 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C48" s="3">
         <v>46248</v>
       </c>
       <c r="D48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E48" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -6260,16 +6263,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C49" s="3">
         <v>46248</v>
       </c>
       <c r="D49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E49" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -6277,16 +6280,16 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C50" s="3">
         <v>46248</v>
       </c>
       <c r="D50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E50" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -6294,16 +6297,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C51" s="3">
         <v>46248</v>
       </c>
       <c r="D51" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E51" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -6311,16 +6314,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C52" s="3">
         <v>46248</v>
       </c>
       <c r="D52" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E52" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -6328,16 +6331,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C53" s="3">
         <v>46248</v>
       </c>
       <c r="D53" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E53" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -6345,22 +6348,22 @@
         <v>53</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C54" s="15">
         <v>46248</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F54" s="15">
         <v>46294</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -6368,22 +6371,22 @@
         <v>54</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C55" s="15">
         <v>46248</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F55" s="15">
         <v>46294</v>
       </c>
       <c r="G55" s="14" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -6391,7 +6394,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C56" s="3">
         <v>46248</v>
@@ -6400,7 +6403,7 @@
         <v>11</v>
       </c>
       <c r="E56" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -6408,7 +6411,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C57" s="3">
         <v>46248</v>
@@ -6417,7 +6420,7 @@
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -6425,7 +6428,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C58" s="3">
         <v>46248</v>
@@ -6434,7 +6437,7 @@
         <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -6442,7 +6445,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C59" s="3">
         <v>46248</v>
@@ -6451,7 +6454,7 @@
         <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -6459,7 +6462,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C60" s="3">
         <v>46248</v>
@@ -6468,7 +6471,7 @@
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -6476,7 +6479,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C61" s="3">
         <v>46248</v>
@@ -6485,7 +6488,7 @@
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -6493,7 +6496,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C62" s="3">
         <v>46248</v>
@@ -6502,7 +6505,7 @@
         <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -6510,7 +6513,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C63" s="3">
         <v>46248</v>
@@ -6519,7 +6522,7 @@
         <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -6527,7 +6530,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C64" s="3">
         <v>46248</v>
@@ -6536,7 +6539,7 @@
         <v>12</v>
       </c>
       <c r="E64" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -6544,7 +6547,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C65" s="3">
         <v>46248</v>
@@ -6553,7 +6556,7 @@
         <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -6561,7 +6564,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C66" s="3">
         <v>46248</v>
@@ -6570,7 +6573,7 @@
         <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -6578,7 +6581,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C67" s="3">
         <v>46248</v>
@@ -6587,7 +6590,7 @@
         <v>12</v>
       </c>
       <c r="E67" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -6595,7 +6598,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C68" s="3">
         <v>46248</v>
@@ -6604,7 +6607,7 @@
         <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -6612,7 +6615,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C69" s="11">
         <v>46249</v>
@@ -6621,7 +6624,7 @@
         <v>12</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -6629,7 +6632,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C70" s="11">
         <v>46249</v>
@@ -6638,7 +6641,7 @@
         <v>12</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -6646,7 +6649,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C71" s="11">
         <v>46249</v>
@@ -6655,7 +6658,7 @@
         <v>12</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -6663,7 +6666,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C72" s="15">
         <v>46249</v>
@@ -6672,13 +6675,13 @@
         <v>12</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F72" s="15">
         <v>46266</v>
       </c>
       <c r="G72" s="14" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -6686,7 +6689,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C73" s="3">
         <v>46249</v>
@@ -6695,7 +6698,7 @@
         <v>12</v>
       </c>
       <c r="E73" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -6703,7 +6706,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C74" s="15">
         <v>46249</v>
@@ -6712,13 +6715,13 @@
         <v>12</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F74" s="15">
         <v>46266</v>
       </c>
       <c r="G74" s="14" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -6726,7 +6729,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C75" s="15">
         <v>46249</v>
@@ -6735,13 +6738,13 @@
         <v>12</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F75" s="15">
         <v>46266</v>
       </c>
       <c r="G75" s="14" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -6749,7 +6752,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C76" s="3">
         <v>46249</v>
@@ -6758,7 +6761,7 @@
         <v>12</v>
       </c>
       <c r="E76" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -6766,7 +6769,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C77" s="3">
         <v>46249</v>
@@ -6775,7 +6778,7 @@
         <v>12</v>
       </c>
       <c r="E77" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -6783,7 +6786,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C78" s="3">
         <v>46249</v>
@@ -6792,7 +6795,7 @@
         <v>12</v>
       </c>
       <c r="E78" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -6800,7 +6803,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C79" s="3">
         <v>46249</v>
@@ -6809,7 +6812,7 @@
         <v>12</v>
       </c>
       <c r="E79" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -6817,7 +6820,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C80" s="3">
         <v>46249</v>
@@ -6826,7 +6829,7 @@
         <v>12</v>
       </c>
       <c r="E80" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -6834,7 +6837,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C81" s="3">
         <v>46249</v>
@@ -6843,7 +6846,7 @@
         <v>12</v>
       </c>
       <c r="E81" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -6851,7 +6854,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C82" s="3">
         <v>46249</v>
@@ -6860,7 +6863,7 @@
         <v>12</v>
       </c>
       <c r="E82" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -6868,7 +6871,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C83" s="3">
         <v>46249</v>
@@ -6877,7 +6880,7 @@
         <v>12</v>
       </c>
       <c r="E83" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -6885,7 +6888,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C84" s="3">
         <v>46249</v>
@@ -6894,7 +6897,7 @@
         <v>12</v>
       </c>
       <c r="E84" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -6902,7 +6905,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C85" s="3">
         <v>46249</v>
@@ -6911,7 +6914,7 @@
         <v>12</v>
       </c>
       <c r="E85" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -6919,7 +6922,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C86" s="3">
         <v>46249</v>
@@ -6928,7 +6931,7 @@
         <v>12</v>
       </c>
       <c r="E86" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -6936,7 +6939,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C87" s="3">
         <v>46249</v>
@@ -6945,7 +6948,7 @@
         <v>12</v>
       </c>
       <c r="E87" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -6953,7 +6956,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C88" s="3">
         <v>46249</v>
@@ -6962,7 +6965,7 @@
         <v>12</v>
       </c>
       <c r="E88" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -6970,7 +6973,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C89" s="3">
         <v>46249</v>
@@ -6979,7 +6982,7 @@
         <v>12</v>
       </c>
       <c r="E89" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -6987,7 +6990,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C90" s="3">
         <v>46249</v>
@@ -6996,7 +6999,7 @@
         <v>12</v>
       </c>
       <c r="E90" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -7004,7 +7007,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C91" s="3">
         <v>46249</v>
@@ -7013,7 +7016,7 @@
         <v>13</v>
       </c>
       <c r="E91" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -7021,7 +7024,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C92" s="3">
         <v>46249</v>
@@ -7030,7 +7033,7 @@
         <v>13</v>
       </c>
       <c r="E92" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -7038,7 +7041,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C93" s="3">
         <v>46249</v>
@@ -7047,7 +7050,7 @@
         <v>13</v>
       </c>
       <c r="E93" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -7055,7 +7058,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C94" s="3">
         <v>46249</v>
@@ -7064,7 +7067,7 @@
         <v>13</v>
       </c>
       <c r="E94" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -7072,7 +7075,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C95" s="3">
         <v>46249</v>
@@ -7081,7 +7084,7 @@
         <v>13</v>
       </c>
       <c r="E95" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -7089,7 +7092,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C96" s="3">
         <v>46249</v>
@@ -7098,7 +7101,7 @@
         <v>13</v>
       </c>
       <c r="E96" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -7106,7 +7109,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C97" s="3">
         <v>46249</v>
@@ -7115,7 +7118,7 @@
         <v>13</v>
       </c>
       <c r="E97" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -7123,16 +7126,16 @@
         <v>97</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C98" s="3">
         <v>46249</v>
       </c>
       <c r="D98" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E98" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -7140,16 +7143,16 @@
         <v>98</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C99" s="3">
         <v>46249</v>
       </c>
       <c r="D99" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E99" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -7157,7 +7160,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C100" s="3">
         <v>46252</v>
@@ -7166,7 +7169,7 @@
         <v>12</v>
       </c>
       <c r="E100" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -7174,7 +7177,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C101" s="3">
         <v>46253</v>
@@ -7183,7 +7186,7 @@
         <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -7191,16 +7194,16 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C102" s="3">
         <v>46256</v>
       </c>
       <c r="D102" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E102" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -7208,7 +7211,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C103" s="3">
         <v>46266</v>
@@ -7217,7 +7220,7 @@
         <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -7225,7 +7228,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C104" s="3">
         <v>46266</v>
@@ -7234,7 +7237,7 @@
         <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -7242,7 +7245,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C105" s="3">
         <v>46266</v>
@@ -7251,7 +7254,7 @@
         <v>12</v>
       </c>
       <c r="E105" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -7259,7 +7262,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C106" s="3">
         <v>46266</v>
@@ -7268,7 +7271,7 @@
         <v>12</v>
       </c>
       <c r="E106" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -7276,7 +7279,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="16" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C107" s="3">
         <v>46266</v>
@@ -7285,7 +7288,7 @@
         <v>12</v>
       </c>
       <c r="E107" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -7293,7 +7296,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C108" s="3">
         <v>46266</v>
@@ -7302,7 +7305,7 @@
         <v>12</v>
       </c>
       <c r="E108" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -7310,7 +7313,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C109" s="3">
         <v>46267</v>
@@ -7319,7 +7322,7 @@
         <v>11</v>
       </c>
       <c r="E109" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -7327,7 +7330,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C110" s="3">
         <v>46267</v>
@@ -7336,7 +7339,7 @@
         <v>11</v>
       </c>
       <c r="E110" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -7344,7 +7347,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C111" s="3">
         <v>46267</v>
@@ -7353,7 +7356,7 @@
         <v>11</v>
       </c>
       <c r="E111" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -7361,7 +7364,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C112" s="3">
         <v>46267</v>
@@ -7370,7 +7373,7 @@
         <v>11</v>
       </c>
       <c r="E112" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -7378,16 +7381,16 @@
         <v>112</v>
       </c>
       <c r="B113" s="16" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C113" s="3">
         <v>46286</v>
       </c>
       <c r="D113" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E113" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -7395,16 +7398,16 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C114" s="3">
         <v>46290</v>
       </c>
       <c r="D114" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E114" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -7412,16 +7415,16 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C115" s="3">
         <v>46290</v>
       </c>
       <c r="D115" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E115" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -7429,16 +7432,16 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C116" s="3">
         <v>46290</v>
       </c>
       <c r="D116" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E116" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -7446,16 +7449,16 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C117" s="3">
         <v>46290</v>
       </c>
       <c r="D117" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E117" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -7463,16 +7466,16 @@
         <v>117</v>
       </c>
       <c r="B118" s="16" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C118" s="3">
         <v>46291</v>
       </c>
       <c r="D118" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E118" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -7480,16 +7483,16 @@
         <v>118</v>
       </c>
       <c r="B119" s="16" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C119" s="3">
         <v>46291</v>
       </c>
       <c r="D119" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E119" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -7497,16 +7500,16 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C120" s="3">
         <v>46291</v>
       </c>
       <c r="D120" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E120" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -7514,16 +7517,16 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C121" s="3">
         <v>46291</v>
       </c>
       <c r="D121" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E121" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -7531,16 +7534,16 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C122" s="3">
         <v>46291</v>
       </c>
       <c r="D122" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E122" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -7548,16 +7551,16 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C123" s="3">
         <v>46291</v>
       </c>
       <c r="D123" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E123" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -7565,16 +7568,16 @@
         <v>123</v>
       </c>
       <c r="B124" s="16" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C124" s="3">
         <v>46291</v>
       </c>
       <c r="D124" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E124" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -7582,16 +7585,16 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C125" s="3">
         <v>46291</v>
       </c>
       <c r="D125" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E125" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -7599,16 +7602,16 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C126" s="3">
         <v>46294</v>
       </c>
       <c r="D126" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E126" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -7616,7 +7619,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C127" s="3">
         <v>46294</v>
@@ -7625,7 +7628,7 @@
         <v>12</v>
       </c>
       <c r="E127" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -7633,7 +7636,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C128" s="3">
         <v>46297</v>
@@ -7642,7 +7645,7 @@
         <v>12</v>
       </c>
       <c r="E128" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -7650,7 +7653,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C129" s="3">
         <v>46298</v>
@@ -7659,7 +7662,7 @@
         <v>12</v>
       </c>
       <c r="E129" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -7667,7 +7670,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C130" s="3">
         <v>46298</v>
@@ -7676,7 +7679,7 @@
         <v>12</v>
       </c>
       <c r="E130" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -7684,7 +7687,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C131" s="3">
         <v>46298</v>
@@ -7693,7 +7696,7 @@
         <v>12</v>
       </c>
       <c r="E131" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -7701,7 +7704,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C132" s="3">
         <v>46298</v>
@@ -7710,7 +7713,7 @@
         <v>12</v>
       </c>
       <c r="E132" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -7718,7 +7721,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C133" s="3">
         <v>46298</v>
@@ -7727,7 +7730,7 @@
         <v>12</v>
       </c>
       <c r="E133" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -9064,7 +9067,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5C6E19E-FDB9-4B9E-B0A7-1D91E81DACEB}">
-  <dimension ref="A2:B6"/>
+  <dimension ref="A2:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -9080,7 +9083,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>430</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -9088,7 +9091,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -9096,7 +9099,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -9104,7 +9107,15 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>434</v>
+        <v>530</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -9122,22 +9133,22 @@
   <sheetData>
     <row r="2" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="33" x14ac:dyDescent="0.25">
@@ -9145,19 +9156,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>64</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>65</v>
       </c>
       <c r="F3" s="9">
         <v>46303</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9165,19 +9176,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>68</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>69</v>
       </c>
       <c r="F4" s="10">
         <v>40305</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9185,19 +9196,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>71</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>72</v>
       </c>
       <c r="F5" s="10">
         <v>40305</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9205,19 +9216,19 @@
         <v>4</v>
       </c>
       <c r="C6" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>73</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>74</v>
       </c>
       <c r="F6" s="10">
         <v>40305</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9225,19 +9236,19 @@
         <v>5</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>77</v>
       </c>
       <c r="F7" s="10">
         <v>40305</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="33" x14ac:dyDescent="0.25">
@@ -9245,19 +9256,19 @@
         <v>6</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>79</v>
       </c>
       <c r="F8" s="10">
         <v>40305</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="33" x14ac:dyDescent="0.25">
@@ -9265,19 +9276,19 @@
         <v>7</v>
       </c>
       <c r="C9" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>81</v>
       </c>
       <c r="F9" s="10">
         <v>40305</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="33" x14ac:dyDescent="0.25">
@@ -9285,19 +9296,19 @@
         <v>8</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="F10" s="10">
         <v>40305</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="33" x14ac:dyDescent="0.25">
@@ -9305,19 +9316,19 @@
         <v>9</v>
       </c>
       <c r="C11" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>85</v>
       </c>
       <c r="F11" s="10">
         <v>40305</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="33" x14ac:dyDescent="0.25">
@@ -9325,19 +9336,19 @@
         <v>10</v>
       </c>
       <c r="C12" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>87</v>
       </c>
       <c r="F12" s="10">
         <v>40305</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9345,19 +9356,19 @@
         <v>11</v>
       </c>
       <c r="C13" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="E13" s="7" t="s">
         <v>89</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>90</v>
       </c>
       <c r="F13" s="10">
         <v>40305</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9365,19 +9376,19 @@
         <v>12</v>
       </c>
       <c r="C14" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>92</v>
       </c>
       <c r="F14" s="10">
         <v>40305</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9385,19 +9396,19 @@
         <v>13</v>
       </c>
       <c r="C15" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>94</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>95</v>
       </c>
       <c r="F15" s="10">
         <v>40305</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9405,19 +9416,19 @@
         <v>14</v>
       </c>
       <c r="C16" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>96</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>97</v>
       </c>
       <c r="F16" s="9">
         <v>46302</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9425,19 +9436,19 @@
         <v>15</v>
       </c>
       <c r="C17" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>98</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>99</v>
       </c>
       <c r="F17" s="9">
         <v>46302</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9445,19 +9456,19 @@
         <v>16</v>
       </c>
       <c r="C18" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>101</v>
       </c>
       <c r="F18" s="9">
         <v>46302</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9465,19 +9476,19 @@
         <v>17</v>
       </c>
       <c r="C19" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>102</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>103</v>
       </c>
       <c r="F19" s="9">
         <v>46302</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9485,19 +9496,19 @@
         <v>18</v>
       </c>
       <c r="C20" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>104</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>105</v>
       </c>
       <c r="F20" s="9">
         <v>46302</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9505,19 +9516,19 @@
         <v>19</v>
       </c>
       <c r="C21" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>106</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>107</v>
       </c>
       <c r="F21" s="9">
         <v>46302</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9525,19 +9536,19 @@
         <v>20</v>
       </c>
       <c r="C22" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>108</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>109</v>
       </c>
       <c r="F22" s="9">
         <v>46302</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9545,19 +9556,19 @@
         <v>21</v>
       </c>
       <c r="C23" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>111</v>
       </c>
       <c r="F23" s="9">
         <v>46302</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9565,19 +9576,19 @@
         <v>22</v>
       </c>
       <c r="C24" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>112</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>113</v>
       </c>
       <c r="F24" s="10">
         <v>40305</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9585,19 +9596,19 @@
         <v>23</v>
       </c>
       <c r="C25" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>114</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>115</v>
       </c>
       <c r="F25" s="10">
         <v>40305</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9605,19 +9616,19 @@
         <v>24</v>
       </c>
       <c r="C26" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>116</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>117</v>
       </c>
       <c r="F26" s="10">
         <v>40304</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9625,19 +9636,19 @@
         <v>25</v>
       </c>
       <c r="C27" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>119</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>120</v>
       </c>
       <c r="F27" s="10">
         <v>40304</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9645,19 +9656,19 @@
         <v>26</v>
       </c>
       <c r="C28" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" s="7" t="s">
         <v>121</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>122</v>
       </c>
       <c r="F28" s="9">
         <v>46302</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9665,19 +9676,19 @@
         <v>27</v>
       </c>
       <c r="C29" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E29" s="7" t="s">
         <v>123</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>124</v>
       </c>
       <c r="F29" s="9">
         <v>46302</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="33" x14ac:dyDescent="0.25">
@@ -9685,19 +9696,19 @@
         <v>28</v>
       </c>
       <c r="C30" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" s="7" t="s">
         <v>125</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>126</v>
       </c>
       <c r="F30" s="9">
         <v>46302</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9705,19 +9716,19 @@
         <v>29</v>
       </c>
       <c r="C31" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E31" s="7" t="s">
         <v>127</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>128</v>
       </c>
       <c r="F31" s="9">
         <v>46302</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9725,19 +9736,19 @@
         <v>30</v>
       </c>
       <c r="C32" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E32" s="7" t="s">
         <v>129</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>130</v>
       </c>
       <c r="F32" s="9">
         <v>46302</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9745,19 +9756,19 @@
         <v>31</v>
       </c>
       <c r="C33" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E33" s="7" t="s">
         <v>131</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>132</v>
       </c>
       <c r="F33" s="9">
         <v>46302</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9765,19 +9776,19 @@
         <v>32</v>
       </c>
       <c r="C34" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E34" s="7" t="s">
         <v>133</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>134</v>
       </c>
       <c r="F34" s="9">
         <v>46302</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9785,19 +9796,19 @@
         <v>33</v>
       </c>
       <c r="C35" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E35" s="7" t="s">
         <v>135</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>136</v>
       </c>
       <c r="F35" s="9">
         <v>46302</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9805,19 +9816,19 @@
         <v>34</v>
       </c>
       <c r="C36" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E36" s="7" t="s">
         <v>137</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>138</v>
       </c>
       <c r="F36" s="9">
         <v>46302</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9825,19 +9836,19 @@
         <v>35</v>
       </c>
       <c r="C37" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E37" s="7" t="s">
         <v>139</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>140</v>
       </c>
       <c r="F37" s="9">
         <v>46302</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9845,19 +9856,19 @@
         <v>36</v>
       </c>
       <c r="C38" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38" s="7" t="s">
         <v>141</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>142</v>
       </c>
       <c r="F38" s="9">
         <v>46302</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9865,19 +9876,19 @@
         <v>37</v>
       </c>
       <c r="C39" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E39" s="7" t="s">
         <v>143</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>144</v>
       </c>
       <c r="F39" s="9">
         <v>46302</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9885,19 +9896,19 @@
         <v>38</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F40" s="9">
         <v>46302</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9905,19 +9916,19 @@
         <v>39</v>
       </c>
       <c r="C41" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41" s="7" t="s">
         <v>146</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>147</v>
       </c>
       <c r="F41" s="9">
         <v>46302</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9925,19 +9936,19 @@
         <v>40</v>
       </c>
       <c r="C42" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42" s="7" t="s">
         <v>148</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>149</v>
       </c>
       <c r="F42" s="9">
         <v>46302</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9945,19 +9956,19 @@
         <v>41</v>
       </c>
       <c r="C43" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E43" s="7" t="s">
         <v>150</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>151</v>
       </c>
       <c r="F43" s="9">
         <v>46302</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9965,19 +9976,19 @@
         <v>42</v>
       </c>
       <c r="C44" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E44" s="7" t="s">
         <v>152</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>153</v>
       </c>
       <c r="F44" s="9">
         <v>46302</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="45" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -9985,19 +9996,19 @@
         <v>43</v>
       </c>
       <c r="C45" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E45" s="7" t="s">
         <v>154</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>155</v>
       </c>
       <c r="F45" s="9">
         <v>46302</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10005,19 +10016,19 @@
         <v>44</v>
       </c>
       <c r="C46" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E46" s="7" t="s">
         <v>156</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>157</v>
       </c>
       <c r="F46" s="9">
         <v>46302</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10025,19 +10036,19 @@
         <v>45</v>
       </c>
       <c r="C47" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E47" s="7" t="s">
         <v>158</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>159</v>
       </c>
       <c r="F47" s="10">
         <v>40305</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10045,19 +10056,19 @@
         <v>46</v>
       </c>
       <c r="C48" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E48" s="7" t="s">
         <v>160</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>161</v>
       </c>
       <c r="F48" s="10">
         <v>40305</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49" spans="2:7" ht="33" x14ac:dyDescent="0.25">
@@ -10065,19 +10076,19 @@
         <v>47</v>
       </c>
       <c r="C49" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>162</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>163</v>
       </c>
       <c r="F49" s="10">
         <v>40305</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10085,19 +10096,19 @@
         <v>48</v>
       </c>
       <c r="C50" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E50" s="7" t="s">
         <v>164</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>165</v>
       </c>
       <c r="F50" s="10">
         <v>40305</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10105,19 +10116,19 @@
         <v>49</v>
       </c>
       <c r="C51" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E51" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>167</v>
       </c>
       <c r="F51" s="9">
         <v>46302</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="52" spans="2:7" ht="33" x14ac:dyDescent="0.25">
@@ -10125,19 +10136,19 @@
         <v>50</v>
       </c>
       <c r="C52" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E52" s="7" t="s">
         <v>168</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>169</v>
       </c>
       <c r="F52" s="10">
         <v>40305</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="53" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10145,19 +10156,19 @@
         <v>51</v>
       </c>
       <c r="C53" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E53" s="7" t="s">
         <v>170</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>171</v>
       </c>
       <c r="F53" s="10">
         <v>40305</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10165,19 +10176,19 @@
         <v>52</v>
       </c>
       <c r="C54" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E54" s="7" t="s">
         <v>172</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>173</v>
       </c>
       <c r="F54" s="10">
         <v>40305</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10185,19 +10196,19 @@
         <v>53</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F55" s="9">
         <v>46302</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10205,19 +10216,19 @@
         <v>54</v>
       </c>
       <c r="C56" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E56" s="7" t="s">
         <v>175</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>176</v>
       </c>
       <c r="F56" s="10">
         <v>40305</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="57" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10225,19 +10236,19 @@
         <v>55</v>
       </c>
       <c r="C57" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E57" s="7" t="s">
         <v>177</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>178</v>
       </c>
       <c r="F57" s="10">
         <v>40305</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10245,19 +10256,19 @@
         <v>56</v>
       </c>
       <c r="C58" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E58" s="7" t="s">
         <v>179</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>180</v>
       </c>
       <c r="F58" s="9">
         <v>46302</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="2:7" ht="33" x14ac:dyDescent="0.25">
@@ -10265,19 +10276,19 @@
         <v>57</v>
       </c>
       <c r="C59" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E59" s="7" t="s">
         <v>181</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>182</v>
       </c>
       <c r="F59" s="9">
         <v>46302</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10285,19 +10296,19 @@
         <v>58</v>
       </c>
       <c r="C60" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E60" s="7" t="s">
         <v>183</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>184</v>
       </c>
       <c r="F60" s="10">
         <v>40305</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="61" spans="2:7" ht="33" x14ac:dyDescent="0.25">
@@ -10305,19 +10316,19 @@
         <v>59</v>
       </c>
       <c r="C61" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E61" s="7" t="s">
         <v>185</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>186</v>
       </c>
       <c r="F61" s="10">
         <v>40305</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10325,19 +10336,19 @@
         <v>60</v>
       </c>
       <c r="C62" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D62" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D62" s="7" t="s">
+      <c r="E62" s="7" t="s">
         <v>188</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>189</v>
       </c>
       <c r="F62" s="10">
         <v>40305</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10345,19 +10356,19 @@
         <v>61</v>
       </c>
       <c r="C63" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="E63" s="7" t="s">
         <v>190</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>191</v>
       </c>
       <c r="F63" s="10">
         <v>40305</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="64" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10365,19 +10376,19 @@
         <v>62</v>
       </c>
       <c r="C64" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="E64" s="7" t="s">
         <v>192</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>193</v>
       </c>
       <c r="F64" s="9">
         <v>46302</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10385,19 +10396,19 @@
         <v>63</v>
       </c>
       <c r="C65" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D65" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="E65" s="7" t="s">
         <v>195</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>196</v>
       </c>
       <c r="F65" s="10">
         <v>40305</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10405,19 +10416,19 @@
         <v>64</v>
       </c>
       <c r="C66" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="E66" s="7" t="s">
         <v>197</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>198</v>
       </c>
       <c r="F66" s="10">
         <v>40305</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10425,16 +10436,16 @@
         <v>65</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E67" s="10">
         <v>40305</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10442,16 +10453,16 @@
         <v>66</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E68" s="9">
         <v>46302</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10459,16 +10470,16 @@
         <v>67</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E69" s="9">
         <v>46302</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10476,16 +10487,16 @@
         <v>68</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E70" s="9">
         <v>46302</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10493,16 +10504,16 @@
         <v>69</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E71" s="9">
         <v>46302</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="72" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10510,16 +10521,16 @@
         <v>70</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E72" s="10">
         <v>40304</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="73" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10527,16 +10538,16 @@
         <v>71</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E73" s="10">
         <v>40304</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="74" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10544,16 +10555,16 @@
         <v>72</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E74" s="10">
         <v>40304</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="75" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10561,16 +10572,16 @@
         <v>73</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E75" s="10">
         <v>40304</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="76" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10578,16 +10589,16 @@
         <v>74</v>
       </c>
       <c r="C76" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="D76" s="7" t="s">
         <v>207</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>208</v>
       </c>
       <c r="E76" s="9">
         <v>46302</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="77" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10595,16 +10606,16 @@
         <v>75</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E77" s="9">
         <v>46302</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="78" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10612,16 +10623,16 @@
         <v>76</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E78" s="10">
         <v>40304</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="79" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10629,16 +10640,16 @@
         <v>77</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E79" s="10">
         <v>40304</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="80" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -10646,16 +10657,16 @@
         <v>78</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E80" s="10">
         <v>40304</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="81" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -10663,16 +10674,16 @@
         <v>79</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E81" s="9">
         <v>46302</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="82" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -10680,16 +10691,16 @@
         <v>80</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E82" s="9">
         <v>46302</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="83" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -10697,16 +10708,16 @@
         <v>81</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E83" s="10">
         <v>40304</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="84" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -10714,16 +10725,16 @@
         <v>82</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E84" s="10">
         <v>40304</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="85" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -10731,16 +10742,16 @@
         <v>83</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E85" s="9">
         <v>46302</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="86" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -10748,16 +10759,16 @@
         <v>84</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E86" s="10">
         <v>40304</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="87" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -10765,16 +10776,16 @@
         <v>85</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E87" s="10">
         <v>40304</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="88" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -10782,16 +10793,16 @@
         <v>86</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E88" s="10">
         <v>40304</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="89" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -10799,16 +10810,16 @@
         <v>87</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E89" s="9">
         <v>46301</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="90" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -10816,16 +10827,16 @@
         <v>88</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E90" s="10">
         <v>40304</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="91" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -10833,16 +10844,16 @@
         <v>89</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E91" s="10">
         <v>40304</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="92" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -10850,16 +10861,16 @@
         <v>90</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E92" s="10">
         <v>40304</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="93" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -10867,16 +10878,16 @@
         <v>91</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E93" s="10">
         <v>40304</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="94" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -10884,16 +10895,16 @@
         <v>92</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E94" s="10">
         <v>40304</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="95" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -10901,16 +10912,16 @@
         <v>93</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E95" s="10">
         <v>40304</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="96" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -10918,16 +10929,16 @@
         <v>94</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E96" s="10">
         <v>40304</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="97" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -10935,16 +10946,16 @@
         <v>95</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E97" s="10">
         <v>40304</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="98" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -10952,16 +10963,16 @@
         <v>96</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E98" s="10">
         <v>40304</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="99" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -10969,16 +10980,16 @@
         <v>97</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E99" s="10">
         <v>40304</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="100" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -10986,16 +10997,16 @@
         <v>98</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E100" s="10">
         <v>40304</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="101" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11003,16 +11014,16 @@
         <v>99</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E101" s="10">
         <v>40304</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="102" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11020,16 +11031,16 @@
         <v>100</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E102" s="10">
         <v>40304</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="103" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11037,16 +11048,16 @@
         <v>101</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E103" s="9">
         <v>46302</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="104" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11054,16 +11065,16 @@
         <v>102</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E104" s="10">
         <v>40304</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="105" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11071,16 +11082,16 @@
         <v>103</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E105" s="9">
         <v>46302</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="106" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11088,16 +11099,16 @@
         <v>104</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E106" s="9">
         <v>46302</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="107" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11105,16 +11116,16 @@
         <v>105</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E107" s="9">
         <v>46302</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="108" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11122,16 +11133,16 @@
         <v>106</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E108" s="9">
         <v>46302</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="109" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11139,16 +11150,16 @@
         <v>107</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E109" s="9">
         <v>46302</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="110" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11156,16 +11167,16 @@
         <v>108</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E110" s="9">
         <v>46302</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="111" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11173,16 +11184,16 @@
         <v>109</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E111" s="10">
         <v>40303</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="112" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11190,16 +11201,16 @@
         <v>110</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E112" s="10">
         <v>40304</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="113" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11207,16 +11218,16 @@
         <v>111</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E113" s="10">
         <v>40303</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="114" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11224,16 +11235,16 @@
         <v>112</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E114" s="9">
         <v>46301</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="115" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11241,16 +11252,16 @@
         <v>113</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E115" s="9">
         <v>46301</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="116" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11258,16 +11269,16 @@
         <v>114</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E116" s="10">
         <v>40303</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11275,16 +11286,16 @@
         <v>115</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E117" s="9">
         <v>46300</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="118" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11292,16 +11303,16 @@
         <v>116</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E118" s="9">
         <v>46301</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="119" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11309,16 +11320,16 @@
         <v>117</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E119" s="9">
         <v>46300</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="120" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11326,16 +11337,16 @@
         <v>118</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E120" s="9">
         <v>46300</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="121" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11343,16 +11354,16 @@
         <v>119</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E121" s="9">
         <v>46300</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="122" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11360,16 +11371,16 @@
         <v>120</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D122" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E122" s="10">
         <v>40304</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="123" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11377,16 +11388,16 @@
         <v>121</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E123" s="9">
         <v>46301</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="124" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11394,16 +11405,16 @@
         <v>122</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E124" s="9">
         <v>46301</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="125" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11411,16 +11422,16 @@
         <v>123</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E125" s="10">
         <v>40303</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="126" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11428,16 +11439,16 @@
         <v>124</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D126" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E126" s="9">
         <v>46300</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="127" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11445,16 +11456,16 @@
         <v>125</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E127" s="10">
         <v>40303</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="128" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11462,16 +11473,16 @@
         <v>126</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E128" s="9">
         <v>46301</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="129" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11479,16 +11490,16 @@
         <v>127</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D129" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E129" s="9">
         <v>46301</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="130" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11496,16 +11507,16 @@
         <v>128</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D130" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E130" s="9">
         <v>46300</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="131" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11513,16 +11524,16 @@
         <v>129</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E131" s="10">
         <v>40303</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="132" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11530,16 +11541,16 @@
         <v>130</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E132" s="10">
         <v>40303</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="133" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11547,16 +11558,16 @@
         <v>131</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D133" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E133" s="10">
         <v>40303</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="134" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11564,16 +11575,16 @@
         <v>132</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D134" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E134" s="9">
         <v>46301</v>
       </c>
       <c r="F134" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="135" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11581,16 +11592,16 @@
         <v>133</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D135" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E135" s="9">
         <v>46301</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="136" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11598,16 +11609,16 @@
         <v>134</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E136" s="9">
         <v>46301</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="137" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11615,16 +11626,16 @@
         <v>135</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E137" s="10">
         <v>40303</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="138" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11632,16 +11643,16 @@
         <v>136</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D138" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E138" s="10">
         <v>40303</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="139" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11649,16 +11660,16 @@
         <v>137</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D139" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E139" s="10">
         <v>40303</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="140" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11666,16 +11677,16 @@
         <v>138</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E140" s="9">
         <v>46301</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="141" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11683,16 +11694,16 @@
         <v>139</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E141" s="9">
         <v>46301</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="142" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11700,16 +11711,16 @@
         <v>140</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D142" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E142" s="9">
         <v>46301</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="143" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11717,16 +11728,16 @@
         <v>141</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D143" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E143" s="9">
         <v>46300</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="144" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11734,16 +11745,16 @@
         <v>142</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D144" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E144" s="9">
         <v>46301</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="145" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11751,16 +11762,16 @@
         <v>143</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E145" s="9">
         <v>46301</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="146" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11768,16 +11779,16 @@
         <v>144</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D146" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E146" s="10">
         <v>40304</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="147" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11785,16 +11796,16 @@
         <v>145</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E147" s="10">
         <v>40304</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="148" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11802,16 +11813,16 @@
         <v>146</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D148" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E148" s="10">
         <v>40304</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="149" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11819,16 +11830,16 @@
         <v>147</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E149" s="10">
         <v>40304</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="150" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11836,16 +11847,16 @@
         <v>148</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D150" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E150" s="9">
         <v>46301</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="151" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11853,16 +11864,16 @@
         <v>149</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E151" s="9">
         <v>46302</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="152" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11870,16 +11881,16 @@
         <v>150</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D152" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E152" s="10">
         <v>40304</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="153" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11887,16 +11898,16 @@
         <v>151</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E153" s="10">
         <v>40304</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="154" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11904,16 +11915,16 @@
         <v>152</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D154" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E154" s="10">
         <v>40304</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="155" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11921,16 +11932,16 @@
         <v>153</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E155" s="9">
         <v>46299</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="156" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11938,16 +11949,16 @@
         <v>154</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D156" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E156" s="10">
         <v>40301</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="157" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11955,16 +11966,16 @@
         <v>155</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D157" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E157" s="10">
         <v>40302</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="158" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11972,16 +11983,16 @@
         <v>156</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D158" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E158" s="9">
         <v>46299</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="159" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -11989,16 +12000,16 @@
         <v>157</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D159" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E159" s="9">
         <v>46299</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="160" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -12006,16 +12017,16 @@
         <v>158</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D160" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E160" s="9">
         <v>46297</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="161" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -12023,16 +12034,16 @@
         <v>159</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E161" s="9">
         <v>46299</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="162" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -12040,16 +12051,16 @@
         <v>160</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E162" s="9">
         <v>46300</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="163" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -12057,16 +12068,16 @@
         <v>161</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E163" s="9">
         <v>46299</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="164" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -12074,16 +12085,16 @@
         <v>162</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D164" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E164" s="9">
         <v>46299</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="165" spans="2:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -12091,44 +12102,44 @@
         <v>163</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D165" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E165" s="10">
         <v>40304</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="179" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B179" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C179" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="D179" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="D179" s="6" t="s">
+      <c r="E179" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="E179" s="6" t="s">
+      <c r="F179" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="F179" s="6" t="s">
+      <c r="G179" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="G179" s="6" t="s">
+      <c r="H179" s="6" t="s">
         <v>365</v>
-      </c>
-      <c r="H179" s="6" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="180" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B180" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C180" s="7">
         <v>9</v>
@@ -12151,7 +12162,7 @@
     </row>
     <row r="181" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B181" s="8" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C181" s="7">
         <v>9</v>
@@ -12174,7 +12185,7 @@
     </row>
     <row r="182" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B182" s="8" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C182" s="7">
         <v>9</v>
@@ -12197,7 +12208,7 @@
     </row>
     <row r="183" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B183" s="8" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C183" s="7">
         <v>8</v>
@@ -12220,7 +12231,7 @@
     </row>
     <row r="184" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B184" s="8" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C184" s="7">
         <v>8</v>
@@ -12243,7 +12254,7 @@
     </row>
     <row r="185" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B185" s="8" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C185" s="7">
         <v>7</v>
@@ -12266,7 +12277,7 @@
     </row>
     <row r="186" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B186" s="8" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C186" s="7">
         <v>7</v>
@@ -12289,7 +12300,7 @@
     </row>
     <row r="187" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B187" s="8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C187" s="7">
         <v>8</v>
@@ -12312,7 +12323,7 @@
     </row>
     <row r="188" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B188" s="8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C188" s="7">
         <v>8</v>
@@ -12335,7 +12346,7 @@
     </row>
     <row r="189" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B189" s="8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C189" s="7">
         <v>7</v>
@@ -12358,7 +12369,7 @@
     </row>
     <row r="190" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B190" s="8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C190" s="7">
         <v>6</v>
@@ -12381,7 +12392,7 @@
     </row>
     <row r="191" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B191" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C191" s="7">
         <v>6</v>
@@ -12404,7 +12415,7 @@
     </row>
     <row r="192" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B192" s="8" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C192" s="7">
         <v>7</v>
@@ -12427,7 +12438,7 @@
     </row>
     <row r="193" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B193" s="8" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C193" s="7">
         <v>6</v>
@@ -12450,7 +12461,7 @@
     </row>
     <row r="194" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B194" s="8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C194" s="7">
         <v>5</v>
@@ -12473,7 +12484,7 @@
     </row>
     <row r="195" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B195" s="8" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C195" s="7">
         <v>6</v>
@@ -12496,7 +12507,7 @@
     </row>
     <row r="196" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B196" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C196" s="7">
         <v>6</v>
@@ -12519,7 +12530,7 @@
     </row>
     <row r="197" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B197" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C197" s="7">
         <v>5</v>
@@ -12542,7 +12553,7 @@
     </row>
     <row r="198" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B198" s="8" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C198" s="7">
         <v>5</v>
@@ -12565,7 +12576,7 @@
     </row>
     <row r="199" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B199" s="8" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C199" s="7">
         <v>4</v>
@@ -12588,16 +12599,16 @@
     </row>
     <row r="202" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B202" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C202" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C202" s="6" t="s">
-        <v>58</v>
-      </c>
       <c r="D202" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="E202" s="6" t="s">
         <v>387</v>
-      </c>
-      <c r="E202" s="6" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="203" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
@@ -12605,13 +12616,13 @@
         <v>1</v>
       </c>
       <c r="C203" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D203" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E203" s="7" t="s">
         <v>389</v>
-      </c>
-      <c r="E203" s="7" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="204" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
@@ -12619,13 +12630,13 @@
         <v>2</v>
       </c>
       <c r="C204" s="8" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D204" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="E204" s="7" t="s">
         <v>391</v>
-      </c>
-      <c r="E204" s="7" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="205" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
@@ -12633,13 +12644,13 @@
         <v>3</v>
       </c>
       <c r="C205" s="8" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D205" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="206" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
@@ -12647,13 +12658,13 @@
         <v>4</v>
       </c>
       <c r="C206" s="8" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D206" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E206" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="207" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
@@ -12661,13 +12672,13 @@
         <v>5</v>
       </c>
       <c r="C207" s="8" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D207" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E207" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="208" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
@@ -12675,13 +12686,13 @@
         <v>6</v>
       </c>
       <c r="C208" s="8" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D208" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E208" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="209" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
@@ -12689,13 +12700,13 @@
         <v>7</v>
       </c>
       <c r="C209" s="8" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D209" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E209" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="210" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
@@ -12703,13 +12714,13 @@
         <v>8</v>
       </c>
       <c r="C210" s="8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D210" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E210" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="211" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
@@ -12717,13 +12728,13 @@
         <v>9</v>
       </c>
       <c r="C211" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D211" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E211" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="212" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
@@ -12731,13 +12742,13 @@
         <v>10</v>
       </c>
       <c r="C212" s="8" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D212" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E212" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="213" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
@@ -12745,13 +12756,13 @@
         <v>11</v>
       </c>
       <c r="C213" s="8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D213" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E213" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -12774,7 +12785,7 @@
         <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F1" t="s">
         <v>28</v>
@@ -12786,16 +12797,16 @@
         <v>11</v>
       </c>
       <c r="I1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s">
         <v>13</v>
       </c>
       <c r="L1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -12809,7 +12820,7 @@
         <v>46266</v>
       </c>
       <c r="D2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F2">
         <f>COUNTIF(B:B,F1)</f>
@@ -12851,7 +12862,7 @@
         <v>46267</v>
       </c>
       <c r="D3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -12859,13 +12870,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C4" s="3">
         <v>46269</v>
       </c>
       <c r="D4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -12879,7 +12890,7 @@
         <v>46283</v>
       </c>
       <c r="D5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -12893,7 +12904,7 @@
         <v>46286</v>
       </c>
       <c r="D6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -12907,7 +12918,7 @@
         <v>46287</v>
       </c>
       <c r="D7" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -12921,7 +12932,7 @@
         <v>46288</v>
       </c>
       <c r="D8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -12929,13 +12940,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C9" s="3">
         <v>46290</v>
       </c>
       <c r="D9" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -12943,13 +12954,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C10" s="3">
         <v>46291</v>
       </c>
       <c r="D10" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -12957,13 +12968,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C11" s="3">
         <v>46292</v>
       </c>
       <c r="D11" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="Q11" s="12"/>
     </row>
@@ -12978,7 +12989,7 @@
         <v>46294</v>
       </c>
       <c r="D12" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="Q12" s="12"/>
     </row>
@@ -12987,13 +12998,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C13" s="3">
         <v>46295</v>
       </c>
       <c r="D13" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="Q13" s="12"/>
     </row>
@@ -13008,7 +13019,7 @@
         <v>46297</v>
       </c>
       <c r="D14" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="Q14" s="12"/>
     </row>
@@ -13023,7 +13034,7 @@
         <v>46298</v>
       </c>
       <c r="D15" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="Q15" s="12"/>
     </row>
@@ -14677,10 +14688,10 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -14691,22 +14702,22 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C3" t="s">
+        <v>473</v>
+      </c>
+      <c r="D3" t="s">
+        <v>473</v>
+      </c>
+      <c r="E3" t="s">
         <v>474</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
+        <v>473</v>
+      </c>
+      <c r="G3" t="s">
         <v>474</v>
-      </c>
-      <c r="E3" t="s">
-        <v>475</v>
-      </c>
-      <c r="F3" t="s">
-        <v>474</v>
-      </c>
-      <c r="G3" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -14714,22 +14725,22 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C4" t="s">
+        <v>474</v>
+      </c>
+      <c r="D4" t="s">
+        <v>474</v>
+      </c>
+      <c r="E4" t="s">
         <v>475</v>
       </c>
-      <c r="D4" t="s">
-        <v>475</v>
-      </c>
-      <c r="E4" t="s">
-        <v>476</v>
-      </c>
       <c r="F4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -14737,19 +14748,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C5" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E5" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F5" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="G5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -14757,16 +14768,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -14774,7 +14785,7 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -14782,7 +14793,7 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">

--- a/__docs/RoadMap.xlsx
+++ b/__docs/RoadMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E877A4D-AF6E-4D49-A41F-3D51AB9FF340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33EFEB21-599D-470A-8F92-99B8357DB8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тезисы" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="533">
   <si>
     <t>RL3 - это продолжение RL1</t>
   </si>
@@ -1662,6 +1662,9 @@
   </si>
   <si>
     <t>Если дельта заполнится, то мы не получаем стакан.</t>
+  </si>
+  <si>
+    <t>Работа с OrderCords</t>
   </si>
 </sst>
 </file>
@@ -12824,7 +12827,7 @@
       </c>
       <c r="F2">
         <f>COUNTIF(B:B,F1)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2">
         <f>COUNTIF(B:B,G1)</f>
@@ -13041,6 +13044,15 @@
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="3">
+        <v>46297</v>
+      </c>
+      <c r="D16" t="s">
+        <v>532</v>
       </c>
       <c r="Q16" s="12"/>
     </row>

--- a/__docs/RoadMap.xlsx
+++ b/__docs/RoadMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33EFEB21-599D-470A-8F92-99B8357DB8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6F2C6B-DB0D-403D-B391-F2B3B939D77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тезисы" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="540">
   <si>
     <t>RL3 - это продолжение RL1</t>
   </si>
@@ -1665,6 +1665,27 @@
   </si>
   <si>
     <t>Работа с OrderCords</t>
+  </si>
+  <si>
+    <t>Разработка новых WEG</t>
+  </si>
+  <si>
+    <t>Изменненый RAT</t>
+  </si>
+  <si>
+    <t>Mcfly</t>
+  </si>
+  <si>
+    <t>Vanga and  McFly</t>
+  </si>
+  <si>
+    <t>WEG7_PARADOX2</t>
+  </si>
+  <si>
+    <t>Изменный PARADOX</t>
+  </si>
+  <si>
+    <t>WEG8_MOUSE</t>
   </si>
 </sst>
 </file>
@@ -1757,7 +1778,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1791,6 +1812,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2127,7 +2149,7 @@
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="18" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -2135,13 +2157,13 @@
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="17"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -2149,43 +2171,43 @@
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="17"/>
+      <c r="B6" s="18"/>
       <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="17"/>
+      <c r="B7" s="18"/>
       <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="17"/>
+      <c r="B8" s="18"/>
       <c r="C8" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="17"/>
+      <c r="B9" s="18"/>
       <c r="C9" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="17"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="17"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="17"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="2" t="s">
         <v>17</v>
       </c>
@@ -5384,7 +5406,7 @@
       </c>
       <c r="N2">
         <f>COUNTIF(D:D,N1)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O2">
         <f>COUNTIF(D:D,O1)</f>
@@ -5798,7 +5820,7 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="17" t="s">
         <v>312</v>
       </c>
       <c r="C24" s="3">
@@ -5914,37 +5936,49 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31">
+      <c r="A31" s="14">
         <v>30</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="15">
         <v>46248</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="14" t="s">
         <v>431</v>
       </c>
+      <c r="F31" s="15">
+        <v>46302</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>535</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32">
+      <c r="A32" s="14">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="15">
         <v>46248</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="14" t="s">
         <v>43</v>
+      </c>
+      <c r="F32" s="15">
+        <v>46302</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -7107,7 +7141,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -7124,41 +7158,53 @@
         <v>43</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="14">
         <v>97</v>
       </c>
-      <c r="B98" s="5" t="s">
+      <c r="B98" s="14" t="s">
         <v>427</v>
       </c>
-      <c r="C98" s="3">
+      <c r="C98" s="15">
         <v>46249</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E98" s="14" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99">
+      <c r="F98" s="15">
+        <v>46302</v>
+      </c>
+      <c r="G98" s="14" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="14">
         <v>98</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B99" s="14" t="s">
         <v>428</v>
       </c>
-      <c r="C99" s="3">
+      <c r="C99" s="15">
         <v>46249</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D99" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E99" s="14" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F99" s="15">
+        <v>46302</v>
+      </c>
+      <c r="G99" s="14" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -7175,7 +7221,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -7192,7 +7238,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -7209,7 +7255,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -7226,7 +7272,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -7243,7 +7289,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -7260,7 +7306,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -7277,11 +7323,11 @@
         <v>439</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
-      <c r="B107" s="16" t="s">
+      <c r="B107" s="17" t="s">
         <v>446</v>
       </c>
       <c r="C107" s="3">
@@ -7294,7 +7340,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -7311,7 +7357,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -7328,7 +7374,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -7345,7 +7391,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -7362,7 +7408,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -7383,7 +7429,7 @@
       <c r="A113">
         <v>112</v>
       </c>
-      <c r="B113" s="16" t="s">
+      <c r="B113" s="17" t="s">
         <v>464</v>
       </c>
       <c r="C113" s="3">
@@ -7740,10 +7786,34 @@
       <c r="A134">
         <v>133</v>
       </c>
+      <c r="B134" t="s">
+        <v>539</v>
+      </c>
+      <c r="C134" s="3">
+        <v>46302</v>
+      </c>
+      <c r="D134" t="s">
+        <v>47</v>
+      </c>
+      <c r="E134" t="s">
+        <v>534</v>
+      </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>537</v>
+      </c>
+      <c r="C135" s="3">
+        <v>46302</v>
+      </c>
+      <c r="D135" t="s">
+        <v>47</v>
+      </c>
+      <c r="E135" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -12827,7 +12897,7 @@
       </c>
       <c r="F2">
         <f>COUNTIF(B:B,F1)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2">
         <f>COUNTIF(B:B,G1)</f>
@@ -12843,7 +12913,7 @@
       </c>
       <c r="J2">
         <f>COUNTIF(B:B,J1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <f>COUNTIF(B:B,K1)</f>
@@ -13060,11 +13130,29 @@
       <c r="A17">
         <v>16</v>
       </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="3">
+        <v>46301</v>
+      </c>
+      <c r="D17" t="s">
+        <v>532</v>
+      </c>
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="3">
+        <v>46302</v>
+      </c>
+      <c r="D18" t="s">
+        <v>533</v>
       </c>
       <c r="Q18" s="12"/>
     </row>

--- a/__docs/RoadMap.xlsx
+++ b/__docs/RoadMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6F2C6B-DB0D-403D-B391-F2B3B939D77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32469AD4-C4CE-4CA7-AD1E-284D4B81EF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тезисы" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="541">
   <si>
     <t>RL3 - это продолжение RL1</t>
   </si>
@@ -1686,6 +1686,9 @@
   </si>
   <si>
     <t>WEG8_MOUSE</t>
+  </si>
+  <si>
+    <t>Нужны пробойные роботы</t>
   </si>
 </sst>
 </file>
@@ -9140,7 +9143,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5C6E19E-FDB9-4B9E-B0A7-1D91E81DACEB}">
-  <dimension ref="A2:B7"/>
+  <dimension ref="A2:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -9189,6 +9192,14 @@
       </c>
       <c r="B7" t="s">
         <v>531</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>540</v>
       </c>
     </row>
   </sheetData>

--- a/__docs/RoadMap.xlsx
+++ b/__docs/RoadMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32469AD4-C4CE-4CA7-AD1E-284D4B81EF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332D2BB8-BE3B-40CC-BE61-970004360FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тезисы" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="564">
   <si>
     <t>RL3 - это продолжение RL1</t>
   </si>
@@ -1689,6 +1689,75 @@
   </si>
   <si>
     <t>Нужны пробойные роботы</t>
+  </si>
+  <si>
+    <t>PEG4_U4</t>
+  </si>
+  <si>
+    <t>PEG4_U5</t>
+  </si>
+  <si>
+    <t>PEG4_U6</t>
+  </si>
+  <si>
+    <t>Новая версия универсала с фиксириванными порогами</t>
+  </si>
+  <si>
+    <t>Новая версия универсала с адаптивными порогами</t>
+  </si>
+  <si>
+    <t>Новая версия универсала с фп и фильтрацией по велкро</t>
+  </si>
+  <si>
+    <t>PEG11_RAYMIYAMOTO</t>
+  </si>
+  <si>
+    <t>PEG11_SAYATAKAGI</t>
+  </si>
+  <si>
+    <t>PEG11_ALICEMARASATO</t>
+  </si>
+  <si>
+    <t>PEG11_SHIZUKAMARIKAWA</t>
+  </si>
+  <si>
+    <t>Разработка новых PEG4, PEG11, PEG13, PEG14</t>
+  </si>
+  <si>
+    <t>PEG14_REGAL</t>
+  </si>
+  <si>
+    <t>PEG13_DUNE</t>
+  </si>
+  <si>
+    <t>Динамический трехнаправленный сброщик</t>
+  </si>
+  <si>
+    <t>Улучшенная версия PEG14_RWDDCr</t>
+  </si>
+  <si>
+    <t>Робот на add_kusuruken_bb с работой на откате</t>
+  </si>
+  <si>
+    <t>Робот на add_kusuruken_bb только закрытия в тренде</t>
+  </si>
+  <si>
+    <t>Робот на add_kusuruken_bb пробой малого канала</t>
+  </si>
+  <si>
+    <t>Робот на add_kusuruken_bb пмк с выбором направления</t>
+  </si>
+  <si>
+    <t>UEG6_SURVIVALIST</t>
+  </si>
+  <si>
+    <t>UEG6_ADVENTURE с буфером и rsi</t>
+  </si>
+  <si>
+    <t>UEG9_POLITICIAN</t>
+  </si>
+  <si>
+    <t>UEG9_GRAVY2 без стопа и с rsi</t>
   </si>
 </sst>
 </file>
@@ -5339,7 +5408,7 @@
   <dimension ref="A1:P398"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.5703125" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="7.28515625" customWidth="1"/>
     <col min="5" max="5" width="55" customWidth="1"/>
@@ -5401,7 +5470,7 @@
       </c>
       <c r="L2">
         <f>COUNTIF(D:D,L1)</f>
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="M2">
         <f>COUNTIF(D:D,M1)</f>
@@ -5413,7 +5482,7 @@
       </c>
       <c r="O2">
         <f>COUNTIF(D:D,O1)</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P2">
         <f>COUNTIF(D:D,P1)</f>
@@ -6447,54 +6516,72 @@
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57">
+      <c r="A57" s="14">
         <v>56</v>
       </c>
-      <c r="B57" s="16" t="s">
+      <c r="B57" s="14" t="s">
         <v>345</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C57" s="15">
         <v>46248</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="14" t="s">
         <v>43</v>
       </c>
+      <c r="F57" s="15">
+        <v>46305</v>
+      </c>
+      <c r="G57" s="14" t="s">
+        <v>465</v>
+      </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58">
+      <c r="A58" s="14">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="14" t="s">
         <v>346</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C58" s="15">
         <v>46248</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="14" t="s">
         <v>43</v>
       </c>
+      <c r="F58" s="15">
+        <v>46305</v>
+      </c>
+      <c r="G58" s="14" t="s">
+        <v>465</v>
+      </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59">
+      <c r="A59" s="14">
         <v>58</v>
       </c>
-      <c r="B59" s="16" t="s">
+      <c r="B59" s="14" t="s">
         <v>347</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="15">
         <v>46248</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="14" t="s">
         <v>431</v>
+      </c>
+      <c r="F59" s="15">
+        <v>46305</v>
+      </c>
+      <c r="G59" s="14" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -7823,123 +7910,255 @@
       <c r="A136">
         <v>135</v>
       </c>
+      <c r="B136" t="s">
+        <v>541</v>
+      </c>
+      <c r="C136" s="3">
+        <v>46305</v>
+      </c>
+      <c r="D136" t="s">
+        <v>12</v>
+      </c>
+      <c r="E136" t="s">
+        <v>545</v>
+      </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
+      <c r="B137" t="s">
+        <v>542</v>
+      </c>
+      <c r="C137" s="3">
+        <v>46305</v>
+      </c>
+      <c r="D137" t="s">
+        <v>12</v>
+      </c>
+      <c r="E137" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
+      <c r="B138" t="s">
+        <v>543</v>
+      </c>
+      <c r="C138" s="3">
+        <v>46305</v>
+      </c>
+      <c r="D138" t="s">
+        <v>12</v>
+      </c>
+      <c r="E138" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
+      <c r="B139" t="s">
+        <v>547</v>
+      </c>
+      <c r="C139" s="3">
+        <v>46305</v>
+      </c>
+      <c r="D139" t="s">
+        <v>12</v>
+      </c>
+      <c r="E139" t="s">
+        <v>556</v>
+      </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
+      <c r="B140" t="s">
+        <v>548</v>
+      </c>
+      <c r="C140" s="3">
+        <v>46305</v>
+      </c>
+      <c r="D140" t="s">
+        <v>12</v>
+      </c>
+      <c r="E140" t="s">
+        <v>558</v>
+      </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
+      <c r="B141" t="s">
+        <v>549</v>
+      </c>
+      <c r="C141" s="3">
+        <v>46305</v>
+      </c>
+      <c r="D141" t="s">
+        <v>12</v>
+      </c>
+      <c r="E141" t="s">
+        <v>559</v>
+      </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
+      <c r="B142" t="s">
+        <v>550</v>
+      </c>
+      <c r="C142" s="3">
+        <v>46305</v>
+      </c>
+      <c r="D142" t="s">
+        <v>12</v>
+      </c>
+      <c r="E142" t="s">
+        <v>557</v>
+      </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
+      <c r="B143" t="s">
+        <v>552</v>
+      </c>
+      <c r="C143" s="3">
+        <v>46305</v>
+      </c>
+      <c r="D143" t="s">
+        <v>12</v>
+      </c>
+      <c r="E143" t="s">
+        <v>555</v>
+      </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B144" t="s">
+        <v>553</v>
+      </c>
+      <c r="C144" s="3">
+        <v>46305</v>
+      </c>
+      <c r="D144" t="s">
+        <v>12</v>
+      </c>
+      <c r="E144" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B145" t="s">
+        <v>560</v>
+      </c>
+      <c r="C145" s="3">
+        <v>46306</v>
+      </c>
+      <c r="D145" t="s">
+        <v>49</v>
+      </c>
+      <c r="E145" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B146" t="s">
+        <v>562</v>
+      </c>
+      <c r="C146" s="3">
+        <v>46306</v>
+      </c>
+      <c r="D146" t="s">
+        <v>49</v>
+      </c>
+      <c r="E146" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
@@ -12912,7 +13131,7 @@
       </c>
       <c r="G2">
         <f>COUNTIF(B:B,G1)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <f>COUNTIF(B:B,H1)</f>
@@ -13170,6 +13389,15 @@
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="3">
+        <v>46305</v>
+      </c>
+      <c r="D19" t="s">
+        <v>551</v>
       </c>
       <c r="Q19" s="12"/>
     </row>

--- a/__docs/RoadMap.xlsx
+++ b/__docs/RoadMap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332D2BB8-BE3B-40CC-BE61-970004360FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4872A07-C9FD-483A-BA35-93D419DE73EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="566">
   <si>
     <t>RL3 - это продолжение RL1</t>
   </si>
@@ -1758,6 +1758,12 @@
   </si>
   <si>
     <t>UEG9_GRAVY2 без стопа и с rsi</t>
+  </si>
+  <si>
+    <t>SEGML2_TUNNELER</t>
+  </si>
+  <si>
+    <t>Отбой от буффера линейной регрессии в окне</t>
   </si>
 </sst>
 </file>
@@ -5486,7 +5492,7 @@
       </c>
       <c r="P2">
         <f>COUNTIF(D:D,P1)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -8096,6 +8102,18 @@
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>564</v>
+      </c>
+      <c r="C147" s="3">
+        <v>46312</v>
+      </c>
+      <c r="D147" t="s">
+        <v>13</v>
+      </c>
+      <c r="E147" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">

--- a/__docs/RoadMap.xlsx
+++ b/__docs/RoadMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4872A07-C9FD-483A-BA35-93D419DE73EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B18D9D-B75E-40F5-AE1A-8E145BCFED69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тезисы" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Анализ нейронки стратегий" sheetId="7" r:id="rId7"/>
     <sheet name="Работа" sheetId="8" r:id="rId8"/>
     <sheet name="Текущие задачи" sheetId="9" r:id="rId9"/>
+    <sheet name="Идеи" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="625">
   <si>
     <t>RL3 - это продолжение RL1</t>
   </si>
@@ -1764,6 +1765,183 @@
   </si>
   <si>
     <t>Отбой от буффера линейной регрессии в окне</t>
+  </si>
+  <si>
+    <t>Трендовые линии по WZZ</t>
+  </si>
+  <si>
+    <t>Роботы с супертрендом (возможно с графическим стопом)</t>
+  </si>
+  <si>
+    <t>Феникс с вариациями действия через параметры</t>
+  </si>
+  <si>
+    <t>Зигзаг по дончану (фиксировать точки смены)</t>
+  </si>
+  <si>
+    <t>Рельсы в экстремумах DC</t>
+  </si>
+  <si>
+    <t>Пробой SMA, если ширина BB большая</t>
+  </si>
+  <si>
+    <t>ML-подход на отношение баров между собой</t>
+  </si>
+  <si>
+    <t>velcro на BB</t>
+  </si>
+  <si>
+    <t>Процентный буффер от SMA (канал в чем собирать)</t>
+  </si>
+  <si>
+    <t>Отложить несколько процентных буфферов от SMA (так называмая зебра)</t>
+  </si>
+  <si>
+    <t>Сборщик спреда, если мы внутри канала sma+проецентный буффер</t>
+  </si>
+  <si>
+    <t>Анализ выгодности открытия по времени</t>
+  </si>
+  <si>
+    <t>Оцифровать ленту и кластера</t>
+  </si>
+  <si>
+    <t>Подписать в тестере кол-во сделок на картинках</t>
+  </si>
+  <si>
+    <t>Доработать add_level и работу с ним</t>
+  </si>
+  <si>
+    <t>Трейлинг-стоп по add_level</t>
+  </si>
+  <si>
+    <t>Узнать у разработчкиов cscalp, как мудрый поставил таймер на стаканы</t>
+  </si>
+  <si>
+    <t>В тестер учет количество позитивных дней</t>
+  </si>
+  <si>
+    <t>Профиль объема и уровни по нему</t>
+  </si>
+  <si>
+    <t>Зоны обхема и анализ где входить и выходить</t>
+  </si>
+  <si>
+    <t>Ширину канала BB можно брать по относительному изменению значений</t>
+  </si>
+  <si>
+    <t>Алор баланс-покупок продаж с онлайн тестом, для анализа возможности использования</t>
+  </si>
+  <si>
+    <t>Уровни по DC (если сильно не изменился)</t>
+  </si>
+  <si>
+    <t>UEG6 фильтр на близость SMAs</t>
+  </si>
+  <si>
+    <t>SEG_mini с  онлайн оптимизацией</t>
+  </si>
+  <si>
+    <t>VT8 стартовый тайм мод</t>
+  </si>
+  <si>
+    <t>Anger с откатным вариантом, как феникс</t>
+  </si>
+  <si>
+    <t>Сборщикам выставлять сделку на место, где больше 100% объема в сумме</t>
+  </si>
+  <si>
+    <t>Решить проблему reset в OC</t>
+  </si>
+  <si>
+    <t>WEG биг бар и работа с ним. Смотреть где находится относительно канала</t>
+  </si>
+  <si>
+    <t>Тонкая колбаса для пробоя (возможно ml-колбаса)</t>
+  </si>
+  <si>
+    <t>Попробовать Ишимоку</t>
+  </si>
+  <si>
+    <t>Квадраты в окне</t>
+  </si>
+  <si>
+    <t>Квадраты с субпереходами (типа 10-квадрат 5-субпереход регрессия)</t>
+  </si>
+  <si>
+    <t>Индикатор главной линии</t>
+  </si>
+  <si>
+    <t>Подсчет кол-во очередных касаний краев DC</t>
+  </si>
+  <si>
+    <t>Полный график через отношения к последнему бару по данным UI</t>
+  </si>
+  <si>
+    <t>WS на 2 pedal одной определяем тренда, по второй торгуем</t>
+  </si>
+  <si>
+    <t>Оптимизация робота внтури дня. Дополнительная программа</t>
+  </si>
+  <si>
+    <t>Fractal dimension index fdi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hurst exponent </t>
+  </si>
+  <si>
+    <t>vertical horizinatla filter vhf</t>
+  </si>
+  <si>
+    <t>variance ratio test vr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">range compression z-score </t>
+  </si>
+  <si>
+    <t>percentle rank</t>
+  </si>
+  <si>
+    <t>blendaer score</t>
+  </si>
+  <si>
+    <t>Робот дебатер</t>
+  </si>
+  <si>
+    <t>Робот, а что если (проверять вход на каждой свече и считать лучшие условия для входа</t>
+  </si>
+  <si>
+    <t>Взаимосвязь активов через GNN</t>
+  </si>
+  <si>
+    <t>ML подход c WZZ</t>
+  </si>
+  <si>
+    <t>RL подход с WZZ</t>
+  </si>
+  <si>
+    <t>Анализ роботов  по отклонению от кривой доходности</t>
+  </si>
+  <si>
+    <t>Канал по среднему размеру размеру бара</t>
+  </si>
+  <si>
+    <t>Нужно работать на расширение волатильности</t>
+  </si>
+  <si>
+    <t>Вместо среднего брать значения на увеличение RSI</t>
+  </si>
+  <si>
+    <t>Использование WZZ для поиска структру на большем таймфрейме</t>
+  </si>
+  <si>
+    <t>С помощью канала линейной регрессии и DC определять фазу рынка</t>
+  </si>
+  <si>
+    <t>Приоритет</t>
+  </si>
+  <si>
+    <t>Канал по макс и мин отношению (отклонению?)</t>
   </si>
 </sst>
 </file>
@@ -2209,6 +2387,2210 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0A91E3F-F37C-4545-96E7-E4F4B465E1C2}">
+  <dimension ref="A1:C368"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="84.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>606</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>607</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>608</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>609</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>610</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>611</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>617</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>619</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>622</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>579</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>580</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>581</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>583</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>602</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>604</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>613</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>566</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>582</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>598</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>599</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>600</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>612</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>620</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>594</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>567</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>568</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>569</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>570</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>571</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>572</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>573</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>574</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>575</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>576</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>577</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>578</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>584</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>585</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>586</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>587</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>588</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>589</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>590</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>624</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>591</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>592</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>593</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>595</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>596</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>597</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>601</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>603</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>614</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>615</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>616</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>618</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>621</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A289">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A291">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A293">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A295">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A296">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A298">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A299">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A300">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A301">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A302">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A303">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A307">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A308">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A309">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A310">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A311">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A312">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A313">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A314">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A315">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A316">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A317">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A318">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A319">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A320">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A321">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A322">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A323">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A324">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A325">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A326">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A327">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A328">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A329">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A330">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A331">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A332">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A333">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A334">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A335">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A336">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A337">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A338">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A340">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A341">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A342">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A343">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A344">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A345">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A346">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A347">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A348">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A349">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A350">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A351">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A352">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A353">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A354">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A356">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A357">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A358">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A359">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A360">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A361">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A362">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A363">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A364">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A365">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A366">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A367">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A368">
+        <v>367</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:C369">
+    <sortCondition descending="1" ref="C2:C369"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E2C9599-8D49-4801-ADB3-0479553EEEEE}">
   <dimension ref="B2:C13"/>

--- a/__docs/RoadMap.xlsx
+++ b/__docs/RoadMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B18D9D-B75E-40F5-AE1A-8E145BCFED69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE92AF34-E7AD-49A6-A56E-8307045083E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тезисы" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="628">
   <si>
     <t>RL3 - это продолжение RL1</t>
   </si>
@@ -1902,9 +1902,6 @@
     <t>percentle rank</t>
   </si>
   <si>
-    <t>blendaer score</t>
-  </si>
-  <si>
     <t>Робот дебатер</t>
   </si>
   <si>
@@ -1942,6 +1939,18 @@
   </si>
   <si>
     <t>Канал по макс и мин отношению (отклонению?)</t>
+  </si>
+  <si>
+    <t>Индикатор моментум</t>
+  </si>
+  <si>
+    <t>Индикатор Монте-Карло</t>
+  </si>
+  <si>
+    <t>Посмотреть индикаторы на TV, которых у нас нет</t>
+  </si>
+  <si>
+    <t>blender score</t>
   </si>
 </sst>
 </file>
@@ -2392,19 +2401,20 @@
   <dimension ref="A1:C368"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
     <col min="2" max="2" width="84.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>605</v>
       </c>
       <c r="C2">
@@ -2415,7 +2425,7 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>606</v>
       </c>
       <c r="C3">
@@ -2426,7 +2436,7 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>607</v>
       </c>
       <c r="C4">
@@ -2437,7 +2447,7 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>608</v>
       </c>
       <c r="C5">
@@ -2448,7 +2458,7 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>609</v>
       </c>
       <c r="C6">
@@ -2459,7 +2469,7 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>610</v>
       </c>
       <c r="C7">
@@ -2470,8 +2480,8 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>611</v>
+      <c r="B8" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -2481,8 +2491,8 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>617</v>
+      <c r="B9" s="4" t="s">
+        <v>616</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -2493,7 +2503,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -2504,7 +2514,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -2581,7 +2591,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -2647,7 +2657,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -2658,7 +2668,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -2669,10 +2679,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>594</v>
+        <v>626</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -2680,7 +2690,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>567</v>
+        <v>594</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -2691,7 +2701,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -2702,7 +2712,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -2713,7 +2723,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -2724,7 +2734,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -2735,7 +2745,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -2746,7 +2756,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -2757,7 +2767,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -2768,7 +2778,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -2779,7 +2789,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -2790,7 +2800,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -2801,7 +2811,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -2812,7 +2822,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -2823,7 +2833,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -2834,7 +2844,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -2845,7 +2855,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -2856,7 +2866,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -2867,7 +2877,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -2878,7 +2888,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -2889,7 +2899,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>624</v>
+        <v>590</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -2900,7 +2910,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>591</v>
+        <v>623</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -2911,7 +2921,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -2922,7 +2932,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -2933,7 +2943,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -2944,7 +2954,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -2955,7 +2965,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -2966,7 +2976,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -2977,7 +2987,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -2988,7 +2998,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -2999,7 +3009,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -3010,7 +3020,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -3021,7 +3031,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -3032,7 +3042,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -3042,16 +3052,34 @@
       <c r="A60">
         <v>59</v>
       </c>
+      <c r="B60" t="s">
+        <v>620</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
+      <c r="B61" t="s">
+        <v>624</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
+      <c r="B62" t="s">
+        <v>625</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
@@ -4584,8 +4612,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:C369">
-    <sortCondition descending="1" ref="C2:C369"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:C368">
+    <sortCondition descending="1" ref="C2:C368"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/__docs/RoadMap.xlsx
+++ b/__docs/RoadMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE92AF34-E7AD-49A6-A56E-8307045083E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6314DA61-1457-46BC-B4B6-508004CB3EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тезисы" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="638">
   <si>
     <t>RL3 - это продолжение RL1</t>
   </si>
@@ -1815,9 +1815,6 @@
     <t>Трейлинг-стоп по add_level</t>
   </si>
   <si>
-    <t>Узнать у разработчкиов cscalp, как мудрый поставил таймер на стаканы</t>
-  </si>
-  <si>
     <t>В тестер учет количество позитивных дней</t>
   </si>
   <si>
@@ -1951,6 +1948,39 @@
   </si>
   <si>
     <t>blender score</t>
+  </si>
+  <si>
+    <t>PEG17_AIUR</t>
+  </si>
+  <si>
+    <t>PEG17_PHOENIX попытка исправить текущие проблемы</t>
+  </si>
+  <si>
+    <t>PEG17_ALDERA</t>
+  </si>
+  <si>
+    <t>сестра PEG17_SELENDIS с использованием cvd</t>
+  </si>
+  <si>
+    <t>SID с отдельным скаченным датафреймом для истории</t>
+  </si>
+  <si>
+    <t>Сделать торговых роботов на perchan</t>
+  </si>
+  <si>
+    <t>Сделать торговых роботов на предолженных дипсиком индикаторах тренда</t>
+  </si>
+  <si>
+    <t>PEG26_JUNKRAT</t>
+  </si>
+  <si>
+    <t>PEG26_GAZLOWE</t>
+  </si>
+  <si>
+    <t>Модификация PEG26_UNKNOWN. Только контр-тренд</t>
+  </si>
+  <si>
+    <t>Модификация PEG26_UNKNOWN. С добавление пробоя</t>
   </si>
 </sst>
 </file>
@@ -2085,7 +2115,18 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2407,95 +2448,95 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>605</v>
+      <c r="B2" t="s">
+        <v>573</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>606</v>
+      <c r="B3" t="s">
+        <v>588</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>607</v>
+      <c r="B4" t="s">
+        <v>591</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>608</v>
+      <c r="B5" t="s">
+        <v>599</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>609</v>
+      <c r="B6" t="s">
+        <v>602</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>610</v>
+      <c r="B7" t="s">
+        <v>620</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>627</v>
+      <c r="B8" t="s">
+        <v>597</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>616</v>
+      <c r="B9" t="s">
+        <v>598</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2503,32 +2544,32 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>621</v>
+      <c r="B11" s="17" t="s">
+        <v>632</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>579</v>
+      <c r="B12" s="17" t="s">
+        <v>633</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -2536,10 +2577,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -2547,10 +2588,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -2558,10 +2599,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -2569,10 +2610,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>602</v>
+        <v>581</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -2580,10 +2621,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2591,10 +2632,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>612</v>
+        <v>566</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -2602,10 +2643,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -2613,10 +2654,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>582</v>
+        <v>622</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2624,10 +2665,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -2635,10 +2676,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -2646,10 +2687,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -2657,10 +2698,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -2668,10 +2709,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -2679,10 +2720,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>626</v>
+        <v>585</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -2690,10 +2731,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -2701,10 +2742,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -2712,10 +2753,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>568</v>
+        <v>583</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -2723,10 +2764,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -2734,10 +2775,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -2745,10 +2786,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>571</v>
+        <v>582</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -2756,10 +2797,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>572</v>
+        <v>616</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -2767,10 +2808,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>573</v>
+        <v>619</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -2778,10 +2819,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -2789,10 +2830,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -2800,7 +2841,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>576</v>
+        <v>625</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -2811,7 +2852,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>577</v>
+        <v>593</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -2822,7 +2863,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -2833,7 +2874,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>584</v>
+        <v>569</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -2844,7 +2885,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>585</v>
+        <v>570</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -2855,7 +2896,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>586</v>
+        <v>571</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -2866,7 +2907,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>587</v>
+        <v>572</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -2877,7 +2918,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -2888,7 +2929,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -2899,7 +2940,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -2910,7 +2951,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>623</v>
+        <v>596</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -2921,7 +2962,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -2932,7 +2973,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>592</v>
+        <v>612</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -2943,7 +2984,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>593</v>
+        <v>613</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -2954,7 +2995,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>595</v>
+        <v>614</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -2965,7 +3006,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>596</v>
+        <v>623</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -2976,7 +3017,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>597</v>
+        <v>624</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -2986,8 +3027,8 @@
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
-        <v>601</v>
+      <c r="B54" s="17" t="s">
+        <v>631</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -2997,99 +3038,111 @@
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" t="s">
-        <v>603</v>
+      <c r="B55" s="17" t="s">
+        <v>568</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
-        <v>613</v>
+      <c r="B56" s="17" t="s">
+        <v>574</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" t="s">
-        <v>614</v>
+      <c r="B57" s="17" t="s">
+        <v>604</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
-        <v>615</v>
+      <c r="B58" s="17" t="s">
+        <v>605</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" t="s">
-        <v>617</v>
+      <c r="B59" s="17" t="s">
+        <v>606</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
-        <v>620</v>
+      <c r="B60" s="17" t="s">
+        <v>607</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" t="s">
-        <v>624</v>
+      <c r="B61" s="17" t="s">
+        <v>608</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" t="s">
-        <v>625</v>
+      <c r="B62" s="17" t="s">
+        <v>609</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
+      <c r="B63" s="17" t="s">
+        <v>626</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
+      <c r="B64" s="17" t="s">
+        <v>615</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65">
@@ -4612,9 +4665,14 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:C368">
-    <sortCondition descending="1" ref="C2:C368"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:C369">
+    <sortCondition descending="1" ref="C2:C369"/>
   </sortState>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7886,7 +7944,7 @@
       </c>
       <c r="L2">
         <f>COUNTIF(D:D,L1)</f>
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="M2">
         <f>COUNTIF(D:D,M1)</f>
@@ -10530,20 +10588,68 @@
       <c r="A148">
         <v>147</v>
       </c>
+      <c r="B148" t="s">
+        <v>627</v>
+      </c>
+      <c r="C148" s="3">
+        <v>46318</v>
+      </c>
+      <c r="D148" t="s">
+        <v>12</v>
+      </c>
+      <c r="E148" t="s">
+        <v>628</v>
+      </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
+      <c r="B149" t="s">
+        <v>629</v>
+      </c>
+      <c r="C149" s="3">
+        <v>46318</v>
+      </c>
+      <c r="D149" t="s">
+        <v>12</v>
+      </c>
+      <c r="E149" t="s">
+        <v>630</v>
+      </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
+      <c r="B150" t="s">
+        <v>634</v>
+      </c>
+      <c r="C150" s="3">
+        <v>46318</v>
+      </c>
+      <c r="D150" t="s">
+        <v>12</v>
+      </c>
+      <c r="E150" t="s">
+        <v>636</v>
+      </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>635</v>
+      </c>
+      <c r="C151" s="3">
+        <v>46318</v>
+      </c>
+      <c r="D151" t="s">
+        <v>12</v>
+      </c>
+      <c r="E151" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">

--- a/__docs/RoadMap.xlsx
+++ b/__docs/RoadMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6314DA61-1457-46BC-B4B6-508004CB3EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A33A4A-32D9-4D56-B0EF-403C0CA92FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тезисы" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="Работа" sheetId="8" r:id="rId8"/>
     <sheet name="Текущие задачи" sheetId="9" r:id="rId9"/>
     <sheet name="Идеи" sheetId="10" r:id="rId10"/>
+    <sheet name="Выполненные идеи" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="652">
   <si>
     <t>RL3 - это продолжение RL1</t>
   </si>
@@ -1981,6 +1982,48 @@
   </si>
   <si>
     <t>Модификация PEG26_UNKNOWN. С добавление пробоя</t>
+  </si>
+  <si>
+    <t>Робот похожий на Survivalist, только с двумя парами sma. Одна для определения тренда, другая для торговли</t>
+  </si>
+  <si>
+    <t>Нужно как-то определять все направление окна, а внутри уже собирать в соостветствии с направлением в более маленьком формате</t>
+  </si>
+  <si>
+    <t>Индикатор предполагающий направление объема.  Типа, если был большой бар, но его перекрыли, то занчит это было завершение  тренда, если после большого бара тренд продолжается, то значит можно считать этот бар поддержкой и закреплением направления</t>
+  </si>
+  <si>
+    <t>Феникс с выходом по фибо</t>
+  </si>
+  <si>
+    <t>Робот с зонами поглощения по зигзагу</t>
+  </si>
+  <si>
+    <t>Индикатор объема по тренду. Анализировать бары, как ленту.</t>
+  </si>
+  <si>
+    <t>у VT8 метод run_middleware</t>
+  </si>
+  <si>
+    <t>N-баров растет - становимся в шорт</t>
+  </si>
+  <si>
+    <t>робот на ii, если 100% то шорт</t>
+  </si>
+  <si>
+    <t>Индикатор возвратного движения в максимуме и минимуме. Проверять, сколько процентов движения откатилось</t>
+  </si>
+  <si>
+    <t>СС с новыми индикаторами</t>
+  </si>
+  <si>
+    <t>Автоматическая расстоновка в VT</t>
+  </si>
+  <si>
+    <t>Проверить файлы конфигурации VT (может их можно менять)</t>
+  </si>
+  <si>
+    <t>Робот на боллинджере, как только прикрепляемся - идем в пробой, как только открепляемся идем в отбой. Наверное фильтром должна быть ширина BB</t>
   </si>
 </sst>
 </file>
@@ -2023,7 +2066,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2060,6 +2103,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2073,7 +2122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2111,11 +2160,62 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2456,7 +2556,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>573</v>
+        <v>588</v>
       </c>
       <c r="C2">
         <v>6</v>
@@ -2467,7 +2567,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -2478,10 +2578,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2489,7 +2589,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -2499,8 +2599,8 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>602</v>
+      <c r="B6" s="17" t="s">
+        <v>641</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -2510,33 +2610,33 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>620</v>
+      <c r="B7" s="17" t="s">
+        <v>645</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>597</v>
+      <c r="B8" s="17" t="s">
+        <v>646</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>598</v>
+      <c r="B9" s="17" t="s">
+        <v>651</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2544,7 +2644,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2554,8 +2654,8 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="17" t="s">
-        <v>632</v>
+      <c r="B11" t="s">
+        <v>597</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2565,8 +2665,8 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="17" t="s">
-        <v>633</v>
+      <c r="B12" t="s">
+        <v>598</v>
       </c>
       <c r="C12">
         <v>4</v>
@@ -2577,54 +2677,54 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>575</v>
+        <v>610</v>
       </c>
       <c r="C13">
-        <v>3.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>576</v>
+      <c r="B14" s="17" t="s">
+        <v>632</v>
       </c>
       <c r="C14">
-        <v>3.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>580</v>
+      <c r="B15" s="17" t="s">
+        <v>633</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>581</v>
+      <c r="B16" s="17" t="s">
+        <v>642</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>611</v>
+      <c r="B17" s="17" t="s">
+        <v>648</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2632,10 +2732,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -2643,10 +2743,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>587</v>
+        <v>576</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -2654,7 +2754,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>622</v>
+        <v>580</v>
       </c>
       <c r="C20">
         <v>3</v>
@@ -2665,7 +2765,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="C21">
         <v>3</v>
@@ -2676,10 +2776,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="C22">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -2687,10 +2787,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>589</v>
+        <v>566</v>
       </c>
       <c r="C23">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -2698,10 +2798,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>617</v>
+        <v>587</v>
       </c>
       <c r="C24">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -2709,10 +2809,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C25">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -2720,10 +2820,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="C26">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -2731,10 +2831,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C27">
-        <v>2.2000000000000002</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -2742,10 +2842,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C28">
-        <v>2.2000000000000002</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -2753,10 +2853,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>583</v>
+        <v>617</v>
       </c>
       <c r="C29">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -2764,10 +2864,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>584</v>
+        <v>618</v>
       </c>
       <c r="C30">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -2775,10 +2875,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -2786,10 +2886,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>582</v>
+        <v>601</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -2797,10 +2897,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>616</v>
+        <v>590</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -2808,10 +2908,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>619</v>
+        <v>583</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -2819,10 +2919,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C35">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -2830,10 +2930,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C36">
-        <v>1.1000000000000001</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -2841,10 +2941,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>625</v>
+        <v>582</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -2852,10 +2952,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>593</v>
+        <v>616</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -2863,54 +2963,54 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>567</v>
+        <v>619</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
-        <v>569</v>
+      <c r="B40" s="17" t="s">
+        <v>638</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
-        <v>570</v>
+      <c r="B41" s="17" t="s">
+        <v>639</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
-        <v>571</v>
+      <c r="B42" s="17" t="s">
+        <v>640</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
-        <v>572</v>
+      <c r="B43" s="17" t="s">
+        <v>643</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2918,10 +3018,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2929,10 +3029,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>594</v>
+        <v>578</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -2940,7 +3040,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>595</v>
+        <v>625</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -2951,7 +3051,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -2962,7 +3062,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>600</v>
+        <v>567</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -2973,7 +3073,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>612</v>
+        <v>569</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -2984,7 +3084,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>613</v>
+        <v>570</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -2995,7 +3095,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>614</v>
+        <v>571</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -3006,7 +3106,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>623</v>
+        <v>572</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -3017,7 +3117,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>624</v>
+        <v>577</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -3027,8 +3127,8 @@
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" s="17" t="s">
-        <v>631</v>
+      <c r="B54" t="s">
+        <v>594</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -3038,88 +3138,88 @@
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" s="17" t="s">
-        <v>568</v>
+      <c r="B55" t="s">
+        <v>595</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" s="17" t="s">
-        <v>574</v>
+      <c r="B56" t="s">
+        <v>596</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" s="17" t="s">
-        <v>604</v>
+      <c r="B57" t="s">
+        <v>600</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" s="17" t="s">
-        <v>605</v>
+      <c r="B58" t="s">
+        <v>612</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" s="17" t="s">
-        <v>606</v>
+      <c r="B59" t="s">
+        <v>613</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" s="17" t="s">
-        <v>607</v>
+      <c r="B60" t="s">
+        <v>614</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" s="17" t="s">
-        <v>608</v>
+      <c r="B61" t="s">
+        <v>623</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" s="17" t="s">
-        <v>609</v>
+      <c r="B62" t="s">
+        <v>624</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -3127,10 +3227,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -3138,10 +3238,1909 @@
         <v>63</v>
       </c>
       <c r="B64" s="17" t="s">
+        <v>644</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" s="17" t="s">
+        <v>647</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" s="17" t="s">
+        <v>649</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A289">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A291">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A293">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A295">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A296">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A298">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A299">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A300">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A301">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A302">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A303">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A307">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A308">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A309">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A310">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A311">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A312">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A313">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A314">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A315">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A316">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A317">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A318">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A319">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A320">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A321">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A322">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A323">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A324">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A325">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A326">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A327">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A328">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A329">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A330">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A331">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A332">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A333">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A334">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A335">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A336">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A337">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A338">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A340">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A341">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A342">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A343">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A344">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A345">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A346">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A347">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A348">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A349">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A350">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A351">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A352">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A353">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A354">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A356">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A357">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A358">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A359">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A360">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A361">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A362">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A363">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A364">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A365">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A366">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A367">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A368">
+        <v>367</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:C368">
+    <sortCondition descending="1" ref="C2:C368"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A24498-4D9E-45FA-80E7-A529576A45A3}">
+  <dimension ref="A2:B525"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="91.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="17" t="s">
         <v>615</v>
       </c>
-      <c r="C64">
-        <v>0</v>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
@@ -4664,15 +6663,792 @@
         <v>367</v>
       </c>
     </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A369">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A370">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A371">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A372">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A373">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A374">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A375">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A376">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A377">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A378">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A379">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A380">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A381">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A382">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A383">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A384">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A385">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A386">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A387">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A388">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A389">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A390">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A391">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A392">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A393">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A394">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A395">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A396">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A397">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A398">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A399">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A400">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A401">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A402">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A403">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A404">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A405">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A406">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A407">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A408">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A409">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A410">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A411">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A412">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A413">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A414">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A415">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A416">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A417">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A418">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A419">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A420">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A421">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A422">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A423">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A424">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A425">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A426">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A427">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A428">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A429">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A430">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A431">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A432">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A433">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A434">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A435">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A436">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A437">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A438">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A439">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A440">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A441">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A442">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A443">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A444">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A445">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A446">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A447">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A448">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A449">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A450">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A451">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A452">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A453">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A454">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A455">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A456">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A457">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A458">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A459">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A460">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A461">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A462">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A463">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A464">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A465">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A466">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A467">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A468">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A469">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A470">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A471">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A472">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A473">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A474">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A475">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A476">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A477">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A478">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A479">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A480">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A481">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A482">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A483">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A484">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A485">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A486">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A487">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A488">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A489">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A490">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A491">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A492">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A493">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A494">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A495">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A496">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="497" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A497">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="498" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A498">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="499" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A499">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="500" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A500">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="501" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A501">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="502" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A502">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="503" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A503">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="504" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A504">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="505" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A505">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="506" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A506">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="507" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A507">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="508" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A508">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="509" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A509">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="510" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A510">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="511" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A511">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="512" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A512">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="513" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A513">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="514" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A514">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="515" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A515">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="516" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A516">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="517" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A517">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="518" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A518">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="519" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A519">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="520" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A520">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="521" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A521">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="522" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A522">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="523" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A523">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="524" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A524">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="525" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A525">
+        <v>524</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:C369">
-    <sortCondition descending="1" ref="C2:C369"/>
-  </sortState>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
